--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\_Projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8FB0A2-CF35-4336-86E8-6FC5E284924D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786CC19C-4F78-4E7F-88C4-8A344D9C5BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="23160" windowHeight="13040" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="89">
   <si>
     <t>Planification globale</t>
   </si>
@@ -176,9 +176,6 @@
     <t xml:space="preserve">Créer game.php  </t>
   </si>
   <si>
-    <t>Créer ganeAction:executeAction, movePiece</t>
-  </si>
-  <si>
     <t>Créer le composant : Board(grille 10x10, zones infranchissables)</t>
   </si>
   <si>
@@ -258,6 +255,48 @@
   </si>
   <si>
     <t>Dans la page index.jsx : ajout du formulaire (signup, signin, signout)</t>
+  </si>
+  <si>
+    <t>Implémentation du LobbyManager</t>
+  </si>
+  <si>
+    <t>Implémentation du Controleur</t>
+  </si>
+  <si>
+    <t>Implémentation du GameManager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Développement de l'IA - Algorithme MCTS </t>
+  </si>
+  <si>
+    <t>Créer la classe Board</t>
+  </si>
+  <si>
+    <t>Créer la classe User/Player</t>
+  </si>
+  <si>
+    <t>Créer la classe Move</t>
+  </si>
+  <si>
+    <t>Créer la classe Piece</t>
+  </si>
+  <si>
+    <t>Créer gameAction:executeAction, movePiece</t>
+  </si>
+  <si>
+    <t>Créer la classe AIPlayer</t>
+  </si>
+  <si>
+    <t>Créer la classe ObservedPiece/BeliefPiece</t>
+  </si>
+  <si>
+    <t>Créer la classe Node et la classe InfoSet</t>
+  </si>
+  <si>
+    <t>Créer la classe MCTS</t>
+  </si>
+  <si>
+    <t>Communication entre le serveur et le client (envois/réceptions)</t>
   </si>
 </sst>
 </file>
@@ -384,9 +423,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -424,7 +463,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -530,7 +569,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -672,7 +711,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -680,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A98864-B157-464B-9C9C-D10C2E7AC6B8}">
-  <dimension ref="B1:F102"/>
+  <dimension ref="B1:F101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.1796875" customWidth="1"/>
@@ -704,7 +743,7 @@
     </row>
     <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -842,7 +881,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>34</v>
@@ -963,7 +1002,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>34</v>
@@ -974,7 +1013,7 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>34</v>
@@ -985,7 +1024,7 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>34</v>
@@ -996,7 +1035,7 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>34</v>
@@ -1007,7 +1046,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>34</v>
@@ -1018,7 +1057,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>28</v>
@@ -1029,10 +1068,10 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1040,7 +1079,7 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>34</v>
@@ -1051,7 +1090,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>34</v>
@@ -1062,7 +1101,7 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>34</v>
@@ -1073,7 +1112,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>28</v>
@@ -1084,7 +1123,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>28</v>
@@ -1095,7 +1134,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>32</v>
@@ -1106,7 +1145,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>32</v>
@@ -1117,7 +1156,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>32</v>
@@ -1128,7 +1167,7 @@
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>34</v>
@@ -1139,7 +1178,7 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>28</v>
@@ -1175,7 +1214,7 @@
         <v>67</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -1186,7 +1225,7 @@
         <v>68</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -1194,10 +1233,10 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -1208,7 +1247,7 @@
         <v>71</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -1219,7 +1258,7 @@
         <v>72</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -1227,95 +1266,143 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
+      <c r="B54" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
+      <c r="B62" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
+      <c r="B64" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -1579,19 +1666,12 @@
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E102" xr:uid="{C1E49912-FB61-4F2F-8F8F-588FF6944C57}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E44 E45:E101" xr:uid="{C1E49912-FB61-4F2F-8F8F-588FF6944C57}">
       <formula1>"Haute,Moyenne,Basse,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D102" xr:uid="{A1B83402-03F9-4A0F-BE40-AAB54D35ECC4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D44 D45:D101" xr:uid="{A1B83402-03F9-4A0F-BE40-AAB54D35ECC4}">
       <formula1>"Sprint 1,Sprint 2,Sprint 3,Sprint 4,"</formula1>
     </dataValidation>
   </dataValidations>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786CC19C-4F78-4E7F-88C4-8A344D9C5BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762792D6-77CB-42B8-8643-629A33515C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Sprint 3" sheetId="4" r:id="rId5"/>
     <sheet name="Sprint 4" sheetId="5" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$1:$D$101</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="116">
   <si>
     <t>Planification globale</t>
   </si>
@@ -236,9 +239,6 @@
     <t>Implémentation du chat entre joueurs: céation de la base de donnée, affichage</t>
   </si>
   <si>
-    <t>Implémentation des options d'accessibilité (langie,contraste élevé,suppression animations)</t>
-  </si>
-  <si>
     <t>Serveur/client</t>
   </si>
   <si>
@@ -297,6 +297,90 @@
   </si>
   <si>
     <t>Communication entre le serveur et le client (envois/réceptions)</t>
+  </si>
+  <si>
+    <t>Implémentation des options d'accessibilité (langue,contraste élevé,suppression animations)</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation du système de tours </t>
+  </si>
+  <si>
+    <t>Logique de score</t>
+  </si>
+  <si>
+    <t>Implémentation de la logique de déplacement des pièces</t>
+  </si>
+  <si>
+    <t>Validation des mouvements</t>
+  </si>
+  <si>
+    <t>Vérification du placement initial des pièces</t>
+  </si>
+  <si>
+    <t>Affichage fin de partie</t>
+  </si>
+  <si>
+    <t>Implémentation des règles du jeu (sans combat)</t>
+  </si>
+  <si>
+    <t>Création de la base de données MySQL et de la table users</t>
+  </si>
+  <si>
+    <t>Base de données</t>
+  </si>
+  <si>
+    <t>Implémentation de la logique de connection de joueur (jeton)</t>
+  </si>
+  <si>
+    <t>Création du reste des tables de la base de données</t>
+  </si>
+  <si>
+    <t>Choix du projet</t>
+  </si>
+  <si>
+    <t>Choix de l'équipe</t>
+  </si>
+  <si>
+    <t>Document de définition</t>
+  </si>
+  <si>
+    <t>Document de conception</t>
+  </si>
+  <si>
+    <t>Document de planification</t>
+  </si>
+  <si>
+    <t>Diagramme de classes</t>
+  </si>
+  <si>
+    <t>Diagramme de base de données</t>
+  </si>
+  <si>
+    <t>Diagramme de cas d'usage</t>
+  </si>
+  <si>
+    <t>Maquette</t>
+  </si>
+  <si>
+    <t>Semaine E</t>
+  </si>
+  <si>
+    <t>Eddy</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Eddy/Charlotte</t>
+  </si>
+  <si>
+    <t>Communication entre le Charlotte et le Eddy (envois/réceptions)</t>
+  </si>
+  <si>
+    <t>Charlotte/Eddy</t>
   </si>
 </sst>
 </file>
@@ -339,7 +423,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,8 +436,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -390,11 +486,211 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -405,6 +701,77 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -765,7 +1132,9 @@
       <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
@@ -776,7 +1145,9 @@
       <c r="C7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
@@ -787,7 +1158,9 @@
       <c r="C8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
@@ -798,7 +1171,9 @@
       <c r="C9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
@@ -809,7 +1184,9 @@
       <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
@@ -820,7 +1197,9 @@
       <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
@@ -831,7 +1210,9 @@
       <c r="C12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
@@ -842,7 +1223,9 @@
       <c r="C13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
@@ -853,7 +1236,9 @@
       <c r="C14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
@@ -864,7 +1249,9 @@
       <c r="C15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
@@ -875,18 +1262,22 @@
       <c r="C16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
@@ -897,7 +1288,9 @@
       <c r="C18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
@@ -908,7 +1301,9 @@
       <c r="C19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
@@ -919,7 +1314,9 @@
       <c r="C20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
@@ -930,7 +1327,9 @@
       <c r="C21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
@@ -941,7 +1340,9 @@
       <c r="C22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
@@ -952,7 +1353,9 @@
       <c r="C23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
@@ -963,7 +1366,9 @@
       <c r="C24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
@@ -974,7 +1379,9 @@
       <c r="C25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
@@ -985,7 +1392,9 @@
       <c r="C26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
@@ -996,18 +1405,22 @@
       <c r="C27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
@@ -1018,7 +1431,9 @@
       <c r="C29" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
@@ -1029,18 +1444,22 @@
       <c r="C30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
@@ -1051,7 +1470,9 @@
       <c r="C32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
@@ -1062,7 +1483,9 @@
       <c r="C33" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
@@ -1073,7 +1496,9 @@
       <c r="C34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
@@ -1084,7 +1509,9 @@
       <c r="C35" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
@@ -1095,7 +1522,9 @@
       <c r="C36" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
@@ -1106,7 +1535,9 @@
       <c r="C37" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
@@ -1117,7 +1548,9 @@
       <c r="C38" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
@@ -1128,7 +1561,9 @@
       <c r="C39" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
@@ -1139,7 +1574,9 @@
       <c r="C40" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
@@ -1150,7 +1587,9 @@
       <c r="C41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="3"/>
+      <c r="D41" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
@@ -1161,7 +1600,9 @@
       <c r="C42" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
@@ -1172,7 +1613,9 @@
       <c r="C43" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
@@ -1183,7 +1626,9 @@
       <c r="C44" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
@@ -1194,7 +1639,9 @@
       <c r="C45" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
@@ -1205,7 +1652,9 @@
       <c r="C46" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="3"/>
+      <c r="D46" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
@@ -1216,257 +1665,329 @@
       <c r="C47" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="3"/>
+      <c r="D47" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D50" s="3"/>
+      <c r="D50" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D51" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="3"/>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D53" s="3"/>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D54" s="3"/>
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D59" s="3"/>
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B65" s="3"/>
+      <c r="B65" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B66" s="3"/>
+      <c r="B66" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B67" s="3"/>
+      <c r="B67" s="10" t="s">
+        <v>103</v>
+      </c>
       <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B69" s="3"/>
+      <c r="B69" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
+      <c r="D69" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B70" s="3"/>
+      <c r="B70" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
+      <c r="D70" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B71" s="3"/>
+      <c r="B71" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
+      <c r="D71" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="3"/>
+      <c r="B72" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B73" s="3"/>
+      <c r="B73" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
+      <c r="D73" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
@@ -1667,11 +2188,12 @@
       <c r="F101" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:D101" xr:uid="{E2A98864-B157-464B-9C9C-D10C2E7AC6B8}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E44 E45:E101" xr:uid="{C1E49912-FB61-4F2F-8F8F-588FF6944C57}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E101" xr:uid="{C1E49912-FB61-4F2F-8F8F-588FF6944C57}">
       <formula1>"Haute,Moyenne,Basse,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D44 D45:D101" xr:uid="{A1B83402-03F9-4A0F-BE40-AAB54D35ECC4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D101" xr:uid="{A1B83402-03F9-4A0F-BE40-AAB54D35ECC4}">
       <formula1>"Sprint 1,Sprint 2,Sprint 3,Sprint 4,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1682,29 +2204,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC485589-D367-4045-AC2C-21AA964CF385}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.54296875" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" customWidth="1"/>
     <col min="5" max="5" width="19.81640625" customWidth="1"/>
     <col min="6" max="6" width="18.7265625" customWidth="1"/>
     <col min="7" max="7" width="9.7265625" customWidth="1"/>
-    <col min="8" max="8" width="16.26953125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
     <col min="9" max="9" width="18.7265625" customWidth="1"/>
     <col min="10" max="10" width="9.54296875" customWidth="1"/>
     <col min="11" max="11" width="16.1796875" customWidth="1"/>
     <col min="12" max="12" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1723,8 +2245,18 @@
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.5">
+      <c r="M3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1759,265 +2291,840 @@
       <c r="L4" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="L12" s="5"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="L16" s="5"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="L19" s="5"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="L22" s="5"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="L23" s="5"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="L24" s="5"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="L25" s="5"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="L26" s="5"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="L27" s="5"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="L28" s="5"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="L29" s="5"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="L30" s="5"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="L31" s="5"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="L32" s="5"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="L33" s="5"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="L34" s="5"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="L35" s="5"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="L36" s="5"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="L37" s="5"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="L38" s="5"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="L39" s="5"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="L40" s="5"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="L41" s="5"/>
+      <c r="M4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="17"/>
+      <c r="B5" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="33">
+        <v>1</v>
+      </c>
+      <c r="F5" s="34"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="15"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" s="17"/>
+      <c r="B6" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="47"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="36">
+        <v>1</v>
+      </c>
+      <c r="I6" s="37"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="18"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" s="17"/>
+      <c r="B7" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="47"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="J7" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" s="36">
+        <v>1</v>
+      </c>
+      <c r="L7" s="37"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="18"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="17"/>
+      <c r="B8" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="47"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="J8" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="K8" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="L8" s="18"/>
+      <c r="M8" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="N8" s="36">
+        <v>1</v>
+      </c>
+      <c r="O8" s="38"/>
+      <c r="P8" s="52"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="18"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" s="17"/>
+      <c r="B9" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="47"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="N9" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="O9" s="17"/>
+      <c r="P9" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="41"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10" s="17"/>
+      <c r="B10" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="K10" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="N10" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="41"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" s="17"/>
+      <c r="B11" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="47"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="K11" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="N11" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="O11" s="17"/>
+      <c r="P11" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="41"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" s="17"/>
+      <c r="B12" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="47"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="K12" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="N12" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="O12" s="17"/>
+      <c r="P12" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="41"/>
+    </row>
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="17"/>
+      <c r="B13" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="N13" s="28">
+        <v>0.8</v>
+      </c>
+      <c r="O13" s="21"/>
+      <c r="P13" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="45"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2026,11 +3133,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31117888-BBE7-4BD8-9871-AB22BAD895CD}">
-  <dimension ref="B1:L41"/>
+  <dimension ref="B1:L40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" customWidth="1"/>
+    <col min="2" max="2" width="77.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.26953125" customWidth="1"/>
     <col min="4" max="4" width="15.54296875" customWidth="1"/>
     <col min="5" max="5" width="20.81640625" customWidth="1"/>
@@ -2065,7 +3172,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -2101,263 +3208,688 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="8"/>
-      <c r="C5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="B5" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="15"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="B6" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="8"/>
-      <c r="C7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="B7" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="8"/>
-      <c r="C8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="B8" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="8"/>
-      <c r="C9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="L9" s="5"/>
+      <c r="B9" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="8"/>
-      <c r="C10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="B10" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="8"/>
-      <c r="C11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="L11" s="5"/>
+      <c r="B11" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="8"/>
-      <c r="C12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="L12" s="5"/>
+      <c r="B12" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="8"/>
-      <c r="C13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="L13" s="5"/>
+      <c r="B13" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="8"/>
-      <c r="C14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="B14" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="18"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="8"/>
-      <c r="C15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="L15" s="5"/>
+      <c r="B15" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="18"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="8"/>
-      <c r="C16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="L16" s="5"/>
+      <c r="B16" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="8"/>
-      <c r="C17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="B17" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="30"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="8"/>
-      <c r="C18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="B18" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="30"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="8"/>
-      <c r="C19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="B19" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="8"/>
-      <c r="C20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="L20" s="5"/>
+      <c r="B20" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="30"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="18"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="8"/>
-      <c r="C21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="L21" s="5"/>
+      <c r="B21" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="30"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="8"/>
-      <c r="C22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="L22" s="5"/>
+      <c r="B22" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="18"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="8"/>
-      <c r="C23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="L23" s="5"/>
+      <c r="B23" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="30"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="18"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="8"/>
-      <c r="C24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="L24" s="5"/>
+      <c r="B24" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="30"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="17"/>
+      <c r="L24" s="18"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="8"/>
-      <c r="C25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="B25" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="30"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="17"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="8"/>
-      <c r="C26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="L26" s="5"/>
+      <c r="B26" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="30"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K26" s="17"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="8"/>
-      <c r="C27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="L27" s="5"/>
+      <c r="B27" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="30"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K27" s="17"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="8"/>
-      <c r="C28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="B28" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="30"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K28" s="17"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="8"/>
-      <c r="C29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="L29" s="5"/>
+      <c r="B29" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="30"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K29" s="17"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="8"/>
-      <c r="C30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="L30" s="5"/>
+      <c r="B30" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="30"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K30" s="17"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="8"/>
-      <c r="C31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="L31" s="5"/>
+      <c r="B31" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="30"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K31" s="17"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="8"/>
-      <c r="C32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="L32" s="5"/>
+      <c r="B32" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K32" s="17"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="8"/>
-      <c r="C33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="L33" s="5"/>
+      <c r="B33" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="30"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K33" s="17"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="8"/>
-      <c r="C34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="L34" s="5"/>
+      <c r="B34" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="30"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K34" s="17"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35" s="8"/>
-      <c r="C35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="L35" s="5"/>
+      <c r="B35" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="30"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K35" s="17"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36" s="8"/>
-      <c r="C36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="L36" s="5"/>
+      <c r="B36" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="30"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K36" s="17"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37" s="8"/>
-      <c r="C37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="B37" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="30"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K37" s="17"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38" s="8"/>
-      <c r="C38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="L38" s="5"/>
+      <c r="B38" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="30"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K38" s="17"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39" s="8"/>
-      <c r="C39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="L39" s="5"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B40" s="8"/>
-      <c r="C40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="L40" s="5"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B41" s="8"/>
-      <c r="C41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="L41" s="5"/>
+      <c r="B39" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="30"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="K39" s="17"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="31"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="K40" s="21"/>
+      <c r="L40" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2550,11 +4082,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A181AE-6DCE-4F2E-9BC3-78C1EB9A33C7}">
-  <dimension ref="B1:L41"/>
+  <dimension ref="B1:L40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" customWidth="1"/>
+    <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.1796875" customWidth="1"/>
     <col min="4" max="4" width="15.7265625" customWidth="1"/>
     <col min="5" max="5" width="21.26953125" customWidth="1"/>
@@ -2591,7 +4123,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -2627,263 +4159,642 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="8"/>
-      <c r="C5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="B5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="15"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="5"/>
+      <c r="B6" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="17"/>
       <c r="F6" s="5"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="8"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="17"/>
       <c r="F7" s="5"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
       <c r="I7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="8"/>
-      <c r="C8" s="5"/>
+      <c r="B8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="17"/>
       <c r="F8" s="5"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
       <c r="I8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="8"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="17"/>
       <c r="F9" s="5"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
       <c r="I9" s="5"/>
-      <c r="L9" s="5"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="8"/>
-      <c r="C10" s="5"/>
+      <c r="B10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
       <c r="F10" s="5"/>
+      <c r="G10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="17"/>
       <c r="I10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="8"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="5"/>
+      <c r="G11" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="17"/>
       <c r="I11" s="5"/>
-      <c r="L11" s="5"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="8"/>
-      <c r="C12" s="5"/>
+      <c r="B12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
       <c r="F12" s="5"/>
+      <c r="G12" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="17"/>
       <c r="I12" s="5"/>
-      <c r="L12" s="5"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="8"/>
-      <c r="C13" s="5"/>
+      <c r="B13" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
       <c r="F13" s="5"/>
+      <c r="G13" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="17"/>
       <c r="I13" s="5"/>
-      <c r="L13" s="5"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="8"/>
-      <c r="C14" s="5"/>
+      <c r="B14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
       <c r="F14" s="5"/>
+      <c r="G14" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="17"/>
       <c r="I14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="18"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="8"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="5"/>
+      <c r="G15" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="17"/>
       <c r="I15" s="5"/>
-      <c r="L15" s="5"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="18"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="8"/>
-      <c r="C16" s="5"/>
+      <c r="B16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
       <c r="F16" s="5"/>
+      <c r="G16" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="17"/>
       <c r="I16" s="5"/>
-      <c r="L16" s="5"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="8"/>
-      <c r="C17" s="5"/>
+      <c r="B17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="5"/>
+      <c r="G17" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="17"/>
       <c r="I17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="8"/>
-      <c r="C18" s="5"/>
+      <c r="B18" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
       <c r="F18" s="5"/>
+      <c r="G18" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="17"/>
       <c r="I18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="8"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="5"/>
+      <c r="G19" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="17"/>
       <c r="I19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="8"/>
-      <c r="C20" s="5"/>
+      <c r="B20" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="5"/>
+      <c r="G20" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="17"/>
       <c r="I20" s="5"/>
-      <c r="L20" s="5"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="18"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="8"/>
-      <c r="C21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="L21" s="5"/>
+      <c r="B21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="8"/>
-      <c r="C22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="L22" s="5"/>
+      <c r="B22" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="8"/>
-      <c r="C23" s="5"/>
+      <c r="B23" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="5"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="5"/>
-      <c r="L23" s="5"/>
+      <c r="J23" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K23" s="17"/>
+      <c r="L23" s="18"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="8"/>
-      <c r="C24" s="5"/>
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
       <c r="F24" s="5"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
       <c r="I24" s="5"/>
-      <c r="L24" s="5"/>
+      <c r="J24" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="17"/>
+      <c r="L24" s="18"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="8"/>
-      <c r="C25" s="5"/>
+      <c r="B25" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="5"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="J25" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="17"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="8"/>
-      <c r="C26" s="5"/>
+      <c r="B26" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="5"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
       <c r="I26" s="5"/>
-      <c r="L26" s="5"/>
+      <c r="J26" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K26" s="17"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="8"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="5"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="5"/>
-      <c r="L27" s="5"/>
+      <c r="J27" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K27" s="17"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="8"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
       <c r="F28" s="5"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
       <c r="I28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="J28" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K28" s="17"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="8"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="5"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
       <c r="I29" s="5"/>
-      <c r="L29" s="5"/>
+      <c r="J29" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K29" s="17"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="8"/>
-      <c r="C30" s="5"/>
+      <c r="B30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
       <c r="F30" s="5"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
       <c r="I30" s="5"/>
-      <c r="L30" s="5"/>
+      <c r="J30" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K30" s="17"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="8"/>
-      <c r="C31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="L31" s="5"/>
+      <c r="B31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K31" s="17"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="8"/>
-      <c r="C32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="L32" s="5"/>
+      <c r="B32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K32" s="17"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="8"/>
-      <c r="C33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="L33" s="5"/>
+      <c r="B33" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K33" s="17"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="8"/>
-      <c r="C34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="L34" s="5"/>
+      <c r="B34" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35" s="8"/>
-      <c r="C35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="L35" s="5"/>
+      <c r="B35" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36" s="8"/>
-      <c r="C36" s="5"/>
+      <c r="B36" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
       <c r="F36" s="5"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
       <c r="I36" s="5"/>
-      <c r="L36" s="5"/>
+      <c r="J36" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K36" s="17"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37" s="8"/>
-      <c r="C37" s="5"/>
+      <c r="B37" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
       <c r="F37" s="5"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
       <c r="I37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="J37" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K37" s="17"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38" s="8"/>
-      <c r="C38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="L38" s="5"/>
+      <c r="B38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39" s="8"/>
-      <c r="C39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="L39" s="5"/>
+      <c r="B39" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" s="23" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B40" s="8"/>
-      <c r="C40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="L40" s="5"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B41" s="8"/>
-      <c r="C41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="L41" s="5"/>
+      <c r="B40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2893,10 +4804,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DECEB1-A674-4E9A-9A60-FE266B1759EE}">
-  <dimension ref="B1:O41"/>
+  <dimension ref="B1:O69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.7265625" customWidth="1"/>
+    <col min="2" max="2" width="77.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7265625" customWidth="1"/>
     <col min="4" max="4" width="16.26953125" customWidth="1"/>
     <col min="5" max="5" width="15.54296875" customWidth="1"/>
@@ -2938,7 +4850,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -2983,300 +4895,739 @@
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B5" s="8"/>
-      <c r="C5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="O5" s="5"/>
+      <c r="B5" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="15"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="O6" s="5"/>
+      <c r="B6" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="18"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="8"/>
-      <c r="C7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="O7" s="5"/>
+      <c r="B7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="18"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="8"/>
-      <c r="C8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="O8" s="5"/>
+      <c r="B8" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="18"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B9" s="8"/>
-      <c r="C9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="O9" s="5"/>
+      <c r="B9" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="18"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8"/>
-      <c r="C10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="O10" s="5"/>
+      <c r="B10" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="8"/>
-      <c r="C11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="B11" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="18"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="8"/>
-      <c r="C12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="O12" s="5"/>
+      <c r="B12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="18"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="8"/>
-      <c r="C13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="O13" s="5"/>
+      <c r="B13" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="18"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="8"/>
-      <c r="C14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="O14" s="5"/>
+      <c r="B14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="18"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="8"/>
-      <c r="C15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="O15" s="5"/>
+      <c r="B15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="18"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="8"/>
-      <c r="C16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="O16" s="5"/>
+      <c r="B16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="18"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="8"/>
-      <c r="C17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="O17" s="5"/>
+      <c r="B17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="30"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="18"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B18" s="8"/>
-      <c r="C18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="O18" s="5"/>
+      <c r="B18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="30"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8"/>
-      <c r="C19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="O19" s="5"/>
+      <c r="B19" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="18"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="8"/>
-      <c r="C20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="B20" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="30"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="18"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B21" s="8"/>
-      <c r="C21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="O21" s="5"/>
+      <c r="B21" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="30"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="18"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="8"/>
-      <c r="C22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="B22" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="18"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B23" s="8"/>
-      <c r="C23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="O23" s="5"/>
+      <c r="B23" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="30"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="18"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="8"/>
-      <c r="C24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="O24" s="5"/>
+      <c r="B24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="30"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="18"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="8"/>
-      <c r="C25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="O25" s="5"/>
+      <c r="B25" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="30"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="17"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="18"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="8"/>
-      <c r="C26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="O26" s="5"/>
+      <c r="B26" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="30"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="18"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B27" s="8"/>
-      <c r="C27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="O27" s="5"/>
+      <c r="B27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="30"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="K27" s="17"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="18"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8"/>
-      <c r="C28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="O28" s="5"/>
+      <c r="B28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="30"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="K28" s="17"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="18"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="8"/>
-      <c r="C29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="O29" s="5"/>
+      <c r="B29" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="30"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="K29" s="17"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="18"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B30" s="8"/>
-      <c r="C30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="O30" s="5"/>
+      <c r="B30" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="30"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="K30" s="17"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="18"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="8"/>
-      <c r="C31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="O31" s="5"/>
+      <c r="B31" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="30"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="N31" s="17"/>
+      <c r="O31" s="18"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B32" s="8"/>
-      <c r="C32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="O32" s="5"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="8"/>
-      <c r="C33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="O33" s="5"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="8"/>
-      <c r="C34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="O34" s="5"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="8"/>
-      <c r="C35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="O35" s="5"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B36" s="8"/>
-      <c r="C36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="O36" s="5"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8"/>
-      <c r="C37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="O37" s="5"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="8"/>
-      <c r="C38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="O38" s="5"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B39" s="8"/>
-      <c r="C39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="O39" s="5"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="8"/>
-      <c r="C40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="O40" s="5"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="8"/>
-      <c r="C41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="O41" s="5"/>
+      <c r="B32" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="N32" s="17"/>
+      <c r="O32" s="18"/>
+    </row>
+    <row r="33" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="31"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="N33" s="21"/>
+      <c r="O33" s="22"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B60" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" t="s">
+        <v>89</v>
+      </c>
+      <c r="L60" s="5"/>
+      <c r="O60" s="5"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B61" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" t="s">
+        <v>89</v>
+      </c>
+      <c r="L61" s="5"/>
+      <c r="O61" s="5"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B63" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" t="s">
+        <v>89</v>
+      </c>
+      <c r="L63" s="5"/>
+      <c r="O63" s="5"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B64" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" t="s">
+        <v>89</v>
+      </c>
+      <c r="O64" s="5"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B67" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="J67" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="M68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B69" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" t="s">
+        <v>89</v>
+      </c>
+      <c r="O69" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\_Projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F7176B-92F4-4BA7-B806-AACEA65B28BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C408D2F2-66B1-46D2-99B1-41876276B4C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
@@ -37,10 +37,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -943,9 +943,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -983,7 +983,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1089,7 +1089,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1231,7 +1231,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2901,6 +2901,10 @@
     <col min="10" max="10" width="9.54296875" customWidth="1"/>
     <col min="11" max="11" width="16.1796875" customWidth="1"/>
     <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\_Projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C408D2F2-66B1-46D2-99B1-41876276B4C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3FC9E3-4596-44C7-BC50-AEB209581C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
@@ -37,10 +37,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -842,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -903,8 +903,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -914,17 +912,8 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -943,9 +932,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -983,7 +972,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1089,7 +1078,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1231,7 +1220,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1258,10 +1247,9 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B3" s="46" t="s">
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="46"/>
     </row>
     <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B5" s="2" t="s">
@@ -1727,10 +1715,10 @@
     </row>
     <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D39" s="48" t="s">
+      <c r="D39" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="49">
+      <c r="E39" s="47">
         <f>SUM(E6:E37)</f>
         <v>101.5</v>
       </c>
@@ -1773,11 +1761,9 @@
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="46" t="s">
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
     </row>
     <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
@@ -3176,7 +3162,7 @@
       <c r="R10" s="32"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="26" t="s">
         <v>102</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -3199,11 +3185,13 @@
       <c r="N11" s="20">
         <v>0.9</v>
       </c>
-      <c r="P11" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="32"/>
+      <c r="P11" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="27">
+        <v>1</v>
+      </c>
+      <c r="R11" s="28"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
@@ -3230,12 +3218,11 @@
         <v>1</v>
       </c>
       <c r="O12" s="29"/>
-      <c r="P12" s="57"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="59"/>
+      <c r="P12" s="35"/>
+      <c r="R12" s="14"/>
     </row>
     <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="52" t="s">
         <v>101</v>
       </c>
       <c r="C13" s="17" t="s">
@@ -3250,16 +3237,16 @@
       <c r="J13" s="36"/>
       <c r="K13" s="16"/>
       <c r="L13" s="17"/>
-      <c r="M13" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="N13" s="51">
+      <c r="M13" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="N13" s="49">
         <v>1</v>
       </c>
-      <c r="O13" s="52"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="55"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="17"/>
     </row>
     <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
@@ -3375,442 +3362,306 @@
       <c r="B6" s="18"/>
       <c r="C6" s="41"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="46"/>
       <c r="F6" s="14"/>
       <c r="G6" s="18"/>
-      <c r="H6" s="46"/>
       <c r="I6" s="14"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="18"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="46"/>
       <c r="F7" s="14"/>
       <c r="G7" s="18"/>
-      <c r="H7" s="46"/>
       <c r="I7" s="14"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="18"/>
       <c r="C8" s="41"/>
       <c r="D8" s="18"/>
-      <c r="E8" s="46"/>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
-      <c r="H8" s="46"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="18"/>
       <c r="C9" s="41"/>
       <c r="D9" s="18"/>
-      <c r="E9" s="46"/>
       <c r="F9" s="14"/>
       <c r="G9" s="18"/>
-      <c r="H9" s="46"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="18"/>
       <c r="C10" s="41"/>
       <c r="D10" s="18"/>
-      <c r="E10" s="46"/>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
-      <c r="H10" s="46"/>
       <c r="I10" s="14"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="18"/>
       <c r="C11" s="41"/>
       <c r="D11" s="18"/>
-      <c r="E11" s="46"/>
       <c r="F11" s="14"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="46"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="18"/>
       <c r="C12" s="41"/>
       <c r="D12" s="18"/>
-      <c r="E12" s="46"/>
       <c r="F12" s="14"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="46"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="18"/>
       <c r="C13" s="41"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="46"/>
       <c r="F13" s="14"/>
       <c r="G13" s="18"/>
-      <c r="H13" s="46"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="18"/>
       <c r="C14" s="41"/>
       <c r="D14" s="18"/>
-      <c r="E14" s="46"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="46"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="18"/>
       <c r="C15" s="41"/>
       <c r="D15" s="18"/>
-      <c r="E15" s="46"/>
       <c r="F15" s="14"/>
       <c r="G15" s="18"/>
-      <c r="H15" s="46"/>
       <c r="I15" s="14"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="18"/>
       <c r="C16" s="41"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="46"/>
       <c r="F16" s="14"/>
       <c r="G16" s="18"/>
-      <c r="H16" s="46"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="18"/>
       <c r="C17" s="41"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="46"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="46"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="18"/>
       <c r="C18" s="41"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="46"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="46"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="18"/>
       <c r="C19" s="41"/>
       <c r="D19" s="18"/>
-      <c r="E19" s="46"/>
       <c r="F19" s="14"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="46"/>
       <c r="I19" s="14"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="18"/>
       <c r="C20" s="41"/>
       <c r="D20" s="18"/>
-      <c r="E20" s="46"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="46"/>
       <c r="I20" s="14"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="18"/>
       <c r="C21" s="41"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="46"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
       <c r="I21" s="14"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="18"/>
       <c r="C22" s="41"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="46"/>
       <c r="F22" s="14"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="18"/>
       <c r="C23" s="41"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="46"/>
       <c r="F23" s="14"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="46"/>
       <c r="I23" s="14"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="18"/>
       <c r="C24" s="41"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="46"/>
       <c r="F24" s="14"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="46"/>
       <c r="I24" s="14"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="18"/>
       <c r="C25" s="41"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="46"/>
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="46"/>
       <c r="I25" s="14"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="18"/>
       <c r="C26" s="41"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="46"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="46"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="18"/>
       <c r="C27" s="41"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="46"/>
       <c r="F27" s="14"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="46"/>
       <c r="I27" s="14"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="18"/>
       <c r="C28" s="41"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="46"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="46"/>
       <c r="I28" s="14"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="18"/>
       <c r="C29" s="41"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="46"/>
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="46"/>
       <c r="I29" s="14"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="18"/>
       <c r="C30" s="41"/>
       <c r="D30" s="18"/>
-      <c r="E30" s="46"/>
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="46"/>
       <c r="I30" s="14"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="18"/>
       <c r="C31" s="41"/>
       <c r="D31" s="18"/>
-      <c r="E31" s="46"/>
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="46"/>
       <c r="I31" s="14"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="18"/>
       <c r="C32" s="41"/>
       <c r="D32" s="18"/>
-      <c r="E32" s="46"/>
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="46"/>
       <c r="I32" s="14"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="18"/>
       <c r="C33" s="41"/>
       <c r="D33" s="18"/>
-      <c r="E33" s="46"/>
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
-      <c r="H33" s="46"/>
       <c r="I33" s="14"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="18"/>
       <c r="C34" s="41"/>
       <c r="D34" s="18"/>
-      <c r="E34" s="46"/>
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
-      <c r="H34" s="46"/>
       <c r="I34" s="14"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="18"/>
       <c r="C35" s="41"/>
       <c r="D35" s="18"/>
-      <c r="E35" s="46"/>
       <c r="F35" s="14"/>
       <c r="G35" s="18"/>
-      <c r="H35" s="46"/>
       <c r="I35" s="14"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="18"/>
       <c r="C36" s="41"/>
       <c r="D36" s="18"/>
-      <c r="E36" s="46"/>
       <c r="F36" s="14"/>
       <c r="G36" s="18"/>
-      <c r="H36" s="46"/>
       <c r="I36" s="14"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="18"/>
       <c r="C37" s="41"/>
       <c r="D37" s="18"/>
-      <c r="E37" s="46"/>
       <c r="F37" s="14"/>
       <c r="G37" s="18"/>
-      <c r="H37" s="46"/>
       <c r="I37" s="14"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="18"/>
       <c r="C38" s="41"/>
       <c r="D38" s="18"/>
-      <c r="E38" s="46"/>
       <c r="F38" s="14"/>
       <c r="G38" s="18"/>
-      <c r="H38" s="46"/>
       <c r="I38" s="14"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="18"/>
       <c r="C39" s="41"/>
       <c r="D39" s="18"/>
-      <c r="E39" s="46"/>
       <c r="F39" s="14"/>
       <c r="G39" s="18"/>
-      <c r="H39" s="46"/>
       <c r="I39" s="14"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3934,13 +3785,9 @@
       <c r="D8" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="46"/>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
-      <c r="H8" s="46"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
@@ -3953,13 +3800,9 @@
       <c r="D9" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="46"/>
       <c r="F9" s="14"/>
       <c r="G9" s="18"/>
-      <c r="H9" s="46"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
@@ -3972,13 +3815,9 @@
       <c r="D10" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="46"/>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
-      <c r="H10" s="46"/>
       <c r="I10" s="14"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
@@ -3991,13 +3830,9 @@
       <c r="D11" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="46"/>
       <c r="F11" s="14"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="46"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
@@ -4008,15 +3843,11 @@
         <v>107</v>
       </c>
       <c r="D12" s="18"/>
-      <c r="E12" s="46"/>
       <c r="F12" s="14"/>
       <c r="G12" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="46"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
@@ -4027,15 +3858,11 @@
         <v>107</v>
       </c>
       <c r="D13" s="18"/>
-      <c r="E13" s="46"/>
       <c r="F13" s="14"/>
       <c r="G13" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H13" s="46"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
@@ -4046,15 +3873,11 @@
         <v>107</v>
       </c>
       <c r="D14" s="18"/>
-      <c r="E14" s="46"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="46"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
@@ -4065,15 +3888,11 @@
         <v>107</v>
       </c>
       <c r="D15" s="18"/>
-      <c r="E15" s="46"/>
       <c r="F15" s="14"/>
       <c r="G15" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="46"/>
       <c r="I15" s="14"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
@@ -4084,15 +3903,11 @@
         <v>107</v>
       </c>
       <c r="D16" s="18"/>
-      <c r="E16" s="46"/>
       <c r="F16" s="14"/>
       <c r="G16" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="46"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
@@ -4103,15 +3918,11 @@
         <v>108</v>
       </c>
       <c r="D17" s="18"/>
-      <c r="E17" s="46"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="46"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
@@ -4122,15 +3933,11 @@
         <v>108</v>
       </c>
       <c r="D18" s="18"/>
-      <c r="E18" s="46"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H18" s="46"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
@@ -4141,15 +3948,11 @@
         <v>108</v>
       </c>
       <c r="D19" s="18"/>
-      <c r="E19" s="46"/>
       <c r="F19" s="14"/>
       <c r="G19" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H19" s="46"/>
       <c r="I19" s="14"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
@@ -4160,15 +3963,11 @@
         <v>108</v>
       </c>
       <c r="D20" s="18"/>
-      <c r="E20" s="46"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="46"/>
       <c r="I20" s="14"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
@@ -4179,15 +3978,12 @@
         <v>108</v>
       </c>
       <c r="D21" s="18"/>
-      <c r="E21" s="46"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
       <c r="I21" s="14"/>
-      <c r="J21" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K21" s="46"/>
+      <c r="J21" t="s">
+        <v>89</v>
+      </c>
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
@@ -4198,15 +3994,12 @@
         <v>108</v>
       </c>
       <c r="D22" s="18"/>
-      <c r="E22" s="46"/>
       <c r="F22" s="14"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K22" s="46"/>
+      <c r="J22" t="s">
+        <v>89</v>
+      </c>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
@@ -4217,15 +4010,12 @@
         <v>108</v>
       </c>
       <c r="D23" s="18"/>
-      <c r="E23" s="46"/>
       <c r="F23" s="14"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="46"/>
       <c r="I23" s="14"/>
-      <c r="J23" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K23" s="46"/>
+      <c r="J23" t="s">
+        <v>89</v>
+      </c>
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
@@ -4236,15 +4026,12 @@
         <v>108</v>
       </c>
       <c r="D24" s="18"/>
-      <c r="E24" s="46"/>
       <c r="F24" s="14"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="46"/>
       <c r="I24" s="14"/>
-      <c r="J24" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="K24" s="46"/>
+      <c r="J24" t="s">
+        <v>89</v>
+      </c>
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
@@ -4255,15 +4042,12 @@
         <v>108</v>
       </c>
       <c r="D25" s="18"/>
-      <c r="E25" s="46"/>
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="46"/>
       <c r="I25" s="14"/>
-      <c r="J25" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="K25" s="46"/>
+      <c r="J25" t="s">
+        <v>89</v>
+      </c>
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
@@ -4274,15 +4058,12 @@
         <v>107</v>
       </c>
       <c r="D26" s="18"/>
-      <c r="E26" s="46"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="46"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="K26" s="46"/>
+      <c r="J26" t="s">
+        <v>89</v>
+      </c>
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
@@ -4293,15 +4074,12 @@
         <v>107</v>
       </c>
       <c r="D27" s="18"/>
-      <c r="E27" s="46"/>
       <c r="F27" s="14"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="46"/>
       <c r="I27" s="14"/>
-      <c r="J27" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K27" s="46"/>
+      <c r="J27" t="s">
+        <v>89</v>
+      </c>
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
@@ -4312,15 +4090,12 @@
         <v>107</v>
       </c>
       <c r="D28" s="18"/>
-      <c r="E28" s="46"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="46"/>
       <c r="I28" s="14"/>
-      <c r="J28" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K28" s="46"/>
+      <c r="J28" t="s">
+        <v>89</v>
+      </c>
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
@@ -4331,15 +4106,12 @@
         <v>107</v>
       </c>
       <c r="D29" s="18"/>
-      <c r="E29" s="46"/>
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="46"/>
       <c r="I29" s="14"/>
-      <c r="J29" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K29" s="46"/>
+      <c r="J29" t="s">
+        <v>89</v>
+      </c>
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
@@ -4350,15 +4122,12 @@
         <v>107</v>
       </c>
       <c r="D30" s="18"/>
-      <c r="E30" s="46"/>
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="46"/>
       <c r="I30" s="14"/>
-      <c r="J30" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K30" s="46"/>
+      <c r="J30" t="s">
+        <v>89</v>
+      </c>
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
@@ -4369,15 +4138,12 @@
         <v>107</v>
       </c>
       <c r="D31" s="18"/>
-      <c r="E31" s="46"/>
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="46"/>
       <c r="I31" s="14"/>
-      <c r="J31" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K31" s="46"/>
+      <c r="J31" t="s">
+        <v>89</v>
+      </c>
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
@@ -4388,15 +4154,12 @@
         <v>107</v>
       </c>
       <c r="D32" s="18"/>
-      <c r="E32" s="46"/>
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="46"/>
       <c r="I32" s="14"/>
-      <c r="J32" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K32" s="46"/>
+      <c r="J32" t="s">
+        <v>89</v>
+      </c>
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
@@ -4407,15 +4170,12 @@
         <v>107</v>
       </c>
       <c r="D33" s="18"/>
-      <c r="E33" s="46"/>
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
-      <c r="H33" s="46"/>
       <c r="I33" s="14"/>
-      <c r="J33" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K33" s="46"/>
+      <c r="J33" t="s">
+        <v>89</v>
+      </c>
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
@@ -4426,15 +4186,12 @@
         <v>107</v>
       </c>
       <c r="D34" s="18"/>
-      <c r="E34" s="46"/>
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
-      <c r="H34" s="46"/>
       <c r="I34" s="14"/>
-      <c r="J34" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="K34" s="46"/>
+      <c r="J34" t="s">
+        <v>89</v>
+      </c>
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4746,442 +4503,306 @@
       <c r="B6" s="18"/>
       <c r="C6" s="41"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="46"/>
       <c r="F6" s="14"/>
       <c r="G6" s="18"/>
-      <c r="H6" s="46"/>
       <c r="I6" s="14"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="18"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="46"/>
       <c r="F7" s="14"/>
       <c r="G7" s="18"/>
-      <c r="H7" s="46"/>
       <c r="I7" s="14"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="18"/>
       <c r="C8" s="41"/>
       <c r="D8" s="18"/>
-      <c r="E8" s="46"/>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
-      <c r="H8" s="46"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="18"/>
       <c r="C9" s="41"/>
       <c r="D9" s="18"/>
-      <c r="E9" s="46"/>
       <c r="F9" s="14"/>
       <c r="G9" s="18"/>
-      <c r="H9" s="46"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="18"/>
       <c r="C10" s="41"/>
       <c r="D10" s="18"/>
-      <c r="E10" s="46"/>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
-      <c r="H10" s="46"/>
       <c r="I10" s="14"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="18"/>
       <c r="C11" s="41"/>
       <c r="D11" s="18"/>
-      <c r="E11" s="46"/>
       <c r="F11" s="14"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="46"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="18"/>
       <c r="C12" s="41"/>
       <c r="D12" s="18"/>
-      <c r="E12" s="46"/>
       <c r="F12" s="14"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="46"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="18"/>
       <c r="C13" s="41"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="46"/>
       <c r="F13" s="14"/>
       <c r="G13" s="18"/>
-      <c r="H13" s="46"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="18"/>
       <c r="C14" s="41"/>
       <c r="D14" s="18"/>
-      <c r="E14" s="46"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="46"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="18"/>
       <c r="C15" s="41"/>
       <c r="D15" s="18"/>
-      <c r="E15" s="46"/>
       <c r="F15" s="14"/>
       <c r="G15" s="18"/>
-      <c r="H15" s="46"/>
       <c r="I15" s="14"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="18"/>
       <c r="C16" s="41"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="46"/>
       <c r="F16" s="14"/>
       <c r="G16" s="18"/>
-      <c r="H16" s="46"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="18"/>
       <c r="C17" s="41"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="46"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="46"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="18"/>
       <c r="C18" s="41"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="46"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="46"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="18"/>
       <c r="C19" s="41"/>
       <c r="D19" s="18"/>
-      <c r="E19" s="46"/>
       <c r="F19" s="14"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="46"/>
       <c r="I19" s="14"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="18"/>
       <c r="C20" s="41"/>
       <c r="D20" s="18"/>
-      <c r="E20" s="46"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="46"/>
       <c r="I20" s="14"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="18"/>
       <c r="C21" s="41"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="46"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
       <c r="I21" s="14"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="18"/>
       <c r="C22" s="41"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="46"/>
       <c r="F22" s="14"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="18"/>
       <c r="C23" s="41"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="46"/>
       <c r="F23" s="14"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="46"/>
       <c r="I23" s="14"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="18"/>
       <c r="C24" s="41"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="46"/>
       <c r="F24" s="14"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="46"/>
       <c r="I24" s="14"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="18"/>
       <c r="C25" s="41"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="46"/>
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="46"/>
       <c r="I25" s="14"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="18"/>
       <c r="C26" s="41"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="46"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="46"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="18"/>
       <c r="C27" s="41"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="46"/>
       <c r="F27" s="14"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="46"/>
       <c r="I27" s="14"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="18"/>
       <c r="C28" s="41"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="46"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="46"/>
       <c r="I28" s="14"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="18"/>
       <c r="C29" s="41"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="46"/>
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="46"/>
       <c r="I29" s="14"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="18"/>
       <c r="C30" s="41"/>
       <c r="D30" s="18"/>
-      <c r="E30" s="46"/>
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="46"/>
       <c r="I30" s="14"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="18"/>
       <c r="C31" s="41"/>
       <c r="D31" s="18"/>
-      <c r="E31" s="46"/>
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="46"/>
       <c r="I31" s="14"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="18"/>
       <c r="C32" s="41"/>
       <c r="D32" s="18"/>
-      <c r="E32" s="46"/>
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="46"/>
       <c r="I32" s="14"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="18"/>
       <c r="C33" s="41"/>
       <c r="D33" s="18"/>
-      <c r="E33" s="46"/>
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
-      <c r="H33" s="46"/>
       <c r="I33" s="14"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="18"/>
       <c r="C34" s="41"/>
       <c r="D34" s="18"/>
-      <c r="E34" s="46"/>
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
-      <c r="H34" s="46"/>
       <c r="I34" s="14"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="18"/>
       <c r="C35" s="41"/>
       <c r="D35" s="18"/>
-      <c r="E35" s="46"/>
       <c r="F35" s="14"/>
       <c r="G35" s="18"/>
-      <c r="H35" s="46"/>
       <c r="I35" s="14"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="18"/>
       <c r="C36" s="41"/>
       <c r="D36" s="18"/>
-      <c r="E36" s="46"/>
       <c r="F36" s="14"/>
       <c r="G36" s="18"/>
-      <c r="H36" s="46"/>
       <c r="I36" s="14"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="18"/>
       <c r="C37" s="41"/>
       <c r="D37" s="18"/>
-      <c r="E37" s="46"/>
       <c r="F37" s="14"/>
       <c r="G37" s="18"/>
-      <c r="H37" s="46"/>
       <c r="I37" s="14"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="18"/>
       <c r="C38" s="41"/>
       <c r="D38" s="18"/>
-      <c r="E38" s="46"/>
       <c r="F38" s="14"/>
       <c r="G38" s="18"/>
-      <c r="H38" s="46"/>
       <c r="I38" s="14"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="18"/>
       <c r="C39" s="41"/>
       <c r="D39" s="18"/>
-      <c r="E39" s="46"/>
       <c r="F39" s="14"/>
       <c r="G39" s="18"/>
-      <c r="H39" s="46"/>
       <c r="I39" s="14"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6047,442 +5668,306 @@
       <c r="B7" s="18"/>
       <c r="C7" s="41"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="46"/>
       <c r="F7" s="14"/>
       <c r="G7" s="18"/>
-      <c r="H7" s="46"/>
       <c r="I7" s="14"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="18"/>
       <c r="C8" s="41"/>
       <c r="D8" s="18"/>
-      <c r="E8" s="46"/>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
-      <c r="H8" s="46"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="18"/>
       <c r="C9" s="41"/>
       <c r="D9" s="18"/>
-      <c r="E9" s="46"/>
       <c r="F9" s="14"/>
       <c r="G9" s="18"/>
-      <c r="H9" s="46"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="18"/>
       <c r="C10" s="41"/>
       <c r="D10" s="18"/>
-      <c r="E10" s="46"/>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
-      <c r="H10" s="46"/>
       <c r="I10" s="14"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="18"/>
       <c r="C11" s="41"/>
       <c r="D11" s="18"/>
-      <c r="E11" s="46"/>
       <c r="F11" s="14"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="46"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="18"/>
       <c r="C12" s="41"/>
       <c r="D12" s="18"/>
-      <c r="E12" s="46"/>
       <c r="F12" s="14"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="46"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="18"/>
       <c r="C13" s="41"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="46"/>
       <c r="F13" s="14"/>
       <c r="G13" s="18"/>
-      <c r="H13" s="46"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="18"/>
       <c r="C14" s="41"/>
       <c r="D14" s="18"/>
-      <c r="E14" s="46"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="46"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="18"/>
       <c r="C15" s="41"/>
       <c r="D15" s="18"/>
-      <c r="E15" s="46"/>
       <c r="F15" s="14"/>
       <c r="G15" s="18"/>
-      <c r="H15" s="46"/>
       <c r="I15" s="14"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="18"/>
       <c r="C16" s="41"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="46"/>
       <c r="F16" s="14"/>
       <c r="G16" s="18"/>
-      <c r="H16" s="46"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="18"/>
       <c r="C17" s="41"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="46"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="46"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="18"/>
       <c r="C18" s="41"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="46"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="46"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="18"/>
       <c r="C19" s="41"/>
       <c r="D19" s="18"/>
-      <c r="E19" s="46"/>
       <c r="F19" s="14"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="46"/>
       <c r="I19" s="14"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="18"/>
       <c r="C20" s="41"/>
       <c r="D20" s="18"/>
-      <c r="E20" s="46"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="46"/>
       <c r="I20" s="14"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="18"/>
       <c r="C21" s="41"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="46"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
       <c r="I21" s="14"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="18"/>
       <c r="C22" s="41"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="46"/>
       <c r="F22" s="14"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="18"/>
       <c r="C23" s="41"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="46"/>
       <c r="F23" s="14"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="46"/>
       <c r="I23" s="14"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="18"/>
       <c r="C24" s="41"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="46"/>
       <c r="F24" s="14"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="46"/>
       <c r="I24" s="14"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="18"/>
       <c r="C25" s="41"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="46"/>
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="46"/>
       <c r="I25" s="14"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="18"/>
       <c r="C26" s="41"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="46"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="46"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="18"/>
       <c r="C27" s="41"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="46"/>
       <c r="F27" s="14"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="46"/>
       <c r="I27" s="14"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="18"/>
       <c r="C28" s="41"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="46"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="46"/>
       <c r="I28" s="14"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="18"/>
       <c r="C29" s="41"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="46"/>
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="46"/>
       <c r="I29" s="14"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="18"/>
       <c r="C30" s="41"/>
       <c r="D30" s="18"/>
-      <c r="E30" s="46"/>
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="46"/>
       <c r="I30" s="14"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="18"/>
       <c r="C31" s="41"/>
       <c r="D31" s="18"/>
-      <c r="E31" s="46"/>
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="46"/>
       <c r="I31" s="14"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="18"/>
       <c r="C32" s="41"/>
       <c r="D32" s="18"/>
-      <c r="E32" s="46"/>
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="46"/>
       <c r="I32" s="14"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="18"/>
       <c r="C33" s="41"/>
       <c r="D33" s="18"/>
-      <c r="E33" s="46"/>
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
-      <c r="H33" s="46"/>
       <c r="I33" s="14"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="18"/>
       <c r="C34" s="41"/>
       <c r="D34" s="18"/>
-      <c r="E34" s="46"/>
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
-      <c r="H34" s="46"/>
       <c r="I34" s="14"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="18"/>
       <c r="C35" s="41"/>
       <c r="D35" s="18"/>
-      <c r="E35" s="46"/>
       <c r="F35" s="14"/>
       <c r="G35" s="18"/>
-      <c r="H35" s="46"/>
       <c r="I35" s="14"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="18"/>
       <c r="C36" s="41"/>
       <c r="D36" s="18"/>
-      <c r="E36" s="46"/>
       <c r="F36" s="14"/>
       <c r="G36" s="18"/>
-      <c r="H36" s="46"/>
       <c r="I36" s="14"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="18"/>
       <c r="C37" s="41"/>
       <c r="D37" s="18"/>
-      <c r="E37" s="46"/>
       <c r="F37" s="14"/>
       <c r="G37" s="18"/>
-      <c r="H37" s="46"/>
       <c r="I37" s="14"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="18"/>
       <c r="C38" s="41"/>
       <c r="D38" s="18"/>
-      <c r="E38" s="46"/>
       <c r="F38" s="14"/>
       <c r="G38" s="18"/>
-      <c r="H38" s="46"/>
       <c r="I38" s="14"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="18"/>
       <c r="C39" s="41"/>
       <c r="D39" s="18"/>
-      <c r="E39" s="46"/>
       <c r="F39" s="14"/>
       <c r="G39" s="18"/>
-      <c r="H39" s="46"/>
       <c r="I39" s="14"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B40" s="18"/>
       <c r="C40" s="41"/>
       <c r="D40" s="18"/>
-      <c r="E40" s="46"/>
       <c r="F40" s="14"/>
       <c r="G40" s="18"/>
-      <c r="H40" s="46"/>
       <c r="I40" s="14"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
       <c r="L40" s="14"/>
     </row>
     <row r="41" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3FC9E3-4596-44C7-BC50-AEB209581C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3F533C-39A6-4B68-A629-9F0BD55DE36C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -32,23 +32,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="159">
   <si>
     <t>Planification globale</t>
   </si>
@@ -326,9 +315,6 @@
     <t>Implémentation de la logique de déplacement des pièces</t>
   </si>
   <si>
-    <t>Vérification du placement initial des pièces</t>
-  </si>
-  <si>
     <t>Implémentation des règles du jeu (sans combat)</t>
   </si>
   <si>
@@ -420,9 +406,6 @@
   </si>
   <si>
     <t>Communication entre le Serveur et le Client (envois/réceptions)</t>
-  </si>
-  <si>
-    <t>Implémentation de l'AI</t>
   </si>
   <si>
     <t>Mise en place de l’infrastructure serveur et base de données</t>
@@ -573,7 +556,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,14 +575,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -838,11 +815,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -873,10 +895,6 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -890,9 +908,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
@@ -914,11 +929,109 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -932,9 +1045,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -972,7 +1085,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1078,7 +1191,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1220,7 +1333,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1267,13 +1380,13 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="40" t="s">
-        <v>156</v>
+      <c r="D6" s="35" t="s">
+        <v>154</v>
       </c>
       <c r="E6" s="12">
         <v>10</v>
@@ -1281,13 +1394,13 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="41" t="s">
-        <v>156</v>
+      <c r="D7" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E7" s="14">
         <v>4</v>
@@ -1295,13 +1408,13 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="41" t="s">
-        <v>156</v>
+      <c r="D8" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E8" s="14">
         <v>4</v>
@@ -1309,13 +1422,13 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="41" t="s">
-        <v>156</v>
+      <c r="D9" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E9" s="14">
         <v>2</v>
@@ -1323,13 +1436,13 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="41" t="s">
-        <v>156</v>
+      <c r="D10" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E10" s="14">
         <v>1</v>
@@ -1337,13 +1450,13 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="41" t="s">
-        <v>156</v>
+      <c r="D11" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
@@ -1351,13 +1464,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="41" t="s">
-        <v>156</v>
+      <c r="D12" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E12" s="14">
         <v>3</v>
@@ -1365,13 +1478,13 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="41" t="s">
-        <v>156</v>
+      <c r="D13" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E13" s="14">
         <v>3</v>
@@ -1379,13 +1492,13 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="41" t="s">
-        <v>156</v>
+      <c r="D14" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E14" s="14">
         <v>2</v>
@@ -1393,13 +1506,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="41" t="s">
-        <v>156</v>
+      <c r="D15" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E15" s="14">
         <v>4</v>
@@ -1407,13 +1520,13 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="41" t="s">
-        <v>156</v>
+      <c r="D16" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E16" s="14">
         <v>1</v>
@@ -1421,13 +1534,13 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="41" t="s">
-        <v>156</v>
+      <c r="D17" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E17" s="14">
         <v>2</v>
@@ -1435,13 +1548,13 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="41" t="s">
-        <v>156</v>
+      <c r="D18" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E18" s="14">
         <v>1.5</v>
@@ -1449,13 +1562,13 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C19" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="41" t="s">
-        <v>156</v>
+      <c r="D19" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E19" s="14">
         <v>3</v>
@@ -1463,13 +1576,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="41" t="s">
-        <v>158</v>
+      <c r="D20" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E20" s="14">
         <v>4</v>
@@ -1477,13 +1590,13 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="41" t="s">
-        <v>156</v>
+      <c r="D21" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E21" s="14">
         <v>3</v>
@@ -1491,13 +1604,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="41" t="s">
-        <v>156</v>
+      <c r="D22" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E22" s="14">
         <v>2</v>
@@ -1505,13 +1618,13 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C23" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="41" t="s">
-        <v>156</v>
+      <c r="D23" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E23" s="14">
         <v>4</v>
@@ -1519,13 +1632,13 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="41" t="s">
-        <v>158</v>
+      <c r="D24" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E24" s="14">
         <v>1.5</v>
@@ -1533,13 +1646,13 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C25" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="41" t="s">
-        <v>156</v>
+      <c r="D25" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E25" s="14">
         <v>5</v>
@@ -1547,13 +1660,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C26" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="41" t="s">
-        <v>158</v>
+      <c r="D26" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E26" s="14">
         <v>3</v>
@@ -1561,13 +1674,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C27" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="41" t="s">
-        <v>156</v>
+      <c r="D27" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E27" s="14">
         <v>7</v>
@@ -1575,13 +1688,13 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="41" t="s">
-        <v>157</v>
+      <c r="D28" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="E28" s="14">
         <v>1</v>
@@ -1589,13 +1702,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C29" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="41" t="s">
-        <v>158</v>
+      <c r="D29" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E29" s="14">
         <v>3.5</v>
@@ -1603,13 +1716,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="41" t="s">
-        <v>158</v>
+      <c r="D30" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E30" s="14">
         <v>4</v>
@@ -1617,13 +1730,13 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C31" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="41" t="s">
-        <v>157</v>
+      <c r="D31" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="E31" s="14">
         <v>3</v>
@@ -1631,13 +1744,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="41" t="s">
-        <v>158</v>
+      <c r="D32" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E32" s="14">
         <v>2</v>
@@ -1645,13 +1758,13 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="41" t="s">
-        <v>156</v>
+      <c r="D33" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="E33" s="14">
         <v>4</v>
@@ -1659,13 +1772,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C34" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="41" t="s">
-        <v>157</v>
+      <c r="D34" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="E34" s="14">
         <v>4</v>
@@ -1673,13 +1786,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="41" t="s">
-        <v>157</v>
+      <c r="D35" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="E35" s="14">
         <v>4</v>
@@ -1687,13 +1800,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C36" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D36" s="41" t="s">
-        <v>157</v>
+      <c r="D36" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="E36" s="14">
         <v>3</v>
@@ -1701,13 +1814,13 @@
     </row>
     <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C37" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="42" t="s">
-        <v>157</v>
+      <c r="D37" s="37" t="s">
+        <v>155</v>
       </c>
       <c r="E37" s="17">
         <v>2</v>
@@ -1715,10 +1828,10 @@
     </row>
     <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D39" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39" s="47">
+      <c r="D39" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="E39" s="42">
         <f>SUM(E6:E37)</f>
         <v>101.5</v>
       </c>
@@ -2551,7 +2664,7 @@
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
@@ -2562,7 +2675,7 @@
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
@@ -2573,7 +2686,7 @@
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
@@ -2584,7 +2697,7 @@
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
@@ -2595,7 +2708,7 @@
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
@@ -2606,7 +2719,7 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
@@ -2617,7 +2730,7 @@
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
@@ -2628,7 +2741,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
@@ -2639,7 +2752,7 @@
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
@@ -2650,7 +2763,7 @@
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
@@ -2661,7 +2774,7 @@
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
@@ -2923,7 +3036,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
@@ -2984,208 +3097,212 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="30" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="24">
         <v>1</v>
       </c>
       <c r="F5" s="25"/>
-      <c r="G5" s="37"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="19"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="37"/>
+      <c r="J5" s="33"/>
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="37"/>
+      <c r="M5" s="33"/>
       <c r="N5" s="11"/>
       <c r="O5" s="11"/>
-      <c r="P5" s="37"/>
+      <c r="P5" s="33"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="35"/>
+        <v>108</v>
+      </c>
+      <c r="D6" s="31"/>
       <c r="F6" s="14"/>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="34" t="s">
         <v>89</v>
       </c>
       <c r="H6" s="27">
         <v>1</v>
       </c>
       <c r="I6" s="28"/>
-      <c r="J6" s="35"/>
+      <c r="J6" s="31"/>
       <c r="L6" s="14"/>
-      <c r="M6" s="35"/>
-      <c r="P6" s="35"/>
+      <c r="M6" s="31"/>
+      <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="35"/>
+        <v>108</v>
+      </c>
+      <c r="D7" s="31"/>
       <c r="F7" s="14"/>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="31" t="s">
         <v>89</v>
       </c>
       <c r="H7" s="20">
         <v>0.6</v>
       </c>
       <c r="I7" s="14"/>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="34" t="s">
         <v>89</v>
       </c>
       <c r="K7" s="27">
         <v>1</v>
       </c>
       <c r="L7" s="28"/>
-      <c r="M7" s="35"/>
-      <c r="P7" s="35"/>
+      <c r="M7" s="31"/>
+      <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="35"/>
+        <v>106</v>
+      </c>
+      <c r="D8" s="31"/>
       <c r="F8" s="14"/>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="31" t="s">
         <v>89</v>
       </c>
       <c r="H8" s="20">
         <v>0.6</v>
       </c>
       <c r="I8" s="14"/>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="31" t="s">
         <v>89</v>
       </c>
       <c r="K8" s="20">
         <v>0.9</v>
       </c>
       <c r="L8" s="14"/>
-      <c r="M8" s="38" t="s">
+      <c r="M8" s="34" t="s">
         <v>89</v>
       </c>
       <c r="N8" s="27">
         <v>1</v>
       </c>
       <c r="O8" s="29"/>
-      <c r="P8" s="35"/>
+      <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B9" s="30" t="s">
-        <v>100</v>
+      <c r="B9" s="26" t="s">
+        <v>99</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="35"/>
+        <v>108</v>
+      </c>
+      <c r="D9" s="31"/>
       <c r="F9" s="14"/>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="31" t="s">
         <v>89</v>
       </c>
       <c r="H9" s="20">
         <v>0.3</v>
       </c>
       <c r="I9" s="14"/>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="31" t="s">
         <v>89</v>
       </c>
       <c r="K9" s="20">
         <v>0.7</v>
       </c>
       <c r="L9" s="14"/>
-      <c r="M9" s="35" t="s">
+      <c r="M9" s="31" t="s">
         <v>89</v>
       </c>
       <c r="N9" s="20">
         <v>0.9</v>
       </c>
-      <c r="P9" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="32"/>
+      <c r="P9" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="27">
+        <v>1</v>
+      </c>
+      <c r="R9" s="28"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B10" s="30" t="s">
-        <v>104</v>
+      <c r="B10" s="26" t="s">
+        <v>103</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="35"/>
+        <v>108</v>
+      </c>
+      <c r="D10" s="31"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="31" t="s">
         <v>89</v>
       </c>
       <c r="H10" s="20">
         <v>0.2</v>
       </c>
       <c r="I10" s="14"/>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="31" t="s">
         <v>89</v>
       </c>
       <c r="K10" s="20">
         <v>0.6</v>
       </c>
       <c r="L10" s="14"/>
-      <c r="M10" s="35" t="s">
+      <c r="M10" s="31" t="s">
         <v>89</v>
       </c>
       <c r="N10" s="20">
         <v>0.9</v>
       </c>
-      <c r="P10" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="32"/>
+      <c r="P10" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="27">
+        <v>1</v>
+      </c>
+      <c r="R10" s="28"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="35"/>
+        <v>108</v>
+      </c>
+      <c r="D11" s="31"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="35"/>
+      <c r="G11" s="31"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="35" t="s">
+      <c r="J11" s="31" t="s">
         <v>89</v>
       </c>
       <c r="K11" s="20">
         <v>0.3</v>
       </c>
       <c r="L11" s="14"/>
-      <c r="M11" s="35" t="s">
+      <c r="M11" s="31" t="s">
         <v>89</v>
       </c>
       <c r="N11" s="20">
         <v>0.9</v>
       </c>
-      <c r="P11" s="38" t="s">
+      <c r="P11" s="34" t="s">
         <v>89</v>
       </c>
       <c r="Q11" s="27">
@@ -3195,57 +3312,57 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="35"/>
+        <v>107</v>
+      </c>
+      <c r="D12" s="31"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="35"/>
+      <c r="G12" s="31"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="35" t="s">
+      <c r="J12" s="31" t="s">
         <v>89</v>
       </c>
       <c r="K12" s="20">
         <v>0.5</v>
       </c>
       <c r="L12" s="14"/>
-      <c r="M12" s="38" t="s">
+      <c r="M12" s="34" t="s">
         <v>89</v>
       </c>
       <c r="N12" s="27">
         <v>1</v>
       </c>
       <c r="O12" s="29"/>
-      <c r="P12" s="35"/>
+      <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
     <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="52" t="s">
-        <v>101</v>
+      <c r="B13" s="47" t="s">
+        <v>100</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="36"/>
+        <v>108</v>
+      </c>
+      <c r="D13" s="32"/>
       <c r="E13" s="16"/>
       <c r="F13" s="17"/>
-      <c r="G13" s="36"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="16"/>
       <c r="I13" s="17"/>
-      <c r="J13" s="36"/>
+      <c r="J13" s="32"/>
       <c r="K13" s="16"/>
       <c r="L13" s="17"/>
-      <c r="M13" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="N13" s="49">
+      <c r="M13" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="N13" s="44">
         <v>1</v>
       </c>
-      <c r="O13" s="50"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="51"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
     <row r="21" spans="10:19" x14ac:dyDescent="0.35">
@@ -3280,6 +3397,7 @@
     <col min="4" max="4" width="15.54296875" customWidth="1"/>
     <col min="5" max="5" width="20.81640625" customWidth="1"/>
     <col min="6" max="6" width="19.26953125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.1796875" customWidth="1"/>
     <col min="9" max="9" width="19.7265625" customWidth="1"/>
     <col min="11" max="11" width="16.26953125" customWidth="1"/>
@@ -3346,10 +3464,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="21"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="11"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="12"/>
       <c r="G5" s="21"/>
       <c r="H5" s="11"/>
@@ -3359,8 +3477,8 @@
       <c r="L5" s="12"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="18"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="18"/>
       <c r="F6" s="14"/>
       <c r="G6" s="18"/>
@@ -3368,8 +3486,8 @@
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="18"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="18"/>
       <c r="F7" s="14"/>
       <c r="G7" s="18"/>
@@ -3377,8 +3495,8 @@
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="18"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="14"/>
       <c r="D8" s="18"/>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
@@ -3386,8 +3504,8 @@
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="18"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="14"/>
       <c r="D9" s="18"/>
       <c r="F9" s="14"/>
       <c r="G9" s="18"/>
@@ -3395,8 +3513,8 @@
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="18"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="18"/>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
@@ -3404,8 +3522,8 @@
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="18"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="18"/>
       <c r="F11" s="14"/>
       <c r="G11" s="18"/>
@@ -3413,8 +3531,8 @@
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="18"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="18"/>
       <c r="F12" s="14"/>
       <c r="G12" s="18"/>
@@ -3422,8 +3540,8 @@
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="18"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
       <c r="G13" s="18"/>
@@ -3431,8 +3549,8 @@
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="18"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="18"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18"/>
@@ -3440,8 +3558,8 @@
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="18"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="14"/>
       <c r="D15" s="18"/>
       <c r="F15" s="14"/>
       <c r="G15" s="18"/>
@@ -3449,8 +3567,8 @@
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="18"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="18"/>
       <c r="F16" s="14"/>
       <c r="G16" s="18"/>
@@ -3458,8 +3576,8 @@
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="18"/>
-      <c r="C17" s="41"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18"/>
@@ -3467,8 +3585,8 @@
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="18"/>
-      <c r="C18" s="41"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18"/>
@@ -3476,8 +3594,8 @@
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="18"/>
-      <c r="C19" s="41"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
       <c r="G19" s="18"/>
@@ -3485,8 +3603,8 @@
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="18"/>
-      <c r="C20" s="41"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="18"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18"/>
@@ -3494,8 +3612,8 @@
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="18"/>
-      <c r="C21" s="41"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18"/>
@@ -3503,8 +3621,8 @@
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="18"/>
-      <c r="C22" s="41"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
       <c r="G22" s="18"/>
@@ -3512,8 +3630,8 @@
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="18"/>
-      <c r="C23" s="41"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="14"/>
       <c r="D23" s="18"/>
       <c r="F23" s="14"/>
       <c r="G23" s="18"/>
@@ -3521,8 +3639,8 @@
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="18"/>
-      <c r="C24" s="41"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="18"/>
       <c r="F24" s="14"/>
       <c r="G24" s="18"/>
@@ -3530,8 +3648,8 @@
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="18"/>
-      <c r="C25" s="41"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="18"/>
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
@@ -3539,8 +3657,8 @@
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="18"/>
-      <c r="C26" s="41"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
@@ -3548,8 +3666,8 @@
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="18"/>
-      <c r="C27" s="41"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
       <c r="G27" s="18"/>
@@ -3557,8 +3675,8 @@
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="18"/>
-      <c r="C28" s="41"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="14"/>
       <c r="D28" s="18"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
@@ -3566,8 +3684,8 @@
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="18"/>
-      <c r="C29" s="41"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="14"/>
       <c r="D29" s="18"/>
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
@@ -3575,8 +3693,8 @@
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="18"/>
-      <c r="C30" s="41"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="14"/>
       <c r="D30" s="18"/>
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
@@ -3584,8 +3702,8 @@
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="18"/>
-      <c r="C31" s="41"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="18"/>
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
@@ -3593,17 +3711,17 @@
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="18"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="18"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="50"/>
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="18"/>
-      <c r="C33" s="41"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="18"/>
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
@@ -3611,8 +3729,8 @@
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="18"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="14"/>
       <c r="D34" s="18"/>
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
@@ -3620,8 +3738,8 @@
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35" s="18"/>
-      <c r="C35" s="41"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="14"/>
       <c r="D35" s="18"/>
       <c r="F35" s="14"/>
       <c r="G35" s="18"/>
@@ -3629,8 +3747,8 @@
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36" s="18"/>
-      <c r="C36" s="41"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="14"/>
       <c r="D36" s="18"/>
       <c r="F36" s="14"/>
       <c r="G36" s="18"/>
@@ -3638,8 +3756,8 @@
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37" s="18"/>
-      <c r="C37" s="41"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="14"/>
       <c r="D37" s="18"/>
       <c r="F37" s="14"/>
       <c r="G37" s="18"/>
@@ -3647,8 +3765,8 @@
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38" s="18"/>
-      <c r="C38" s="41"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="18"/>
       <c r="F38" s="14"/>
       <c r="G38" s="18"/>
@@ -3656,8 +3774,8 @@
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39" s="18"/>
-      <c r="C39" s="41"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="18"/>
       <c r="F39" s="14"/>
       <c r="G39" s="18"/>
@@ -3665,8 +3783,8 @@
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="22"/>
-      <c r="C40" s="42"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="17"/>
       <c r="D40" s="22"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
@@ -3678,7 +3796,16 @@
       <c r="L40" s="17"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5:B40">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>COUNTIF(D5:L5,100%)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3695,6 +3822,8 @@
     <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:12" ht="46" x14ac:dyDescent="1">
@@ -3708,17 +3837,23 @@
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="48">
+        <v>46083</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="48">
+        <v>46090</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="48">
+        <v>46104</v>
+      </c>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -3757,11 +3892,11 @@
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="40" t="s">
-        <v>110</v>
+      <c r="C7" s="35" t="s">
+        <v>109</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>89</v>
@@ -3776,11 +3911,11 @@
       <c r="L7" s="12"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>107</v>
+      <c r="C8" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>89</v>
@@ -3791,11 +3926,11 @@
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>107</v>
+      <c r="C9" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>89</v>
@@ -3806,11 +3941,11 @@
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>108</v>
+      <c r="C10" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>89</v>
@@ -3821,11 +3956,11 @@
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>110</v>
+      <c r="B11" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>109</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>89</v>
@@ -3836,11 +3971,11 @@
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>107</v>
+      <c r="C12" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D12" s="18"/>
       <c r="F12" s="14"/>
@@ -3851,11 +3986,11 @@
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>107</v>
+      <c r="C13" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
@@ -3866,11 +4001,11 @@
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="41" t="s">
-        <v>107</v>
+      <c r="C14" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D14" s="18"/>
       <c r="F14" s="14"/>
@@ -3881,11 +4016,11 @@
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="41" t="s">
-        <v>107</v>
+      <c r="C15" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D15" s="18"/>
       <c r="F15" s="14"/>
@@ -3896,11 +4031,11 @@
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="41" t="s">
-        <v>107</v>
+      <c r="C16" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D16" s="18"/>
       <c r="F16" s="14"/>
@@ -3911,11 +4046,11 @@
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>108</v>
+      <c r="B17" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
@@ -3926,11 +4061,11 @@
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="41" t="s">
-        <v>108</v>
+      <c r="C18" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
@@ -3941,11 +4076,11 @@
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="41" t="s">
-        <v>108</v>
+      <c r="C19" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
@@ -3956,11 +4091,11 @@
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="41" t="s">
-        <v>108</v>
+      <c r="C20" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D20" s="18"/>
       <c r="F20" s="14"/>
@@ -3971,11 +4106,11 @@
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="41" t="s">
-        <v>108</v>
+      <c r="C21" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
@@ -3987,11 +4122,11 @@
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>108</v>
+      <c r="B22" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
@@ -4003,11 +4138,11 @@
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>108</v>
+      <c r="B23" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D23" s="18"/>
       <c r="F23" s="14"/>
@@ -4019,11 +4154,11 @@
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="41" t="s">
-        <v>108</v>
+      <c r="C24" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D24" s="18"/>
       <c r="F24" s="14"/>
@@ -4038,8 +4173,8 @@
       <c r="B25" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="41" t="s">
-        <v>108</v>
+      <c r="C25" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="D25" s="18"/>
       <c r="F25" s="14"/>
@@ -4051,11 +4186,11 @@
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="41" t="s">
-        <v>107</v>
+      <c r="C26" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
@@ -4070,8 +4205,8 @@
       <c r="B27" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>107</v>
+      <c r="C27" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
@@ -4083,11 +4218,11 @@
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>107</v>
+      <c r="C28" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D28" s="18"/>
       <c r="F28" s="14"/>
@@ -4099,11 +4234,11 @@
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>107</v>
+      <c r="C29" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D29" s="18"/>
       <c r="F29" s="14"/>
@@ -4115,11 +4250,11 @@
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>107</v>
+      <c r="C30" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D30" s="18"/>
       <c r="F30" s="14"/>
@@ -4131,11 +4266,11 @@
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>107</v>
+      <c r="C31" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D31" s="18"/>
       <c r="F31" s="14"/>
@@ -4147,11 +4282,11 @@
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="41" t="s">
-        <v>107</v>
+      <c r="C32" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D32" s="18"/>
       <c r="F32" s="14"/>
@@ -4163,11 +4298,11 @@
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>107</v>
+      <c r="C33" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D33" s="18"/>
       <c r="F33" s="14"/>
@@ -4179,11 +4314,11 @@
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>107</v>
+      <c r="C34" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="D34" s="18"/>
       <c r="F34" s="14"/>
@@ -4195,11 +4330,11 @@
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="42" t="s">
-        <v>107</v>
+      <c r="C35" s="37" t="s">
+        <v>106</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="16"/>
@@ -4230,6 +4365,7 @@
     <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
     <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
@@ -4419,10 +4555,10 @@
     <col min="4" max="4" width="15.7265625" customWidth="1"/>
     <col min="5" max="5" width="21.26953125" customWidth="1"/>
     <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="9.54296875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.81640625" customWidth="1"/>
     <col min="9" max="9" width="18.7265625" customWidth="1"/>
-    <col min="10" max="10" width="9.81640625" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.26953125" customWidth="1"/>
     <col min="12" max="12" width="18.7265625" customWidth="1"/>
   </cols>
@@ -4438,17 +4574,23 @@
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="48">
+        <v>46111</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="48">
+        <v>46125</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="48">
+        <v>46132</v>
+      </c>
       <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -4487,8 +4629,8 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="21"/>
-      <c r="C5" s="40"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="12"/>
       <c r="D5" s="21"/>
       <c r="E5" s="11"/>
       <c r="F5" s="12"/>
@@ -4500,8 +4642,8 @@
       <c r="L5" s="12"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="18"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="18"/>
       <c r="F6" s="14"/>
       <c r="G6" s="18"/>
@@ -4509,8 +4651,8 @@
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="18"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="18"/>
       <c r="F7" s="14"/>
       <c r="G7" s="18"/>
@@ -4518,8 +4660,8 @@
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="18"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="14"/>
       <c r="D8" s="18"/>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
@@ -4527,8 +4669,8 @@
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="18"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="14"/>
       <c r="D9" s="18"/>
       <c r="F9" s="14"/>
       <c r="G9" s="18"/>
@@ -4536,8 +4678,8 @@
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="18"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="18"/>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
@@ -4545,8 +4687,8 @@
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="18"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="18"/>
       <c r="F11" s="14"/>
       <c r="G11" s="18"/>
@@ -4554,8 +4696,8 @@
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="18"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="18"/>
       <c r="F12" s="14"/>
       <c r="G12" s="18"/>
@@ -4563,8 +4705,8 @@
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="18"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
       <c r="G13" s="18"/>
@@ -4572,8 +4714,8 @@
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="18"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="18"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18"/>
@@ -4581,8 +4723,8 @@
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="18"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="14"/>
       <c r="D15" s="18"/>
       <c r="F15" s="14"/>
       <c r="G15" s="18"/>
@@ -4590,8 +4732,8 @@
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="18"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="18"/>
       <c r="F16" s="14"/>
       <c r="G16" s="18"/>
@@ -4599,8 +4741,8 @@
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="18"/>
-      <c r="C17" s="41"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18"/>
@@ -4608,8 +4750,8 @@
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="18"/>
-      <c r="C18" s="41"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18"/>
@@ -4617,8 +4759,8 @@
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="18"/>
-      <c r="C19" s="41"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
       <c r="G19" s="18"/>
@@ -4626,8 +4768,8 @@
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="18"/>
-      <c r="C20" s="41"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="18"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18"/>
@@ -4635,8 +4777,8 @@
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="18"/>
-      <c r="C21" s="41"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18"/>
@@ -4644,8 +4786,8 @@
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="18"/>
-      <c r="C22" s="41"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
       <c r="G22" s="18"/>
@@ -4653,8 +4795,8 @@
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="18"/>
-      <c r="C23" s="41"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="14"/>
       <c r="D23" s="18"/>
       <c r="F23" s="14"/>
       <c r="G23" s="18"/>
@@ -4662,8 +4804,8 @@
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="18"/>
-      <c r="C24" s="41"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="18"/>
       <c r="F24" s="14"/>
       <c r="G24" s="18"/>
@@ -4671,8 +4813,8 @@
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="18"/>
-      <c r="C25" s="41"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="18"/>
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
@@ -4680,8 +4822,8 @@
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="18"/>
-      <c r="C26" s="41"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
@@ -4689,8 +4831,8 @@
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="18"/>
-      <c r="C27" s="41"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
       <c r="G27" s="18"/>
@@ -4698,8 +4840,8 @@
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="18"/>
-      <c r="C28" s="41"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="14"/>
       <c r="D28" s="18"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
@@ -4707,8 +4849,8 @@
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="18"/>
-      <c r="C29" s="41"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="14"/>
       <c r="D29" s="18"/>
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
@@ -4716,8 +4858,8 @@
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="18"/>
-      <c r="C30" s="41"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="14"/>
       <c r="D30" s="18"/>
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
@@ -4725,8 +4867,8 @@
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="18"/>
-      <c r="C31" s="41"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="18"/>
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
@@ -4734,8 +4876,8 @@
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="18"/>
-      <c r="C32" s="41"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="14"/>
       <c r="D32" s="18"/>
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
@@ -4743,8 +4885,8 @@
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="18"/>
-      <c r="C33" s="41"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="18"/>
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
@@ -4752,8 +4894,8 @@
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="18"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="14"/>
       <c r="D34" s="18"/>
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
@@ -4761,8 +4903,8 @@
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35" s="18"/>
-      <c r="C35" s="41"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="14"/>
       <c r="D35" s="18"/>
       <c r="F35" s="14"/>
       <c r="G35" s="18"/>
@@ -4770,8 +4912,8 @@
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36" s="18"/>
-      <c r="C36" s="41"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="14"/>
       <c r="D36" s="18"/>
       <c r="F36" s="14"/>
       <c r="G36" s="18"/>
@@ -4779,8 +4921,8 @@
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37" s="18"/>
-      <c r="C37" s="41"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="14"/>
       <c r="D37" s="18"/>
       <c r="F37" s="14"/>
       <c r="G37" s="18"/>
@@ -4788,8 +4930,8 @@
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38" s="18"/>
-      <c r="C38" s="41"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="18"/>
       <c r="F38" s="14"/>
       <c r="G38" s="18"/>
@@ -4797,8 +4939,8 @@
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39" s="18"/>
-      <c r="C39" s="41"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="18"/>
       <c r="F39" s="14"/>
       <c r="G39" s="18"/>
@@ -4806,8 +4948,8 @@
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="22"/>
-      <c r="C40" s="42"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="17"/>
       <c r="D40" s="22"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
@@ -4820,6 +4962,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="B5:B40">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>COUNTIF(D5:L5,100%)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4829,7 +4979,7 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B2:O57"/>
+  <dimension ref="B2:O56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
@@ -4911,9 +5061,9 @@
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="38" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="21" t="s">
@@ -4936,7 +5086,7 @@
         <v>55</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>89</v>
@@ -4951,28 +5101,28 @@
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="18"/>
+        <v>107</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="J8" s="18"/>
       <c r="L8" s="14"/>
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>89</v>
@@ -4987,10 +5137,10 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>89</v>
@@ -5005,10 +5155,10 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>89</v>
@@ -5023,16 +5173,18 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="18"/>
+        <v>91</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="F12" s="14"/>
       <c r="G12" s="18"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="J12" s="18"/>
       <c r="L12" s="14"/>
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
@@ -5042,7 +5194,7 @@
         <v>86</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
@@ -5057,16 +5209,16 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>89</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D14" s="18"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="18"/>
+      <c r="G14" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="I14" s="14"/>
       <c r="J14" s="18"/>
       <c r="L14" s="14"/>
@@ -5075,16 +5227,16 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="D15" s="18"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="18"/>
+      <c r="G15" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="I15" s="14"/>
       <c r="J15" s="18"/>
       <c r="L15" s="14"/>
@@ -5093,7 +5245,7 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>107</v>
@@ -5111,10 +5263,10 @@
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
@@ -5129,10 +5281,10 @@
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
@@ -5147,10 +5299,10 @@
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
@@ -5165,10 +5317,10 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D20" s="18"/>
       <c r="F20" s="14"/>
@@ -5183,10 +5335,10 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
@@ -5201,10 +5353,10 @@
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
@@ -5219,10 +5371,10 @@
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" s="18"/>
       <c r="F23" s="14"/>
@@ -5237,9 +5389,9 @@
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
         <v>107</v>
       </c>
       <c r="D24" s="18"/>
@@ -5255,10 +5407,10 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" s="18"/>
       <c r="F25" s="14"/>
@@ -5273,43 +5425,43 @@
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
+        <v>72</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="G26" s="18"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="18"/>
+      <c r="J26" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="L26" s="14"/>
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="G27" s="18"/>
       <c r="I27" s="14"/>
-      <c r="J27" s="18"/>
+      <c r="J27" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="L27" s="14"/>
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>107</v>
@@ -5327,10 +5479,10 @@
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" s="18"/>
       <c r="F29" s="14"/>
@@ -5345,10 +5497,10 @@
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D30" s="18"/>
       <c r="F30" s="14"/>
@@ -5363,10 +5515,10 @@
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D31" s="18"/>
       <c r="F31" s="14"/>
@@ -5374,12 +5526,14 @@
       <c r="I31" s="14"/>
       <c r="J31" s="18"/>
       <c r="L31" s="14"/>
-      <c r="M31" s="18"/>
+      <c r="M31" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="O31" s="14"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>107</v>
@@ -5388,19 +5542,19 @@
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
       <c r="I32" s="14"/>
-      <c r="J32" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="J32" s="18"/>
       <c r="L32" s="14"/>
-      <c r="M32" s="18"/>
+      <c r="M32" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="O32" s="14"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D33" s="18"/>
       <c r="F33" s="14"/>
@@ -5415,7 +5569,7 @@
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>107</v>
@@ -5431,142 +5585,69 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="18"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="18"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="18"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="O35" s="14"/>
-    </row>
-    <row r="36" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="15" t="s">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" s="22"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="N36" s="16"/>
-      <c r="O36" s="17"/>
-    </row>
-    <row r="38" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="45" t="s">
+      <c r="C35" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="22"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="N35" s="16"/>
+      <c r="O35" s="17"/>
+    </row>
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B48" s="35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" s="36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B39" s="40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="41" t="s">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" s="36" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="41" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="41" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B50" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B51" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B52" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B53" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B55" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="41" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B56" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="41" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B57" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" s="42" t="s">
-        <v>108</v>
-      </c>
-    </row>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5577,46 +5658,62 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="B2:M73"/>
+  <dimension ref="B2:O73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.7265625" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
     <col min="3" max="3" width="15.54296875" customWidth="1"/>
     <col min="4" max="4" width="20.26953125" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7265625" customWidth="1"/>
     <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.1796875" customWidth="1"/>
     <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="48">
+        <v>46139</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="48">
+        <v>46146</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="48">
+        <v>46153</v>
+      </c>
       <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="M4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="48">
+        <v>46161</v>
+      </c>
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -5650,10 +5747,19 @@
       <c r="L5" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="21"/>
-      <c r="C6" s="40"/>
+      <c r="M5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="51"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="21"/>
       <c r="E6" s="11"/>
       <c r="F6" s="12"/>
@@ -5663,316 +5769,353 @@
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="12"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="18"/>
-      <c r="C7" s="41"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="12"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="52"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="18"/>
       <c r="F7" s="14"/>
       <c r="G7" s="18"/>
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="18"/>
-      <c r="C8" s="41"/>
+      <c r="O7" s="14"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="52"/>
+      <c r="C8" s="14"/>
       <c r="D8" s="18"/>
       <c r="F8" s="14"/>
       <c r="G8" s="18"/>
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="18"/>
-      <c r="C9" s="41"/>
+      <c r="O8" s="14"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="52"/>
+      <c r="C9" s="14"/>
       <c r="D9" s="18"/>
       <c r="F9" s="14"/>
       <c r="G9" s="18"/>
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="18"/>
-      <c r="C10" s="41"/>
+      <c r="O9" s="14"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="52"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="18"/>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="18"/>
-      <c r="C11" s="41"/>
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="52"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="18"/>
       <c r="F11" s="14"/>
       <c r="G11" s="18"/>
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="18"/>
-      <c r="C12" s="41"/>
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="52"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="18"/>
       <c r="F12" s="14"/>
       <c r="G12" s="18"/>
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="18"/>
-      <c r="C13" s="41"/>
+      <c r="O12" s="14"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="52"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
       <c r="G13" s="18"/>
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="18"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="18"/>
+      <c r="O13" s="14"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="52"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="50"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18"/>
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="18"/>
-      <c r="C15" s="41"/>
+      <c r="O14" s="14"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="52"/>
+      <c r="C15" s="14"/>
       <c r="D15" s="18"/>
       <c r="F15" s="14"/>
       <c r="G15" s="18"/>
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="18"/>
-      <c r="C16" s="41"/>
+      <c r="O15" s="14"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="52"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="18"/>
       <c r="F16" s="14"/>
       <c r="G16" s="18"/>
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="18"/>
-      <c r="C17" s="41"/>
+      <c r="O16" s="14"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="52"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18"/>
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="18"/>
-      <c r="C18" s="41"/>
+      <c r="O17" s="14"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B18" s="52"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18"/>
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="18"/>
-      <c r="C19" s="41"/>
+      <c r="O18" s="14"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="52"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
       <c r="G19" s="18"/>
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="18"/>
-      <c r="C20" s="41"/>
+      <c r="O19" s="14"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="52"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="18"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18"/>
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="18"/>
-      <c r="C21" s="41"/>
+      <c r="O20" s="14"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B21" s="52"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18"/>
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="18"/>
-      <c r="C22" s="41"/>
+      <c r="O21" s="14"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="52"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
       <c r="G22" s="18"/>
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="18"/>
-      <c r="C23" s="41"/>
+      <c r="O22" s="14"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B23" s="52"/>
+      <c r="C23" s="14"/>
       <c r="D23" s="18"/>
       <c r="F23" s="14"/>
       <c r="G23" s="18"/>
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="18"/>
-      <c r="C24" s="41"/>
+      <c r="O23" s="14"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="52"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="18"/>
       <c r="F24" s="14"/>
       <c r="G24" s="18"/>
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="18"/>
-      <c r="C25" s="41"/>
+      <c r="O24" s="14"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="52"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="18"/>
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="18"/>
-      <c r="C26" s="41"/>
+      <c r="O25" s="14"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="52"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="18"/>
-      <c r="C27" s="41"/>
+      <c r="O26" s="14"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B27" s="52"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
       <c r="G27" s="18"/>
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="18"/>
-      <c r="C28" s="41"/>
+      <c r="O27" s="14"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="52"/>
+      <c r="C28" s="14"/>
       <c r="D28" s="18"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="18"/>
-      <c r="C29" s="41"/>
+      <c r="O28" s="14"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="52"/>
+      <c r="C29" s="14"/>
       <c r="D29" s="18"/>
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="18"/>
-      <c r="C30" s="41"/>
+      <c r="O29" s="14"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B30" s="52"/>
+      <c r="C30" s="14"/>
       <c r="D30" s="18"/>
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="18"/>
-      <c r="C31" s="41"/>
+      <c r="O30" s="14"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="52"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="18"/>
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="18"/>
-      <c r="C32" s="41"/>
+      <c r="O31" s="14"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B32" s="52"/>
+      <c r="C32" s="14"/>
       <c r="D32" s="18"/>
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="18"/>
-      <c r="C33" s="41"/>
+      <c r="O32" s="14"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="52"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="18"/>
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="18"/>
-      <c r="C34" s="41"/>
+      <c r="O33" s="14"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="52"/>
+      <c r="C34" s="14"/>
       <c r="D34" s="18"/>
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35" s="18"/>
-      <c r="C35" s="41"/>
+      <c r="O34" s="14"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="52"/>
+      <c r="C35" s="14"/>
       <c r="D35" s="18"/>
       <c r="F35" s="14"/>
       <c r="G35" s="18"/>
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36" s="18"/>
-      <c r="C36" s="41"/>
+      <c r="O35" s="14"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B36" s="52"/>
+      <c r="C36" s="14"/>
       <c r="D36" s="18"/>
       <c r="F36" s="14"/>
       <c r="G36" s="18"/>
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37" s="18"/>
-      <c r="C37" s="41"/>
+      <c r="O36" s="14"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="52"/>
+      <c r="C37" s="14"/>
       <c r="D37" s="18"/>
       <c r="F37" s="14"/>
       <c r="G37" s="18"/>
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38" s="18"/>
-      <c r="C38" s="41"/>
+      <c r="O37" s="14"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="52"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="18"/>
       <c r="F38" s="14"/>
       <c r="G38" s="18"/>
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39" s="18"/>
-      <c r="C39" s="41"/>
+      <c r="O38" s="14"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B39" s="52"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="18"/>
       <c r="F39" s="14"/>
       <c r="G39" s="18"/>
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B40" s="18"/>
-      <c r="C40" s="41"/>
+      <c r="O39" s="14"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="52"/>
+      <c r="C40" s="14"/>
       <c r="D40" s="18"/>
       <c r="F40" s="14"/>
       <c r="G40" s="18"/>
       <c r="I40" s="14"/>
       <c r="L40" s="14"/>
-    </row>
-    <row r="41" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="22"/>
-      <c r="C41" s="42"/>
+      <c r="O40" s="14"/>
+    </row>
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="53"/>
+      <c r="C41" s="17"/>
       <c r="D41" s="22"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
@@ -5982,6 +6125,9 @@
       <c r="J41" s="16"/>
       <c r="K41" s="16"/>
       <c r="L41" s="17"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="17"/>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D64" s="5"/>
@@ -6039,6 +6185,14 @@
       <c r="M73" s="5"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B6:B41">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>COUNTIF(D6:L6,100%)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>COUNTIF(D6:L6,100%)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,43 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3F533C-39A6-4B68-A629-9F0BD55DE36C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1F0310-2F9A-45FC-BF67-D89F89492E03}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
-    <sheet name="Planification trop détaillée" sheetId="11" r:id="rId2"/>
-    <sheet name="Sprint 1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sprint 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Planif Sprint 2" sheetId="8" r:id="rId3"/>
     <sheet name="Sprint 2" sheetId="3" r:id="rId4"/>
-    <sheet name="Planif Sprint 2" sheetId="8" r:id="rId5"/>
-    <sheet name="Mi-mandat" sheetId="7" r:id="rId6"/>
-    <sheet name="Sprint 3" sheetId="4" r:id="rId7"/>
-    <sheet name="Planif Sprint 3" sheetId="9" r:id="rId8"/>
-    <sheet name="Sprint 4" sheetId="5" r:id="rId9"/>
+    <sheet name="Mi-mandat" sheetId="7" r:id="rId5"/>
+    <sheet name="Sprint 3" sheetId="4" r:id="rId6"/>
+    <sheet name="Planif Sprint 3" sheetId="9" r:id="rId7"/>
+    <sheet name="Sprint 4" sheetId="5" r:id="rId8"/>
+    <sheet name="Planification trop détaillée" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$D$1:$D$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Planification trop détaillée'!$B$1:$D$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="160">
   <si>
     <t>Planification globale</t>
   </si>
@@ -514,6 +519,9 @@
   </si>
   <si>
     <t>Temps total:</t>
+  </si>
+  <si>
+    <t>des pertes de connexions aléatoires</t>
   </si>
 </sst>
 </file>
@@ -939,18 +947,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -978,49 +979,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1341,30 +1300,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A98864-B157-464B-9C9C-D10C2E7AC6B8}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="143.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="2" max="2" width="116" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.65" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="2:5" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1378,7 +1337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
         <v>153</v>
       </c>
@@ -1392,7 +1351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>123</v>
       </c>
@@ -1406,7 +1365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>124</v>
       </c>
@@ -1420,7 +1379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
         <v>125</v>
       </c>
@@ -1434,7 +1393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>126</v>
       </c>
@@ -1448,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
         <v>128</v>
       </c>
@@ -1462,7 +1421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>129</v>
       </c>
@@ -1476,7 +1435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>130</v>
       </c>
@@ -1490,7 +1449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="18" t="s">
         <v>157</v>
       </c>
@@ -1504,7 +1463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
         <v>133</v>
       </c>
@@ -1518,7 +1477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
         <v>134</v>
       </c>
@@ -1532,7 +1491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
         <v>136</v>
       </c>
@@ -1546,7 +1505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
         <v>142</v>
       </c>
@@ -1560,7 +1519,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
         <v>131</v>
       </c>
@@ -1574,7 +1533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
         <v>132</v>
       </c>
@@ -1588,7 +1547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="18" t="s">
         <v>137</v>
       </c>
@@ -1602,7 +1561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
         <v>138</v>
       </c>
@@ -1616,7 +1575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
         <v>139</v>
       </c>
@@ -1630,7 +1589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
         <v>141</v>
       </c>
@@ -1644,7 +1603,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
         <v>145</v>
       </c>
@@ -1658,7 +1617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
         <v>146</v>
       </c>
@@ -1672,7 +1631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>147</v>
       </c>
@@ -1686,7 +1645,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" s="18" t="s">
         <v>140</v>
       </c>
@@ -1700,7 +1659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
         <v>143</v>
       </c>
@@ -1714,7 +1673,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" s="18" t="s">
         <v>135</v>
       </c>
@@ -1728,7 +1687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
         <v>144</v>
       </c>
@@ -1742,7 +1701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" s="18" t="s">
         <v>148</v>
       </c>
@@ -1756,7 +1715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" s="18" t="s">
         <v>149</v>
       </c>
@@ -1770,7 +1729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" s="18" t="s">
         <v>150</v>
       </c>
@@ -1784,7 +1743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="18" t="s">
         <v>151</v>
       </c>
@@ -1798,7 +1757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="18" t="s">
         <v>152</v>
       </c>
@@ -1812,7 +1771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="22" t="s">
         <v>127</v>
       </c>
@@ -1826,8 +1785,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D39" s="41" t="s">
         <v>158</v>
       </c>
@@ -1837,7 +1796,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D39" xr:uid="{E2A98864-B157-464B-9C9C-D10C2E7AC6B8}"/>
+  <autoFilter ref="B5:E37" xr:uid="{355B5BC9-E127-44A4-BBE6-CA2E735F8DE3}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Sprint 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D20 D21:D37" xr:uid="{C1E49912-FB61-4F2F-8F8F-588FF6944C57}">
       <formula1>"Haute,Moyenne,Basse,"</formula1>
@@ -1852,1166 +1817,37 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7295A98A-9DE5-4CC0-A28E-4AAE25FE895B}">
-  <sheetPr>
-    <tabColor rgb="FF7030A0"/>
-  </sheetPr>
-  <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="93.26953125" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="42.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:6" ht="44.65" customHeight="1" x14ac:dyDescent="1">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B46" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B48" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B49" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B51" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B52" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B53" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B54" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B55" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B56" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B57" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B58" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B59" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B60" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B62" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B63" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B65" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B66" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B67" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B68" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B69" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B70" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B71" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B73" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B74" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B75" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-    </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-    </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-    </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-    </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-    </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-    </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-    </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="B1:D101" xr:uid="{E2A98864-B157-464B-9C9C-D10C2E7AC6B8}"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D101" xr:uid="{F51E1D81-F30A-455D-8193-BBE5DE529FFA}">
-      <formula1>"Sprint 1,Sprint 2,Sprint 3,Sprint 4,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E101" xr:uid="{0A8A13BB-479E-47FC-B198-FA503076D14C}">
-      <formula1>"Haute,Moyenne,Basse,"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC485589-D367-4045-AC2C-21AA964CF385}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" customWidth="1"/>
-    <col min="9" max="9" width="18.7265625" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
-    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3041,7 +1877,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -3095,7 +1931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -3122,7 +1958,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -3144,7 +1980,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -3171,7 +2007,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -3204,7 +2040,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -3241,7 +2077,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -3278,7 +2114,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -3310,7 +2146,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -3338,7 +2174,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -3365,18 +2201,572 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C124977E-5C0D-4B3E-AF9C-0A24BFACEC79}">
+  <sheetPr>
+    <tabColor theme="7"/>
+  </sheetPr>
+  <dimension ref="B3:L35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="7"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="48">
+        <v>46083</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="48">
+        <v>46090</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="48">
+        <v>46104</v>
+      </c>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="11">
+        <v>100</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="18"/>
+      <c r="I8" s="14"/>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="18"/>
+      <c r="I9" s="14"/>
+      <c r="L9" s="14"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="18"/>
+      <c r="I10" s="14"/>
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="18"/>
+      <c r="I11" s="14"/>
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="L12" s="14"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="L14" s="14"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="14"/>
+      <c r="L15" s="14"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="L16" s="14"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="L17" s="14"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="18"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="L18" s="14"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="18"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="14"/>
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="18"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" s="14"/>
+      <c r="L20" s="14"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="18"/>
+      <c r="I21" s="14"/>
+      <c r="J21" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" s="14"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="18"/>
+      <c r="I22" s="14"/>
+      <c r="J22" t="s">
+        <v>89</v>
+      </c>
+      <c r="L22" s="14"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="18"/>
+      <c r="I23" s="14"/>
+      <c r="J23" t="s">
+        <v>89</v>
+      </c>
+      <c r="L23" s="14"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="18"/>
+      <c r="I24" s="14"/>
+      <c r="J24" t="s">
+        <v>89</v>
+      </c>
+      <c r="L24" s="14"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="18"/>
+      <c r="I25" s="14"/>
+      <c r="J25" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="18"/>
+      <c r="I26" s="14"/>
+      <c r="J26" t="s">
+        <v>89</v>
+      </c>
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="18"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="18"/>
+      <c r="I27" s="14"/>
+      <c r="J27" t="s">
+        <v>89</v>
+      </c>
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="18"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="18"/>
+      <c r="I28" s="14"/>
+      <c r="J28" t="s">
+        <v>89</v>
+      </c>
+      <c r="L28" s="14"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="18"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="18"/>
+      <c r="I29" s="14"/>
+      <c r="J29" t="s">
+        <v>89</v>
+      </c>
+      <c r="L29" s="14"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="18"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="18"/>
+      <c r="I30" s="14"/>
+      <c r="J30" t="s">
+        <v>89</v>
+      </c>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="18"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="18"/>
+      <c r="I31" s="14"/>
+      <c r="J31" t="s">
+        <v>89</v>
+      </c>
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="18"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="18"/>
+      <c r="I32" s="14"/>
+      <c r="J32" t="s">
+        <v>89</v>
+      </c>
+      <c r="L32" s="14"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="18"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="18"/>
+      <c r="I33" s="14"/>
+      <c r="J33" t="s">
+        <v>89</v>
+      </c>
+      <c r="L33" s="14"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="18"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="18"/>
+      <c r="I34" s="14"/>
+      <c r="J34" t="s">
+        <v>89</v>
+      </c>
+      <c r="L34" s="14"/>
+    </row>
+    <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="22"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3389,27 +2779,27 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.26953125" customWidth="1"/>
-    <col min="2" max="2" width="77.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" customWidth="1"/>
-    <col min="4" max="4" width="15.54296875" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" customWidth="1"/>
-    <col min="6" max="6" width="19.26953125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" customWidth="1"/>
-    <col min="9" max="9" width="19.7265625" customWidth="1"/>
-    <col min="11" max="11" width="16.26953125" customWidth="1"/>
-    <col min="12" max="12" width="19.453125" customWidth="1"/>
+    <col min="1" max="1" width="2.21875" customWidth="1"/>
+    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" customWidth="1"/>
+    <col min="9" max="9" width="19.77734375" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3428,7 +2818,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3463,7 +2853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="35"/>
       <c r="C5" s="12"/>
       <c r="D5" s="49"/>
@@ -3476,7 +2866,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="36"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -3485,7 +2875,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="36"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -3494,7 +2884,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="36"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -3503,7 +2893,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -3512,7 +2902,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="36"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -3521,7 +2911,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="36"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -3530,7 +2920,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="36"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -3539,7 +2929,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="36"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -3548,7 +2938,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="36"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -3557,7 +2947,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="36"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -3566,7 +2956,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="36"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -3575,7 +2965,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="36"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3584,7 +2974,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="36"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3593,7 +2983,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="36"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3602,7 +2992,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="36"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3611,7 +3001,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="36"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3620,7 +3010,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="36"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3629,7 +3019,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="36"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3638,7 +3028,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="36"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3647,7 +3037,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="36"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3656,7 +3046,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="36"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3665,7 +3055,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="36"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3674,7 +3064,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="36"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3683,7 +3073,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="36"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3692,7 +3082,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="36"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3701,7 +3091,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="36"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3710,7 +3100,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="36"/>
       <c r="C32" s="14"/>
       <c r="D32" s="50"/>
@@ -3719,7 +3109,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="36"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3728,7 +3118,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="36"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3737,7 +3127,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="36"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3746,7 +3136,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="36"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3755,7 +3145,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="36"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3764,7 +3154,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="36"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3773,7 +3163,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="36"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3782,7 +3172,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="37"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3797,10 +3187,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B40">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>COUNTIF(D5:L5,100%)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3810,570 +3200,26 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C124977E-5C0D-4B3E-AF9C-0A24BFACEC79}">
-  <sheetPr>
-    <tabColor theme="7"/>
-  </sheetPr>
-  <dimension ref="B3:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="77.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" customWidth="1"/>
-    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:12" ht="46" x14ac:dyDescent="1">
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="7"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="48">
-        <v>46083</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="48">
-        <v>46090</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="48">
-        <v>46104</v>
-      </c>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="12"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="18"/>
-      <c r="I8" s="14"/>
-      <c r="L8" s="14"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="18"/>
-      <c r="I9" s="14"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="14"/>
-      <c r="L10" s="14"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="18"/>
-      <c r="I11" s="14"/>
-      <c r="L11" s="14"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="14"/>
-      <c r="L12" s="14"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="18"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="14"/>
-      <c r="L14" s="14"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="18"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="L15" s="14"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="18"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" s="14"/>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="18"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="14"/>
-      <c r="L17" s="14"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" s="18"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" s="14"/>
-      <c r="L18" s="14"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="18"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="14"/>
-      <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="18"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" s="14"/>
-      <c r="L20" s="14"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="18"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="18"/>
-      <c r="I21" s="14"/>
-      <c r="J21" t="s">
-        <v>89</v>
-      </c>
-      <c r="L21" s="14"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="18"/>
-      <c r="I22" s="14"/>
-      <c r="J22" t="s">
-        <v>89</v>
-      </c>
-      <c r="L22" s="14"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" s="18"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="18"/>
-      <c r="I23" s="14"/>
-      <c r="J23" t="s">
-        <v>89</v>
-      </c>
-      <c r="L23" s="14"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" s="18"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="18"/>
-      <c r="I24" s="14"/>
-      <c r="J24" t="s">
-        <v>89</v>
-      </c>
-      <c r="L24" s="14"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="18"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="18"/>
-      <c r="I25" s="14"/>
-      <c r="J25" t="s">
-        <v>89</v>
-      </c>
-      <c r="L25" s="14"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="18"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="18"/>
-      <c r="I26" s="14"/>
-      <c r="J26" t="s">
-        <v>89</v>
-      </c>
-      <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" s="18"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="18"/>
-      <c r="I27" s="14"/>
-      <c r="J27" t="s">
-        <v>89</v>
-      </c>
-      <c r="L27" s="14"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="18"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="18"/>
-      <c r="I28" s="14"/>
-      <c r="J28" t="s">
-        <v>89</v>
-      </c>
-      <c r="L28" s="14"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="18"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="18"/>
-      <c r="I29" s="14"/>
-      <c r="J29" t="s">
-        <v>89</v>
-      </c>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="18"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="18"/>
-      <c r="I30" s="14"/>
-      <c r="J30" t="s">
-        <v>89</v>
-      </c>
-      <c r="L30" s="14"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" s="18"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="18"/>
-      <c r="I31" s="14"/>
-      <c r="J31" t="s">
-        <v>89</v>
-      </c>
-      <c r="L31" s="14"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" s="18"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="18"/>
-      <c r="I32" s="14"/>
-      <c r="J32" t="s">
-        <v>89</v>
-      </c>
-      <c r="L32" s="14"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="18"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="18"/>
-      <c r="I33" s="14"/>
-      <c r="J33" t="s">
-        <v>89</v>
-      </c>
-      <c r="L33" s="14"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="18"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="18"/>
-      <c r="I34" s="14"/>
-      <c r="J34" t="s">
-        <v>89</v>
-      </c>
-      <c r="L34" s="14"/>
-    </row>
-    <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="17"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE02E41-CCB4-4A52-8A11-897838372758}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="70.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" customWidth="1"/>
-    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -4387,151 +3233,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -4541,34 +3387,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A181AE-6DCE-4F2E-9BC3-78C1EB9A33C7}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" customWidth="1"/>
-    <col min="9" max="9" width="18.7265625" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.26953125" customWidth="1"/>
-    <col min="12" max="12" width="18.7265625" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -4593,7 +3439,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -4628,7 +3474,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="51"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
@@ -4641,7 +3487,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="52"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -4650,7 +3496,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -4659,7 +3505,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -4668,7 +3514,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -4677,7 +3523,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -4686,7 +3532,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -4695,7 +3541,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -4704,7 +3550,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -4713,7 +3559,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -4722,7 +3568,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -4731,7 +3577,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -4740,7 +3586,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -4749,7 +3595,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -4758,7 +3604,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -4767,7 +3613,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -4776,7 +3622,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -4785,7 +3631,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -4794,7 +3640,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -4803,7 +3649,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -4812,7 +3658,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -4821,7 +3667,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -4830,7 +3676,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -4839,7 +3685,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -4848,7 +3694,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -4857,7 +3703,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -4866,7 +3712,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -4875,7 +3721,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -4884,7 +3730,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -4893,7 +3739,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -4902,7 +3748,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -4911,7 +3757,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -4920,7 +3766,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -4929,7 +3775,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -4938,7 +3784,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -4947,7 +3793,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="53"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -4963,10 +3809,10 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="B5:B40">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>COUNTIF(D5:L5,100%)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4974,24 +3820,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EA87E6-A735-40DF-9804-F8FF12E4BB41}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -5015,7 +3861,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -5059,7 +3905,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -5081,7 +3927,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -5099,7 +3945,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -5117,7 +3963,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -5135,7 +3981,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -5153,7 +3999,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -5171,7 +4017,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -5189,7 +4035,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -5207,7 +4053,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -5225,7 +4071,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -5243,7 +4089,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -5261,7 +4107,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -5279,7 +4125,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -5297,7 +4143,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -5315,7 +4161,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -5333,7 +4179,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -5351,7 +4197,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -5369,7 +4215,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -5387,7 +4233,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -5405,7 +4251,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -5423,7 +4269,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -5441,7 +4287,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -5459,7 +4305,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -5477,7 +4323,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -5495,7 +4341,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -5513,7 +4359,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -5531,7 +4377,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -5549,7 +4395,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -5567,7 +4413,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -5585,7 +4431,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -5607,81 +4453,81 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DECEB1-A674-4E9A-9A60-FE266B1759EE}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.7265625" customWidth="1"/>
-    <col min="2" max="2" width="51.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.26953125" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7265625" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.26953125" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -5713,7 +4559,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -5757,7 +4603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="51"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
@@ -5773,7 +4619,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -5783,7 +4629,7 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -5793,7 +4639,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -5803,7 +4649,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -5813,7 +4659,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -5823,7 +4669,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -5833,7 +4679,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -5843,7 +4689,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="50"/>
@@ -5853,7 +4699,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -5863,7 +4709,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -5873,7 +4719,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -5883,7 +4729,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -5893,7 +4739,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -5903,7 +4749,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -5913,7 +4759,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -5923,7 +4769,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -5933,7 +4779,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -5943,7 +4789,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -5953,7 +4799,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -5963,7 +4809,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -5973,7 +4819,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -5983,7 +4829,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -5993,7 +4839,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -6003,7 +4849,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -6013,7 +4859,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -6023,7 +4869,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -6033,7 +4879,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -6043,7 +4889,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -6053,7 +4899,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -6063,7 +4909,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -6073,7 +4919,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -6083,7 +4929,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -6093,7 +4939,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -6103,7 +4949,7 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" s="52"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
@@ -6113,7 +4959,7 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="53"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
@@ -6129,7 +4975,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -6138,7 +4984,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -6147,7 +4993,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -6156,7 +5002,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -6165,17 +5011,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -6195,4 +5041,1139 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7295A98A-9DE5-4CC0-A28E-4AAE25FE895B}">
+  <sheetPr filterMode="1">
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="B1:F101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+    </row>
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+    </row>
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+    </row>
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+    </row>
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+    </row>
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+    </row>
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B55" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B56" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B57" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+    </row>
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+    </row>
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B64" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+    </row>
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+    </row>
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+    </row>
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+    </row>
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+    </row>
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+    </row>
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+    </row>
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+    </row>
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+    </row>
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+    </row>
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+    </row>
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B5:F75" xr:uid="{A099B508-44C7-48CD-924B-201E372CDC29}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Sprint 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D101" xr:uid="{F51E1D81-F30A-455D-8193-BBE5DE529FFA}">
+      <formula1>"Sprint 1,Sprint 2,Sprint 3,Sprint 4,"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E101" xr:uid="{0A8A13BB-479E-47FC-B198-FA503076D14C}">
+      <formula1>"Haute,Moyenne,Basse,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1F0310-2F9A-45FC-BF67-D89F89492E03}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5B8994-4681-4D77-AACD-1DB30B3622C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -27,22 +27,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="161">
   <si>
     <t>Planification globale</t>
   </si>
@@ -522,6 +517,9 @@
   </si>
   <si>
     <t>des pertes de connexions aléatoires</t>
+  </si>
+  <si>
+    <t>Telecharger et Installer Node.js</t>
   </si>
 </sst>
 </file>
@@ -979,14 +977,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1304,26 +1302,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:5" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1337,7 +1335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
         <v>153</v>
       </c>
@@ -1351,7 +1349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="18" t="s">
         <v>123</v>
       </c>
@@ -1365,7 +1363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="18" t="s">
         <v>124</v>
       </c>
@@ -1379,7 +1377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
         <v>125</v>
       </c>
@@ -1393,7 +1391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="18" t="s">
         <v>126</v>
       </c>
@@ -1407,7 +1405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
         <v>128</v>
       </c>
@@ -1421,7 +1419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
         <v>129</v>
       </c>
@@ -1435,7 +1433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="18" t="s">
         <v>130</v>
       </c>
@@ -1449,7 +1447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
         <v>157</v>
       </c>
@@ -1463,7 +1461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
         <v>133</v>
       </c>
@@ -1477,7 +1475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
         <v>134</v>
       </c>
@@ -1491,7 +1489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="18" t="s">
         <v>136</v>
       </c>
@@ -1505,7 +1503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="18" t="s">
         <v>142</v>
       </c>
@@ -1519,7 +1517,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" s="18" t="s">
         <v>131</v>
       </c>
@@ -1533,7 +1531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" s="18" t="s">
         <v>132</v>
       </c>
@@ -1547,7 +1545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" s="18" t="s">
         <v>137</v>
       </c>
@@ -1561,7 +1559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
         <v>138</v>
       </c>
@@ -1575,7 +1573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
         <v>139</v>
       </c>
@@ -1589,7 +1587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
         <v>141</v>
       </c>
@@ -1603,7 +1601,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
         <v>145</v>
       </c>
@@ -1617,7 +1615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
         <v>146</v>
       </c>
@@ -1631,7 +1629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
         <v>147</v>
       </c>
@@ -1645,7 +1643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B28" s="18" t="s">
         <v>140</v>
       </c>
@@ -1659,7 +1657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
         <v>143</v>
       </c>
@@ -1673,7 +1671,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
         <v>135</v>
       </c>
@@ -1687,7 +1685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="18" t="s">
         <v>144</v>
       </c>
@@ -1701,7 +1699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B32" s="18" t="s">
         <v>148</v>
       </c>
@@ -1715,7 +1713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
         <v>149</v>
       </c>
@@ -1729,7 +1727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
         <v>150</v>
       </c>
@@ -1743,7 +1741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="18" t="s">
         <v>151</v>
       </c>
@@ -1757,7 +1755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="18" t="s">
         <v>152</v>
       </c>
@@ -1771,7 +1769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="22" t="s">
         <v>127</v>
       </c>
@@ -1785,8 +1783,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D39" s="41" t="s">
         <v>158</v>
       </c>
@@ -1822,32 +1820,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1877,7 +1875,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1931,7 +1929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -1958,7 +1956,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -1980,7 +1978,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2007,7 +2005,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2040,7 +2038,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2077,7 +2075,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2114,7 +2112,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2146,7 +2144,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2174,7 +2172,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2201,15 +2199,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2225,23 +2223,24 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B3:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.1796875" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="3" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="7"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
@@ -2266,7 +2265,7 @@
       </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="7" t="s">
         <v>1</v>
       </c>
@@ -2301,7 +2300,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2324,7 +2323,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -2342,7 +2341,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -2360,7 +2359,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -2375,7 +2374,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36" t="s">
         <v>122</v>
       </c>
@@ -2390,22 +2389,24 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="C12" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="18"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="18" t="s">
-        <v>89</v>
+      <c r="G12" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
       </c>
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -2420,7 +2421,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -2435,7 +2436,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36" t="s">
         <v>29</v>
       </c>
@@ -2450,7 +2451,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
         <v>30</v>
       </c>
@@ -2465,7 +2466,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36" t="s">
         <v>92</v>
       </c>
@@ -2480,7 +2481,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
         <v>51</v>
       </c>
@@ -2495,7 +2496,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36" t="s">
         <v>90</v>
       </c>
@@ -2510,7 +2511,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="36" t="s">
         <v>74</v>
       </c>
@@ -2525,7 +2526,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="36" t="s">
         <v>80</v>
       </c>
@@ -2541,7 +2542,7 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36" t="s">
         <v>93</v>
       </c>
@@ -2557,7 +2558,7 @@
       </c>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36" t="s">
         <v>94</v>
       </c>
@@ -2573,7 +2574,7 @@
       </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36" t="s">
         <v>79</v>
       </c>
@@ -2589,7 +2590,7 @@
       </c>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
         <v>76</v>
       </c>
@@ -2605,7 +2606,7 @@
       </c>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36" t="s">
         <v>31</v>
       </c>
@@ -2621,7 +2622,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
         <v>44</v>
       </c>
@@ -2637,7 +2638,7 @@
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="36" t="s">
         <v>37</v>
       </c>
@@ -2653,7 +2654,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="36" t="s">
         <v>73</v>
       </c>
@@ -2669,7 +2670,7 @@
       </c>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
         <v>38</v>
       </c>
@@ -2685,7 +2686,7 @@
       </c>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="36" t="s">
         <v>39</v>
       </c>
@@ -2701,7 +2702,7 @@
       </c>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36" t="s">
         <v>42</v>
       </c>
@@ -2717,7 +2718,7 @@
       </c>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36" t="s">
         <v>43</v>
       </c>
@@ -2733,7 +2734,7 @@
       </c>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36" t="s">
         <v>61</v>
       </c>
@@ -2749,7 +2750,7 @@
       </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="37" t="s">
         <v>56</v>
       </c>
@@ -2779,27 +2780,27 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.21875" customWidth="1"/>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="19.77734375" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
+    <col min="1" max="1" width="2.1796875" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="19.81640625" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="19.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -2818,7 +2819,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -2853,7 +2854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="35"/>
       <c r="C5" s="12"/>
       <c r="D5" s="49"/>
@@ -2866,7 +2867,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="36"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -2875,7 +2876,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="36"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -2884,7 +2885,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -2893,7 +2894,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -2902,7 +2903,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -2911,7 +2912,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -2920,7 +2921,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -2929,7 +2930,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -2938,7 +2939,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -2947,7 +2948,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -2956,7 +2957,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -2965,7 +2966,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -2974,7 +2975,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -2983,7 +2984,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -2992,7 +2993,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="36"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3001,7 +3002,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="36"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3010,7 +3011,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3019,7 +3020,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3028,7 +3029,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3037,7 +3038,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="36"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3046,7 +3047,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3055,7 +3056,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="36"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3064,7 +3065,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="36"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3073,7 +3074,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="36"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3082,7 +3083,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="36"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3091,7 +3092,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="36"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3100,7 +3101,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36"/>
       <c r="C32" s="14"/>
       <c r="D32" s="50"/>
@@ -3109,7 +3110,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3118,7 +3119,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3127,7 +3128,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="36"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3136,7 +3137,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="36"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3145,7 +3146,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="36"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3154,7 +3155,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="36"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3163,7 +3164,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="36"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3172,7 +3173,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="37"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3187,11 +3188,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B40">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>COUNTIF(D5:L5,100%)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>COUNTIF(D5:L5,100%)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3205,21 +3206,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3233,151 +3234,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -3393,28 +3394,28 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3439,7 +3440,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3474,7 +3475,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="51"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
@@ -3487,7 +3488,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="52"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -3496,7 +3497,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -3505,7 +3506,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -3514,7 +3515,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -3523,7 +3524,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -3532,7 +3533,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -3541,7 +3542,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -3550,7 +3551,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -3559,7 +3560,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -3568,7 +3569,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -3577,7 +3578,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -3586,7 +3587,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3595,7 +3596,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3604,7 +3605,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3613,7 +3614,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3622,7 +3623,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3631,7 +3632,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3640,7 +3641,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3649,7 +3650,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3658,7 +3659,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3667,7 +3668,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3676,7 +3677,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3685,7 +3686,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3694,7 +3695,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3703,7 +3704,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3712,7 +3713,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3721,7 +3722,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -3730,7 +3731,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3739,7 +3740,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3748,7 +3749,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3757,7 +3758,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3766,7 +3767,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3775,7 +3776,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3784,7 +3785,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3793,7 +3794,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="53"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3826,18 +3827,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3861,7 +3862,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3905,7 +3906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3927,7 +3928,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3945,7 +3946,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -3963,7 +3964,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3981,7 +3982,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -3999,7 +4000,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -4017,7 +4018,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -4035,7 +4036,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -4053,7 +4054,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4071,7 +4072,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -4089,7 +4090,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4107,7 +4108,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4125,7 +4126,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4143,7 +4144,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4161,7 +4162,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4179,7 +4180,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4197,7 +4198,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4215,7 +4216,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4233,7 +4234,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4251,7 +4252,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4269,7 +4270,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4287,7 +4288,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4305,7 +4306,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4323,7 +4324,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4341,7 +4342,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4359,7 +4360,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4377,7 +4378,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4395,7 +4396,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4413,7 +4414,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4431,7 +4432,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4453,47 +4454,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4505,29 +4506,29 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4559,7 +4560,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4603,7 +4604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="51"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
@@ -4619,7 +4620,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -4629,7 +4630,7 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -4639,7 +4640,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -4649,7 +4650,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -4659,7 +4660,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -4669,7 +4670,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -4679,7 +4680,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -4689,7 +4690,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="50"/>
@@ -4699,7 +4700,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -4709,7 +4710,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -4719,7 +4720,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -4729,7 +4730,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -4739,7 +4740,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -4749,7 +4750,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -4759,7 +4760,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -4769,7 +4770,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -4779,7 +4780,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -4789,7 +4790,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -4799,7 +4800,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -4809,7 +4810,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -4819,7 +4820,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -4829,7 +4830,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -4839,7 +4840,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -4849,7 +4850,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -4859,7 +4860,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -4869,7 +4870,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -4879,7 +4880,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -4889,7 +4890,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -4899,7 +4900,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -4909,7 +4910,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -4919,7 +4920,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -4929,7 +4930,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -4939,7 +4940,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -4949,7 +4950,7 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B40" s="52"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
@@ -4959,7 +4960,7 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="53"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
@@ -4975,7 +4976,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -4984,7 +4985,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -4993,7 +4994,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -5002,7 +5003,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -5011,17 +5012,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -5049,28 +5050,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="93.1796875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5087,7 +5088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5100,7 +5101,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5113,7 +5114,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5126,7 +5127,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5139,7 +5140,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5152,7 +5153,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5165,7 +5166,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5178,7 +5179,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5191,7 +5192,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5204,7 +5205,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5217,7 +5218,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5230,7 +5231,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5243,7 +5244,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5256,7 +5257,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5269,7 +5270,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5282,7 +5283,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5295,7 +5296,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5308,7 +5309,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5321,7 +5322,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5334,7 +5335,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5347,7 +5348,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5360,7 +5361,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5373,7 +5374,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5386,7 +5387,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5399,7 +5400,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5412,7 +5413,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5425,7 +5426,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5438,7 +5439,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5451,7 +5452,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5464,7 +5465,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5477,7 +5478,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5490,7 +5491,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5503,7 +5504,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5516,7 +5517,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5529,7 +5530,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5542,7 +5543,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5555,7 +5556,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5568,7 +5569,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5581,7 +5582,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5594,7 +5595,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5607,7 +5608,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5620,7 +5621,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5633,7 +5634,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5646,7 +5647,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5659,7 +5660,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5672,7 +5673,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5685,7 +5686,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5698,7 +5699,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5711,7 +5712,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5724,7 +5725,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5737,7 +5738,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5750,7 +5751,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5763,7 +5764,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5776,7 +5777,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5789,7 +5790,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5802,7 +5803,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5815,7 +5816,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5828,7 +5829,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5841,7 +5842,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5854,7 +5855,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5865,7 +5866,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5876,7 +5877,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5887,7 +5888,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5898,7 +5899,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5909,7 +5910,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5920,7 +5921,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5931,7 +5932,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -5942,7 +5943,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -5953,7 +5954,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -5964,7 +5965,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -5975,182 +5976,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1F0310-2F9A-45FC-BF67-D89F89492E03}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB607E7-C505-4FCB-9ED9-8BCDDF6C2399}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -27,22 +27,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="162">
   <si>
     <t>Planification globale</t>
   </si>
@@ -522,6 +517,12 @@
   </si>
   <si>
     <t>des pertes de connexions aléatoires</t>
+  </si>
+  <si>
+    <t>Plus long que prévu, créé plusieurs autres classes nécessaires</t>
+  </si>
+  <si>
+    <t>Reste à créér la classe user et à mettre des choses dans la classe Player</t>
   </si>
 </sst>
 </file>
@@ -979,14 +980,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1304,26 +1305,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:5" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1337,7 +1338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
         <v>153</v>
       </c>
@@ -1351,7 +1352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="18" t="s">
         <v>123</v>
       </c>
@@ -1365,7 +1366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="18" t="s">
         <v>124</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
         <v>125</v>
       </c>
@@ -1393,7 +1394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="18" t="s">
         <v>126</v>
       </c>
@@ -1407,7 +1408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
         <v>128</v>
       </c>
@@ -1421,7 +1422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
         <v>129</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="18" t="s">
         <v>130</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
         <v>157</v>
       </c>
@@ -1463,7 +1464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
         <v>133</v>
       </c>
@@ -1477,7 +1478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
         <v>134</v>
       </c>
@@ -1491,7 +1492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="18" t="s">
         <v>136</v>
       </c>
@@ -1505,7 +1506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="18" t="s">
         <v>142</v>
       </c>
@@ -1519,7 +1520,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" s="18" t="s">
         <v>131</v>
       </c>
@@ -1533,7 +1534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" s="18" t="s">
         <v>132</v>
       </c>
@@ -1547,7 +1548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" s="18" t="s">
         <v>137</v>
       </c>
@@ -1561,7 +1562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
         <v>138</v>
       </c>
@@ -1575,7 +1576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
         <v>139</v>
       </c>
@@ -1589,7 +1590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
         <v>141</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
         <v>145</v>
       </c>
@@ -1617,7 +1618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
         <v>146</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
         <v>147</v>
       </c>
@@ -1645,7 +1646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B28" s="18" t="s">
         <v>140</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
         <v>143</v>
       </c>
@@ -1673,7 +1674,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
         <v>135</v>
       </c>
@@ -1687,7 +1688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="18" t="s">
         <v>144</v>
       </c>
@@ -1701,7 +1702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B32" s="18" t="s">
         <v>148</v>
       </c>
@@ -1715,7 +1716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
         <v>149</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
         <v>150</v>
       </c>
@@ -1743,7 +1744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="18" t="s">
         <v>151</v>
       </c>
@@ -1757,7 +1758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="18" t="s">
         <v>152</v>
       </c>
@@ -1771,7 +1772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="22" t="s">
         <v>127</v>
       </c>
@@ -1785,8 +1786,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D39" s="41" t="s">
         <v>158</v>
       </c>
@@ -1822,32 +1823,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1877,7 +1878,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1931,7 +1932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -1958,7 +1959,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -1980,7 +1981,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2007,7 +2008,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2040,7 +2041,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2077,7 +2078,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2114,7 +2115,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2146,7 +2147,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2174,7 +2175,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2201,15 +2202,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2225,23 +2226,24 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B3:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
+    <col min="9" max="9" width="52.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="3" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="7"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
@@ -2266,7 +2268,7 @@
       </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="7" t="s">
         <v>1</v>
       </c>
@@ -2301,7 +2303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2324,7 +2326,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -2342,7 +2344,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -2360,22 +2362,25 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>89</v>
+      <c r="D10" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="18"/>
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36" t="s">
         <v>122</v>
       </c>
@@ -2390,7 +2395,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -2405,7 +2410,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -2420,7 +2425,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -2435,7 +2440,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36" t="s">
         <v>29</v>
       </c>
@@ -2450,7 +2455,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
         <v>30</v>
       </c>
@@ -2465,7 +2470,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36" t="s">
         <v>92</v>
       </c>
@@ -2474,13 +2479,18 @@
       </c>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
-      <c r="G17" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="14"/>
+      <c r="G17" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>160</v>
+      </c>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
         <v>51</v>
       </c>
@@ -2489,13 +2499,16 @@
       </c>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="18" t="s">
-        <v>89</v>
+      <c r="G18" s="18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
       </c>
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36" t="s">
         <v>90</v>
       </c>
@@ -2510,22 +2523,24 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="36" t="s">
         <v>74</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="18"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="18" t="s">
-        <v>89</v>
+      <c r="G20" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
       </c>
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="36" t="s">
         <v>80</v>
       </c>
@@ -2534,14 +2549,19 @@
       </c>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
-      <c r="G21" s="18"/>
+      <c r="G21" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
       <c r="I21" s="14"/>
       <c r="J21" t="s">
         <v>89</v>
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36" t="s">
         <v>93</v>
       </c>
@@ -2557,7 +2577,7 @@
       </c>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36" t="s">
         <v>94</v>
       </c>
@@ -2573,7 +2593,7 @@
       </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36" t="s">
         <v>79</v>
       </c>
@@ -2582,14 +2602,21 @@
       </c>
       <c r="D24" s="18"/>
       <c r="F24" s="14"/>
-      <c r="G24" s="18"/>
-      <c r="I24" s="14"/>
+      <c r="G24" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H24">
+        <v>25</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>161</v>
+      </c>
       <c r="J24" t="s">
         <v>89</v>
       </c>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
         <v>76</v>
       </c>
@@ -2605,7 +2632,7 @@
       </c>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36" t="s">
         <v>31</v>
       </c>
@@ -2621,7 +2648,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
         <v>44</v>
       </c>
@@ -2637,7 +2664,7 @@
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="36" t="s">
         <v>37</v>
       </c>
@@ -2653,7 +2680,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="36" t="s">
         <v>73</v>
       </c>
@@ -2669,7 +2696,7 @@
       </c>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
         <v>38</v>
       </c>
@@ -2685,7 +2712,7 @@
       </c>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="36" t="s">
         <v>39</v>
       </c>
@@ -2701,7 +2728,7 @@
       </c>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36" t="s">
         <v>42</v>
       </c>
@@ -2717,7 +2744,7 @@
       </c>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36" t="s">
         <v>43</v>
       </c>
@@ -2733,7 +2760,7 @@
       </c>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36" t="s">
         <v>61</v>
       </c>
@@ -2749,7 +2776,7 @@
       </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="37" t="s">
         <v>56</v>
       </c>
@@ -2779,27 +2806,27 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.21875" customWidth="1"/>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="19.77734375" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
+    <col min="1" max="1" width="2.1796875" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="19.81640625" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="19.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -2818,7 +2845,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -2853,7 +2880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="35"/>
       <c r="C5" s="12"/>
       <c r="D5" s="49"/>
@@ -2866,7 +2893,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="36"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -2875,7 +2902,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="36"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -2884,7 +2911,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -2893,7 +2920,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -2902,7 +2929,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -2911,7 +2938,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -2920,7 +2947,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -2929,7 +2956,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -2938,7 +2965,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -2947,7 +2974,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -2956,7 +2983,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -2965,7 +2992,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -2974,7 +3001,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -2983,7 +3010,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -2992,7 +3019,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="36"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3001,7 +3028,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="36"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3010,7 +3037,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3019,7 +3046,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3028,7 +3055,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3037,7 +3064,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="36"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3046,7 +3073,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3055,7 +3082,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="36"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3064,7 +3091,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="36"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3073,7 +3100,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="36"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3082,7 +3109,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="36"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3091,7 +3118,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="36"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3100,7 +3127,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36"/>
       <c r="C32" s="14"/>
       <c r="D32" s="50"/>
@@ -3109,7 +3136,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3118,7 +3145,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3127,7 +3154,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="36"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3136,7 +3163,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="36"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3145,7 +3172,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="36"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3154,7 +3181,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="36"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3163,7 +3190,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="36"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3172,7 +3199,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="37"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3187,11 +3214,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B40">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>COUNTIF(D5:L5,100%)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>COUNTIF(D5:L5,100%)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3205,21 +3232,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3233,151 +3260,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -3393,28 +3420,28 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3439,7 +3466,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3474,7 +3501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="51"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
@@ -3487,7 +3514,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="52"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -3496,7 +3523,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -3505,7 +3532,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -3514,7 +3541,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -3523,7 +3550,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -3532,7 +3559,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -3541,7 +3568,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -3550,7 +3577,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -3559,7 +3586,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -3568,7 +3595,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -3577,7 +3604,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -3586,7 +3613,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3595,7 +3622,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3604,7 +3631,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3613,7 +3640,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3622,7 +3649,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3631,7 +3658,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3640,7 +3667,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3649,7 +3676,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3658,7 +3685,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3667,7 +3694,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3676,7 +3703,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3685,7 +3712,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3694,7 +3721,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3703,7 +3730,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3712,7 +3739,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3721,7 +3748,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -3730,7 +3757,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3739,7 +3766,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3748,7 +3775,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3757,7 +3784,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3766,7 +3793,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3775,7 +3802,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3784,7 +3811,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3793,7 +3820,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="53"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3826,18 +3853,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3861,7 +3888,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3905,7 +3932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3927,7 +3954,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3945,7 +3972,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -3963,7 +3990,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3981,7 +4008,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -3999,7 +4026,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -4017,7 +4044,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -4035,7 +4062,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -4053,7 +4080,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4071,7 +4098,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -4089,7 +4116,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4107,7 +4134,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4125,7 +4152,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4143,7 +4170,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4161,7 +4188,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4179,7 +4206,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4197,7 +4224,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4215,7 +4242,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4233,7 +4260,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4251,7 +4278,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4269,7 +4296,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4287,7 +4314,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4305,7 +4332,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4323,7 +4350,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4341,7 +4368,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4359,7 +4386,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4377,7 +4404,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4395,7 +4422,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4413,7 +4440,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4431,7 +4458,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4453,47 +4480,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4505,29 +4532,29 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4559,7 +4586,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4603,7 +4630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="51"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
@@ -4619,7 +4646,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -4629,7 +4656,7 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -4639,7 +4666,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -4649,7 +4676,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -4659,7 +4686,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -4669,7 +4696,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -4679,7 +4706,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -4689,7 +4716,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="50"/>
@@ -4699,7 +4726,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -4709,7 +4736,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -4719,7 +4746,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -4729,7 +4756,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -4739,7 +4766,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -4749,7 +4776,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -4759,7 +4786,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -4769,7 +4796,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -4779,7 +4806,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -4789,7 +4816,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -4799,7 +4826,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -4809,7 +4836,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -4819,7 +4846,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -4829,7 +4856,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -4839,7 +4866,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -4849,7 +4876,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -4859,7 +4886,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -4869,7 +4896,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -4879,7 +4906,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -4889,7 +4916,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -4899,7 +4926,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -4909,7 +4936,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -4919,7 +4946,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -4929,7 +4956,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -4939,7 +4966,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -4949,7 +4976,7 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B40" s="52"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
@@ -4959,7 +4986,7 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="53"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
@@ -4975,7 +5002,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -4984,7 +5011,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -4993,7 +5020,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -5002,7 +5029,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -5011,17 +5038,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -5049,28 +5076,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="93.1796875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5087,7 +5114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5100,7 +5127,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5113,7 +5140,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5126,7 +5153,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5139,7 +5166,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5152,7 +5179,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5165,7 +5192,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5178,7 +5205,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5191,7 +5218,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5204,7 +5231,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5217,7 +5244,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5230,7 +5257,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5243,7 +5270,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5256,7 +5283,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5269,7 +5296,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5282,7 +5309,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5295,7 +5322,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5308,7 +5335,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5321,7 +5348,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5334,7 +5361,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5347,7 +5374,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5360,7 +5387,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5373,7 +5400,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5386,7 +5413,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5399,7 +5426,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5412,7 +5439,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5425,7 +5452,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5438,7 +5465,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5451,7 +5478,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5464,7 +5491,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5477,7 +5504,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5490,7 +5517,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5503,7 +5530,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5516,7 +5543,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5529,7 +5556,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5542,7 +5569,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5555,7 +5582,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5568,7 +5595,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5581,7 +5608,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5594,7 +5621,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5607,7 +5634,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5620,7 +5647,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5633,7 +5660,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5646,7 +5673,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5659,7 +5686,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5672,7 +5699,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5685,7 +5712,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5698,7 +5725,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5711,7 +5738,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5724,7 +5751,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5737,7 +5764,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5750,7 +5777,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5763,7 +5790,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5776,7 +5803,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5789,7 +5816,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5802,7 +5829,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5815,7 +5842,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5828,7 +5855,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5841,7 +5868,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5854,7 +5881,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5865,7 +5892,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5876,7 +5903,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5887,7 +5914,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5898,7 +5925,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5909,7 +5936,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5920,7 +5947,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5931,7 +5958,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -5942,7 +5969,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -5953,7 +5980,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -5964,7 +5991,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -5975,182 +6002,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB607E7-C505-4FCB-9ED9-8BCDDF6C2399}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C95E976-A156-410F-8D3B-FFCC70E3A401}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -27,17 +27,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="166">
   <si>
     <t>Planification globale</t>
   </si>
@@ -523,6 +528,18 @@
   </si>
   <si>
     <t>Reste à créér la classe user et à mettre des choses dans la classe Player</t>
+  </si>
+  <si>
+    <t>Créer le routage vers les differentes pages: index,lobby,game</t>
+  </si>
+  <si>
+    <t>Créer la page main.jsx</t>
+  </si>
+  <si>
+    <t>Tests: acces pages web:frontend et backend du client</t>
+  </si>
+  <si>
+    <t>Créer IndexAction: signup, signin,signout</t>
   </si>
 </sst>
 </file>
@@ -873,7 +890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -944,6 +961,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1305,26 +1328,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="42.81640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:5" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1338,7 +1361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
         <v>153</v>
       </c>
@@ -1352,7 +1375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>123</v>
       </c>
@@ -1366,7 +1389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>124</v>
       </c>
@@ -1380,7 +1403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
         <v>125</v>
       </c>
@@ -1394,7 +1417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>126</v>
       </c>
@@ -1408,7 +1431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
         <v>128</v>
       </c>
@@ -1422,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>129</v>
       </c>
@@ -1436,7 +1459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>130</v>
       </c>
@@ -1450,7 +1473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="18" t="s">
         <v>157</v>
       </c>
@@ -1464,7 +1487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
         <v>133</v>
       </c>
@@ -1478,7 +1501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
         <v>134</v>
       </c>
@@ -1492,7 +1515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
         <v>136</v>
       </c>
@@ -1506,7 +1529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
         <v>142</v>
       </c>
@@ -1520,7 +1543,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
         <v>131</v>
       </c>
@@ -1534,7 +1557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
         <v>132</v>
       </c>
@@ -1548,7 +1571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="18" t="s">
         <v>137</v>
       </c>
@@ -1562,7 +1585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
         <v>138</v>
       </c>
@@ -1576,7 +1599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
         <v>139</v>
       </c>
@@ -1590,7 +1613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
         <v>141</v>
       </c>
@@ -1604,7 +1627,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
         <v>145</v>
       </c>
@@ -1618,7 +1641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
         <v>146</v>
       </c>
@@ -1632,7 +1655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>147</v>
       </c>
@@ -1646,7 +1669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" s="18" t="s">
         <v>140</v>
       </c>
@@ -1660,7 +1683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
         <v>143</v>
       </c>
@@ -1674,7 +1697,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" s="18" t="s">
         <v>135</v>
       </c>
@@ -1688,7 +1711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
         <v>144</v>
       </c>
@@ -1702,7 +1725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" s="18" t="s">
         <v>148</v>
       </c>
@@ -1716,7 +1739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" s="18" t="s">
         <v>149</v>
       </c>
@@ -1730,7 +1753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" s="18" t="s">
         <v>150</v>
       </c>
@@ -1744,7 +1767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="18" t="s">
         <v>151</v>
       </c>
@@ -1758,7 +1781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="18" t="s">
         <v>152</v>
       </c>
@@ -1772,7 +1795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="22" t="s">
         <v>127</v>
       </c>
@@ -1786,8 +1809,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D39" s="41" t="s">
         <v>158</v>
       </c>
@@ -1823,32 +1846,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
-    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1878,7 +1901,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1932,7 +1955,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -1959,7 +1982,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -1981,7 +2004,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2008,7 +2031,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2064,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2078,7 +2101,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2115,7 +2138,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2147,7 +2170,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2175,7 +2198,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2202,15 +2225,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2225,25 +2248,26 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="B3:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B3:L37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" customWidth="1"/>
-    <col min="9" max="9" width="52.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.21875" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="43.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="46" x14ac:dyDescent="1">
+    <row r="3" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B5" s="7"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
@@ -2268,7 +2292,7 @@
       </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="7" t="s">
         <v>1</v>
       </c>
@@ -2303,7 +2327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2316,7 +2340,7 @@
       <c r="E7" s="11">
         <v>100</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="54" t="s">
         <v>159</v>
       </c>
       <c r="G7" s="21"/>
@@ -2326,7 +2350,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -2344,7 +2368,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -2362,7 +2386,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -2380,7 +2404,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="36" t="s">
         <v>122</v>
       </c>
@@ -2395,7 +2419,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -2404,13 +2428,16 @@
       </c>
       <c r="D12" s="18"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="18" t="s">
-        <v>89</v>
+      <c r="G12" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
       </c>
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -2419,13 +2446,16 @@
       </c>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
-      <c r="G13" s="18" t="s">
-        <v>89</v>
+      <c r="G13" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
       </c>
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -2434,13 +2464,16 @@
       </c>
       <c r="D14" s="18"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="18" t="s">
-        <v>89</v>
+      <c r="G14" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
       </c>
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="36" t="s">
         <v>29</v>
       </c>
@@ -2449,13 +2482,16 @@
       </c>
       <c r="D15" s="18"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="18" t="s">
-        <v>89</v>
+      <c r="G15" s="18">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
       </c>
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="36" t="s">
         <v>30</v>
       </c>
@@ -2464,43 +2500,44 @@
       </c>
       <c r="D16" s="18"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="18" t="s">
-        <v>89</v>
+      <c r="G16" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
       </c>
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="36" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
       <c r="G17" s="18">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
-      <c r="I17" s="14" t="s">
-        <v>160</v>
-      </c>
+      <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
       <c r="G18" s="18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -2508,41 +2545,47 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="36" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
-      <c r="G19" s="18" t="s">
-        <v>89</v>
+      <c r="G19" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
       </c>
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="36" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>107</v>
       </c>
+      <c r="D20" s="18"/>
       <c r="F20" s="14"/>
       <c r="G20" s="18">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
-      <c r="I20" s="14"/>
+      <c r="I20" s="55" t="s">
+        <v>160</v>
+      </c>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="36" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>107</v>
@@ -2550,52 +2593,49 @@
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
       <c r="G21" s="18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21" s="14"/>
-      <c r="J21" t="s">
-        <v>89</v>
-      </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>107</v>
       </c>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="18"/>
+      <c r="G22" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="I22" s="14"/>
-      <c r="J22" t="s">
-        <v>89</v>
-      </c>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="36" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="18"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="18"/>
+      <c r="G23" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
       <c r="I23" s="14"/>
-      <c r="J23" t="s">
-        <v>89</v>
-      </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="36" t="s">
         <v>107</v>
@@ -2606,19 +2646,14 @@
         <v>0.5</v>
       </c>
       <c r="H24">
-        <v>25</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="J24" t="s">
-        <v>89</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="18" t="s">
-        <v>76</v>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="36" t="s">
+        <v>93</v>
       </c>
       <c r="C25" s="36" t="s">
         <v>107</v>
@@ -2627,62 +2662,57 @@
       <c r="F25" s="14"/>
       <c r="G25" s="18"/>
       <c r="I25" s="14"/>
-      <c r="J25" t="s">
-        <v>89</v>
-      </c>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="36" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
       <c r="G26" s="18"/>
       <c r="I26" s="14"/>
-      <c r="J26" t="s">
-        <v>89</v>
-      </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="18" t="s">
-        <v>44</v>
+    <row r="27" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="36" t="s">
+        <v>79</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="18"/>
-      <c r="I27" s="14"/>
-      <c r="J27" t="s">
-        <v>89</v>
+      <c r="G27" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27" s="55" t="s">
+        <v>161</v>
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="36" t="s">
-        <v>37</v>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="18" t="s">
+        <v>76</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28" s="18"/>
       <c r="F28" s="14"/>
       <c r="G28" s="18"/>
       <c r="I28" s="14"/>
-      <c r="J28" t="s">
-        <v>89</v>
-      </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="36" t="s">
-        <v>73</v>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>106</v>
@@ -2691,14 +2721,11 @@
       <c r="F29" s="14"/>
       <c r="G29" s="18"/>
       <c r="I29" s="14"/>
-      <c r="J29" t="s">
-        <v>89</v>
-      </c>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="36" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>106</v>
@@ -2707,14 +2734,11 @@
       <c r="F30" s="14"/>
       <c r="G30" s="18"/>
       <c r="I30" s="14"/>
-      <c r="J30" t="s">
-        <v>89</v>
-      </c>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="36" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>106</v>
@@ -2723,14 +2747,11 @@
       <c r="F31" s="14"/>
       <c r="G31" s="18"/>
       <c r="I31" s="14"/>
-      <c r="J31" t="s">
-        <v>89</v>
-      </c>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="36" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>106</v>
@@ -2739,14 +2760,11 @@
       <c r="F32" s="14"/>
       <c r="G32" s="18"/>
       <c r="I32" s="14"/>
-      <c r="J32" t="s">
-        <v>89</v>
-      </c>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="36" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>106</v>
@@ -2755,14 +2773,11 @@
       <c r="F33" s="14"/>
       <c r="G33" s="18"/>
       <c r="I33" s="14"/>
-      <c r="J33" t="s">
-        <v>89</v>
-      </c>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="36" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>106</v>
@@ -2771,29 +2786,50 @@
       <c r="F34" s="14"/>
       <c r="G34" s="18"/>
       <c r="I34" s="14"/>
-      <c r="J34" t="s">
-        <v>89</v>
-      </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="37" t="s">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="18"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="18"/>
+      <c r="I35" s="14"/>
+      <c r="L35" s="14"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="18"/>
+      <c r="I36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C37" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="17"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2806,27 +2842,27 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.1796875" customWidth="1"/>
-    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.54296875" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" customWidth="1"/>
-    <col min="9" max="9" width="19.81640625" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="19.453125" customWidth="1"/>
+    <col min="1" max="1" width="2.21875" customWidth="1"/>
+    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" customWidth="1"/>
+    <col min="9" max="9" width="19.77734375" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -2845,7 +2881,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -2880,7 +2916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="35"/>
       <c r="C5" s="12"/>
       <c r="D5" s="49"/>
@@ -2893,7 +2929,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="36"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -2902,7 +2938,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="36"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -2911,7 +2947,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="36"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -2920,7 +2956,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -2929,7 +2965,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="36"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -2938,7 +2974,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="36"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -2947,7 +2983,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="36"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -2956,7 +2992,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="36"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -2965,7 +3001,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="36"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -2974,7 +3010,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="36"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -2983,7 +3019,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="36"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -2992,7 +3028,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="36"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3001,7 +3037,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="36"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3010,7 +3046,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="36"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3019,7 +3055,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="36"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3028,7 +3064,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="36"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3037,7 +3073,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="36"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3046,7 +3082,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="36"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3055,7 +3091,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="36"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3064,7 +3100,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="36"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3073,7 +3109,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="36"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3082,7 +3118,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="36"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3091,7 +3127,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="36"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3100,7 +3136,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="36"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3109,7 +3145,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="36"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3118,7 +3154,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="36"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3127,7 +3163,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="36"/>
       <c r="C32" s="14"/>
       <c r="D32" s="50"/>
@@ -3136,7 +3172,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="36"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3145,7 +3181,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="36"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3154,7 +3190,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="36"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3163,7 +3199,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="36"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3172,7 +3208,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="36"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3181,7 +3217,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="36"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3190,7 +3226,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="36"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3199,7 +3235,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="37"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3232,21 +3268,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="70.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" customWidth="1"/>
-    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3260,151 +3296,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -3420,28 +3456,28 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="21.1796875" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3466,7 +3502,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3501,7 +3537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="51"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
@@ -3514,7 +3550,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="52"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -3523,7 +3559,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -3532,7 +3568,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -3541,7 +3577,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -3550,7 +3586,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -3559,7 +3595,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -3568,7 +3604,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -3577,7 +3613,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -3586,7 +3622,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -3595,7 +3631,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -3604,7 +3640,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -3613,7 +3649,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3622,7 +3658,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3631,7 +3667,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3640,7 +3676,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3649,7 +3685,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3658,7 +3694,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3667,7 +3703,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3676,7 +3712,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3685,7 +3721,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3694,7 +3730,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3703,7 +3739,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3712,7 +3748,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3721,7 +3757,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3730,7 +3766,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3739,7 +3775,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3748,7 +3784,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -3757,7 +3793,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3766,7 +3802,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3775,7 +3811,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3784,7 +3820,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3793,7 +3829,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3802,7 +3838,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3811,7 +3847,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3820,7 +3856,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="53"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3853,18 +3889,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3888,7 +3924,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3932,7 +3968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3954,7 +3990,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3972,7 +4008,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -3990,7 +4026,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -4008,7 +4044,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -4026,7 +4062,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -4044,7 +4080,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -4062,7 +4098,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -4080,7 +4116,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4098,7 +4134,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -4116,7 +4152,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4134,7 +4170,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4152,7 +4188,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4170,7 +4206,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4188,7 +4224,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4206,7 +4242,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4224,7 +4260,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4242,7 +4278,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4260,7 +4296,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4278,7 +4314,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4296,7 +4332,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4314,7 +4350,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4332,7 +4368,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4350,7 +4386,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4368,7 +4404,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4386,7 +4422,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4404,7 +4440,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4422,7 +4458,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4440,7 +4476,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4458,7 +4494,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4480,47 +4516,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4532,29 +4568,29 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="51.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4586,7 +4622,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4630,7 +4666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="51"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
@@ -4646,7 +4682,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="52"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -4656,7 +4692,7 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="52"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -4666,7 +4702,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="52"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -4676,7 +4712,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -4686,7 +4722,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="52"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -4696,7 +4732,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="52"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -4706,7 +4742,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -4716,7 +4752,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="14"/>
       <c r="D14" s="50"/>
@@ -4726,7 +4762,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="52"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -4736,7 +4772,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="52"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -4746,7 +4782,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="52"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -4756,7 +4792,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="52"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -4766,7 +4802,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="52"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -4776,7 +4812,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="52"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -4786,7 +4822,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="52"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -4796,7 +4832,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="52"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -4806,7 +4842,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="52"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -4816,7 +4852,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="52"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -4826,7 +4862,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="52"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -4836,7 +4872,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="52"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -4846,7 +4882,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="52"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -4856,7 +4892,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="52"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -4866,7 +4902,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="52"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -4876,7 +4912,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -4886,7 +4922,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="52"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -4896,7 +4932,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="52"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -4906,7 +4942,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="52"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -4916,7 +4952,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -4926,7 +4962,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -4936,7 +4972,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -4946,7 +4982,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="52"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -4956,7 +4992,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" s="52"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -4966,7 +5002,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" s="52"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -4976,7 +5012,7 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" s="52"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
@@ -4986,7 +5022,7 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="53"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
@@ -5002,7 +5038,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -5011,7 +5047,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -5020,7 +5056,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -5029,7 +5065,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -5038,17 +5074,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -5076,28 +5112,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="93.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="2" max="2" width="93.21875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="42.81640625" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5114,7 +5150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5127,7 +5163,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5140,7 +5176,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5153,7 +5189,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5166,7 +5202,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5179,7 +5215,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5192,7 +5228,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5205,7 +5241,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5218,7 +5254,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5231,7 +5267,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5244,7 +5280,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5257,7 +5293,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5270,7 +5306,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5283,7 +5319,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5296,7 +5332,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5309,7 +5345,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5322,7 +5358,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5335,7 +5371,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5348,7 +5384,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5361,7 +5397,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5374,7 +5410,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5387,7 +5423,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5400,7 +5436,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5413,7 +5449,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5426,7 +5462,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5439,7 +5475,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5452,7 +5488,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5465,7 +5501,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5478,7 +5514,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5491,7 +5527,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5504,7 +5540,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5517,7 +5553,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5530,7 +5566,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5543,7 +5579,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5556,7 +5592,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5569,7 +5605,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5582,7 +5618,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5595,7 +5631,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5608,7 +5644,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5621,7 +5657,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5634,7 +5670,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5647,7 +5683,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5660,7 +5696,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5673,7 +5709,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5686,7 +5722,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5699,7 +5735,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5712,7 +5748,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5725,7 +5761,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5738,7 +5774,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5751,7 +5787,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5764,7 +5800,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5777,7 +5813,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5790,7 +5826,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5803,7 +5839,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5816,7 +5852,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5829,7 +5865,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5842,7 +5878,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5855,7 +5891,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5868,7 +5904,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5881,7 +5917,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5892,7 +5928,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5903,7 +5939,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5914,7 +5950,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5925,7 +5961,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5936,7 +5972,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5947,7 +5983,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5958,7 +5994,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -5969,7 +6005,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -5980,7 +6016,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -5991,7 +6027,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -6002,182 +6038,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,48 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C95E976-A156-410F-8D3B-FFCC70E3A401}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86B1876-8C49-4207-9813-D509DE7E0027}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17730" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Planif Sprint 2" sheetId="8" r:id="rId3"/>
-    <sheet name="Sprint 2" sheetId="3" r:id="rId4"/>
-    <sheet name="Mi-mandat" sheetId="7" r:id="rId5"/>
-    <sheet name="Sprint 3" sheetId="4" r:id="rId6"/>
-    <sheet name="Planif Sprint 3" sheetId="9" r:id="rId7"/>
-    <sheet name="Sprint 4" sheetId="5" r:id="rId8"/>
-    <sheet name="Planification trop détaillée" sheetId="11" r:id="rId9"/>
+    <sheet name=" Sprint 2" sheetId="8" r:id="rId3"/>
+    <sheet name="Mi-mandat" sheetId="7" r:id="rId4"/>
+    <sheet name="Sprint 3" sheetId="4" r:id="rId5"/>
+    <sheet name="Planif Sprint 3" sheetId="9" r:id="rId6"/>
+    <sheet name="Sprint 4" sheetId="5" r:id="rId7"/>
+    <sheet name="Planification trop détaillée" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Sprint 2'!$B$5:$L$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="167">
   <si>
     <t>Planification globale</t>
   </si>
@@ -410,9 +405,6 @@
     <t>Gérer les droits administrateurs</t>
   </si>
   <si>
-    <t>Communication entre le Serveur et le Client (envois/réceptions)</t>
-  </si>
-  <si>
     <t>Mise en place de l’infrastructure serveur et base de données</t>
   </si>
   <si>
@@ -540,49 +532,66 @@
   </si>
   <si>
     <t>Créer IndexAction: signup, signin,signout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication entre le Serveur et le Client (envois/réceptions): test  simple </t>
+  </si>
+  <si>
+    <t>Créer le composant : MainLayout : 
+navbar conditionnelle (visible si connecté)
+, fond d'écran dynamique,
+ conteneur principal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="36"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="24"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,18 +600,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FF000000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FFE2EFD9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6DCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -612,10 +633,10 @@
     </border>
     <border>
       <left style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -624,7 +645,7 @@
     <border>
       <left/>
       <right style="thick">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -632,7 +653,7 @@
     </border>
     <border>
       <left style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
@@ -641,13 +662,13 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -656,7 +677,7 @@
       <left/>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -664,20 +685,20 @@
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -686,7 +707,7 @@
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -694,14 +715,14 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -710,24 +731,24 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
@@ -736,45 +757,45 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -782,107 +803,189 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thick">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -890,7 +993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -956,7 +1059,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
@@ -967,11 +1069,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="5" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -1003,19 +1147,44 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFCFDCF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFFFF"/>
+      <color rgb="FFFCFDCF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1324,30 +1493,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A98864-B157-464B-9C9C-D10C2E7AC6B8}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1361,458 +1530,458 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E6" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E8" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E9" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E10" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E12" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E13" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E14" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E15" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E16" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E17" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E18" s="14">
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C19" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E19" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E20" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E21" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E22" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E23" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C24" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E24" s="14">
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C26" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E27" s="14">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E29" s="14">
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E30" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E32" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C37" s="37" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D39" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E39" s="42">
         <f>SUM(E6:E37)</f>
@@ -1820,18 +1989,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:E37" xr:uid="{355B5BC9-E127-44A4-BBE6-CA2E735F8DE3}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Sprint 2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D20 D21:D37" xr:uid="{C1E49912-FB61-4F2F-8F8F-588FF6944C57}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D20 D21:D37" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Haute,Moyenne,Basse,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C20 C21:C37" xr:uid="{A1B83402-03F9-4A0F-BE40-AAB54D35ECC4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C20 C21:C37" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sprint 1,Sprint 2,Sprint 3,Sprint 4,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1846,32 +2008,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1901,7 +2063,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1955,7 +2117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -1982,7 +2144,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2004,7 +2166,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2031,7 +2193,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2064,7 +2226,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2101,7 +2263,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2138,7 +2300,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2170,7 +2332,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2198,7 +2360,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2225,15 +2387,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2248,1013 +2410,677 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="B3:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:L37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.21875" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" customWidth="1"/>
-    <col min="9" max="9" width="43.6640625" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.26953125" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" customWidth="1"/>
+    <col min="11" max="11" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
+      <c r="B3" s="61" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="7"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+      <c r="B5" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="58">
         <v>46083</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="48">
+      <c r="H5" s="58">
         <v>46090</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="58">
         <v>46104</v>
       </c>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="L5" s="68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="65"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="F6" s="69"/>
+      <c r="G6" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="69"/>
+      <c r="J6" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="69"/>
+    </row>
+    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="33">
         <v>3.5</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="55">
         <v>100</v>
       </c>
-      <c r="F7" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="11"/>
+      <c r="F7" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="33"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="12"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="31">
         <v>1.5</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="40">
         <v>100</v>
       </c>
       <c r="F8" s="14"/>
-      <c r="G8" s="18"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="31">
         <v>0.1</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="40">
         <v>100</v>
       </c>
       <c r="F9" s="14"/>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="31">
         <v>0.5</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="40">
         <v>100</v>
       </c>
       <c r="F10" s="14"/>
-      <c r="G10" s="18"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>89</v>
+      <c r="D11" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="40">
+        <v>100</v>
       </c>
       <c r="F11" s="14"/>
-      <c r="G11" s="18"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="40"/>
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="18"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="18">
+      <c r="G12" s="31">
         <v>0.5</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="40">
         <v>100</v>
       </c>
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="18"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="40"/>
       <c r="F13" s="14"/>
-      <c r="G13" s="18">
+      <c r="G13" s="31">
         <v>0.15</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="40">
         <v>100</v>
       </c>
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="18"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="18">
+      <c r="G14" s="31">
         <v>0.15</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="40">
         <v>100</v>
       </c>
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="18"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="18">
-        <v>1</v>
-      </c>
-      <c r="H15">
+      <c r="G15" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="40">
         <v>100</v>
       </c>
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="18"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="40"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="H16">
+      <c r="G16" s="31">
+        <v>1</v>
+      </c>
+      <c r="H16" s="40">
         <v>100</v>
       </c>
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36" t="s">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="C17" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="18"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="14"/>
-      <c r="G17" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="40">
         <v>100</v>
       </c>
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="18"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="H18">
+      <c r="G18" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="40">
         <v>100</v>
       </c>
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C19" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="18"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="40"/>
       <c r="F19" s="14"/>
-      <c r="G19" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="H19">
+      <c r="G19" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="40">
         <v>100</v>
       </c>
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="36" t="s">
+    <row r="20" spans="2:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="B20" s="70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="31"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="31">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="40">
+        <v>100</v>
+      </c>
+      <c r="I20" s="14"/>
+      <c r="L20" s="14"/>
+    </row>
+    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="36" t="s">
         <v>92</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="18"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="H20">
-        <v>100</v>
-      </c>
-      <c r="I20" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="L20" s="14"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="36" t="s">
-        <v>51</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="18"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="40"/>
       <c r="F21" s="14"/>
-      <c r="G21" s="18">
-        <v>1</v>
-      </c>
-      <c r="H21">
+      <c r="G21" s="31">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="40">
         <v>100</v>
       </c>
-      <c r="I21" s="14"/>
+      <c r="I21" s="54" t="s">
+        <v>159</v>
+      </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="18"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="18" t="s">
-        <v>89</v>
+      <c r="G22" s="31">
+        <v>1</v>
+      </c>
+      <c r="H22" s="40">
+        <v>100</v>
       </c>
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>107</v>
       </c>
+      <c r="D23" s="31"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="H23">
-        <v>100</v>
-      </c>
+      <c r="G23" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="40"/>
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C24" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="18"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="14"/>
-      <c r="G24" s="18">
+      <c r="G24" s="31">
         <v>0.5</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="40">
         <v>100</v>
       </c>
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="36" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C25" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="18"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="40"/>
       <c r="F25" s="14"/>
-      <c r="G25" s="18"/>
+      <c r="G25" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="40">
+        <v>100</v>
+      </c>
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="18"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="18"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="40"/>
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="36" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="18"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="40"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="H27">
-        <v>25</v>
-      </c>
-      <c r="I27" s="55" t="s">
-        <v>161</v>
-      </c>
+      <c r="G27" s="31"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
-        <v>76</v>
+    <row r="28" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B28" s="36" t="s">
+        <v>79</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="18"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="40"/>
       <c r="F28" s="14"/>
-      <c r="G28" s="18"/>
-      <c r="I28" s="14"/>
+      <c r="G28" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="40">
+        <v>25</v>
+      </c>
+      <c r="I28" s="54" t="s">
+        <v>160</v>
+      </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="18"/>
+        <v>107</v>
+      </c>
+      <c r="D29" s="31"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="14"/>
-      <c r="G29" s="18"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="40"/>
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="18"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="18"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="40"/>
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="36" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="18"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="40"/>
       <c r="F31" s="14"/>
-      <c r="G31" s="18"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="40"/>
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="18"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="14"/>
-      <c r="G32" s="18"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="40"/>
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="18"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="40"/>
       <c r="F33" s="14"/>
-      <c r="G33" s="18"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="40"/>
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="18"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="40"/>
       <c r="F34" s="14"/>
-      <c r="G34" s="18"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="40"/>
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="36" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="18"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="14"/>
-      <c r="G35" s="18"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="40"/>
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="36" t="s">
         <v>61</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D36" s="18"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="40"/>
       <c r="F36" s="14"/>
-      <c r="G36" s="18"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="40"/>
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="37" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="16"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="56"/>
       <c r="F37" s="17"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="16"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="56"/>
       <c r="I37" s="17"/>
       <c r="J37" s="16"/>
       <c r="K37" s="16"/>
       <c r="L37" s="17"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31117888-BBE7-4BD8-9871-AB22BAD895CD}">
-  <sheetPr>
-    <tabColor theme="7"/>
-  </sheetPr>
-  <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="2.21875" customWidth="1"/>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="19.77734375" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B3" s="7"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="35"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="36"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="18"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="18"/>
-      <c r="I6" s="14"/>
-      <c r="L6" s="14"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="36"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="18"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="18"/>
-      <c r="I7" s="14"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="36"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="18"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="18"/>
-      <c r="I8" s="14"/>
-      <c r="L8" s="14"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="36"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="18"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="18"/>
-      <c r="I9" s="14"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="36"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="18"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="14"/>
-      <c r="L10" s="14"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="36"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="18"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="18"/>
-      <c r="I11" s="14"/>
-      <c r="L11" s="14"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="36"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="18"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="18"/>
-      <c r="I12" s="14"/>
-      <c r="L12" s="14"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="36"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="18"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="18"/>
-      <c r="I13" s="14"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="36"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="18"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="18"/>
-      <c r="I14" s="14"/>
-      <c r="L14" s="14"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="36"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="18"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="14"/>
-      <c r="L15" s="14"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="36"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="18"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="18"/>
-      <c r="I16" s="14"/>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="36"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="18"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="18"/>
-      <c r="I17" s="14"/>
-      <c r="L17" s="14"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="36"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="18"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="18"/>
-      <c r="I18" s="14"/>
-      <c r="L18" s="14"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="36"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="18"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="18"/>
-      <c r="I19" s="14"/>
-      <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="36"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="18"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="18"/>
-      <c r="I20" s="14"/>
-      <c r="L20" s="14"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="36"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="18"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="18"/>
-      <c r="I21" s="14"/>
-      <c r="L21" s="14"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="36"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="18"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="18"/>
-      <c r="I22" s="14"/>
-      <c r="L22" s="14"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="36"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="18"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="18"/>
-      <c r="I23" s="14"/>
-      <c r="L23" s="14"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="36"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="18"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="18"/>
-      <c r="I24" s="14"/>
-      <c r="L24" s="14"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="36"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="18"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="18"/>
-      <c r="I25" s="14"/>
-      <c r="L25" s="14"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="36"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="18"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="18"/>
-      <c r="I26" s="14"/>
-      <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="36"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="18"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="18"/>
-      <c r="I27" s="14"/>
-      <c r="L27" s="14"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="36"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="18"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="18"/>
-      <c r="I28" s="14"/>
-      <c r="L28" s="14"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B29" s="36"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="18"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="18"/>
-      <c r="I29" s="14"/>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B30" s="36"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="18"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="18"/>
-      <c r="I30" s="14"/>
-      <c r="L30" s="14"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B31" s="36"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="18"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="18"/>
-      <c r="I31" s="14"/>
-      <c r="L31" s="14"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="36"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="50"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="18"/>
-      <c r="I32" s="14"/>
-      <c r="L32" s="14"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B33" s="36"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="18"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="18"/>
-      <c r="I33" s="14"/>
-      <c r="L33" s="14"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B34" s="36"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="18"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="18"/>
-      <c r="I34" s="14"/>
-      <c r="L34" s="14"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B35" s="36"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="18"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="18"/>
-      <c r="I35" s="14"/>
-      <c r="L35" s="14"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B36" s="36"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="18"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="18"/>
-      <c r="I36" s="14"/>
-      <c r="L36" s="14"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B37" s="36"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="18"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="18"/>
-      <c r="I37" s="14"/>
-      <c r="L37" s="14"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B38" s="36"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="18"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="18"/>
-      <c r="I38" s="14"/>
-      <c r="L38" s="14"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B39" s="36"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="18"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="18"/>
-      <c r="I39" s="14"/>
-      <c r="L39" s="14"/>
-    </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="37"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B5:B40">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>COUNTIF(D5:L5,100%)=0</formula>
+  <autoFilter ref="B5:L6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <mergeCells count="6">
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="L5:L6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="expression" dxfId="7" priority="6">
+      <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>$C1="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>$C1="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$C1="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3262,27 +3088,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE02E41-CCB4-4A52-8A11-897838372758}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3296,151 +3122,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -3450,34 +3276,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A181AE-6DCE-4F2E-9BC3-78C1EB9A33C7}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3502,7 +3328,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3537,8 +3363,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="51"/>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="50"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
       <c r="E5" s="11"/>
@@ -3550,8 +3376,8 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="52"/>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B6" s="51"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
       <c r="F6" s="14"/>
@@ -3559,8 +3385,8 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="52"/>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
       <c r="F7" s="14"/>
@@ -3568,8 +3394,8 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="52"/>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
       <c r="F8" s="14"/>
@@ -3577,8 +3403,8 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="52"/>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
       <c r="F9" s="14"/>
@@ -3586,8 +3412,8 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="52"/>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
       <c r="F10" s="14"/>
@@ -3595,8 +3421,8 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="52"/>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
       <c r="F11" s="14"/>
@@ -3604,8 +3430,8 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
       <c r="F12" s="14"/>
@@ -3613,8 +3439,8 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
@@ -3622,8 +3448,8 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="52"/>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B14" s="51"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
       <c r="F14" s="14"/>
@@ -3631,8 +3457,8 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="52"/>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
       <c r="F15" s="14"/>
@@ -3640,8 +3466,8 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="52"/>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
       <c r="F16" s="14"/>
@@ -3649,8 +3475,8 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
@@ -3658,8 +3484,8 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="52"/>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
@@ -3667,8 +3493,8 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="52"/>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
@@ -3676,8 +3502,8 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
       <c r="F20" s="14"/>
@@ -3685,8 +3511,8 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
@@ -3694,8 +3520,8 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
@@ -3703,8 +3529,8 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="52"/>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
       <c r="F23" s="14"/>
@@ -3712,8 +3538,8 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="52"/>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
       <c r="F24" s="14"/>
@@ -3721,8 +3547,8 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
       <c r="F25" s="14"/>
@@ -3730,8 +3556,8 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="52"/>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
@@ -3739,8 +3565,8 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
@@ -3748,8 +3574,8 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
       <c r="F28" s="14"/>
@@ -3757,8 +3583,8 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
       <c r="F29" s="14"/>
@@ -3766,8 +3592,8 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B30" s="52"/>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
       <c r="F30" s="14"/>
@@ -3775,8 +3601,8 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B31" s="52"/>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
       <c r="F31" s="14"/>
@@ -3784,8 +3610,8 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="52"/>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
       <c r="F32" s="14"/>
@@ -3793,8 +3619,8 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
       <c r="F33" s="14"/>
@@ -3802,8 +3628,8 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
       <c r="F34" s="14"/>
@@ -3811,8 +3637,8 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B35" s="52"/>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
       <c r="F35" s="14"/>
@@ -3820,8 +3646,8 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
       <c r="F36" s="14"/>
@@ -3829,8 +3655,8 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B37" s="52"/>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
       <c r="F37" s="14"/>
@@ -3838,8 +3664,8 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B38" s="52"/>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
       <c r="F38" s="14"/>
@@ -3847,8 +3673,8 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B39" s="52"/>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
       <c r="F39" s="14"/>
@@ -3856,8 +3682,8 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="53"/>
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="52"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
       <c r="E40" s="16"/>
@@ -3883,24 +3709,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EA87E6-A735-40DF-9804-F8FF12E4BB41}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3924,7 +3750,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3968,7 +3794,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3990,7 +3816,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -4008,7 +3834,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -4026,7 +3852,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -4044,7 +3870,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -4062,7 +3888,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -4080,7 +3906,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -4098,7 +3924,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -4116,7 +3942,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4134,7 +3960,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -4152,7 +3978,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4170,7 +3996,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4188,7 +4014,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4206,7 +4032,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4224,7 +4050,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4242,7 +4068,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4260,7 +4086,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4278,7 +4104,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4296,7 +4122,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4314,7 +4140,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4332,7 +4158,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4350,7 +4176,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4368,7 +4194,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4386,7 +4212,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4404,7 +4230,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4422,7 +4248,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4440,7 +4266,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4458,7 +4284,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4476,7 +4302,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4494,7 +4320,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4516,81 +4342,81 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DECEB1-A674-4E9A-9A60-FE266B1759EE}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4622,7 +4448,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4666,8 +4492,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="51"/>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="50"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
       <c r="E6" s="11"/>
@@ -4682,8 +4508,8 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="52"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
       <c r="F7" s="14"/>
@@ -4692,8 +4518,8 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="52"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
       <c r="F8" s="14"/>
@@ -4702,8 +4528,8 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="52"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
       <c r="F9" s="14"/>
@@ -4712,8 +4538,8 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="52"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
       <c r="F10" s="14"/>
@@ -4722,8 +4548,8 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="52"/>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
       <c r="F11" s="14"/>
@@ -4732,8 +4558,8 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
       <c r="F12" s="14"/>
@@ -4742,8 +4568,8 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
       <c r="F13" s="14"/>
@@ -4752,18 +4578,18 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="52"/>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="51"/>
       <c r="C14" s="14"/>
-      <c r="D14" s="50"/>
+      <c r="D14" s="49"/>
       <c r="F14" s="14"/>
       <c r="G14" s="18"/>
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="52"/>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
       <c r="F15" s="14"/>
@@ -4772,8 +4598,8 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="52"/>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
       <c r="F16" s="14"/>
@@ -4782,8 +4608,8 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
       <c r="F17" s="14"/>
@@ -4792,8 +4618,8 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="52"/>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
       <c r="F18" s="14"/>
@@ -4802,8 +4628,8 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="52"/>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
       <c r="F19" s="14"/>
@@ -4812,8 +4638,8 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
       <c r="F20" s="14"/>
@@ -4822,8 +4648,8 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
       <c r="F21" s="14"/>
@@ -4832,8 +4658,8 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
       <c r="F22" s="14"/>
@@ -4842,8 +4668,8 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="52"/>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
       <c r="F23" s="14"/>
@@ -4852,8 +4678,8 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24" s="52"/>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
       <c r="F24" s="14"/>
@@ -4862,8 +4688,8 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
       <c r="F25" s="14"/>
@@ -4872,8 +4698,8 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="52"/>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
       <c r="F26" s="14"/>
@@ -4882,8 +4708,8 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
       <c r="F27" s="14"/>
@@ -4892,8 +4718,8 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
       <c r="F28" s="14"/>
@@ -4902,8 +4728,8 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
       <c r="F29" s="14"/>
@@ -4912,8 +4738,8 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B30" s="52"/>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
       <c r="F30" s="14"/>
@@ -4922,8 +4748,8 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B31" s="52"/>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
       <c r="F31" s="14"/>
@@ -4932,8 +4758,8 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B32" s="52"/>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
       <c r="F32" s="14"/>
@@ -4942,8 +4768,8 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
       <c r="F33" s="14"/>
@@ -4952,8 +4778,8 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
       <c r="F34" s="14"/>
@@ -4962,8 +4788,8 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B35" s="52"/>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
       <c r="F35" s="14"/>
@@ -4972,8 +4798,8 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
       <c r="F36" s="14"/>
@@ -4982,8 +4808,8 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B37" s="52"/>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
       <c r="F37" s="14"/>
@@ -4992,8 +4818,8 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B38" s="52"/>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
       <c r="F38" s="14"/>
@@ -5002,8 +4828,8 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B39" s="52"/>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
       <c r="F39" s="14"/>
@@ -5012,8 +4838,8 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B40" s="52"/>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="51"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
       <c r="F40" s="14"/>
@@ -5022,8 +4848,8 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="53"/>
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="52"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
       <c r="E41" s="16"/>
@@ -5038,7 +4864,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -5047,7 +4873,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -5056,7 +4882,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -5065,7 +4891,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -5074,17 +4900,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -5106,34 +4932,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7295A98A-9DE5-4CC0-A28E-4AAE25FE895B}">
   <sheetPr filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="93.1796875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5150,7 +4976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5163,7 +4989,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5176,7 +5002,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5189,7 +5015,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5202,7 +5028,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5215,7 +5041,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5228,7 +5054,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5241,7 +5067,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5254,7 +5080,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5267,7 +5093,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5280,7 +5106,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5293,7 +5119,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5306,7 +5132,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5319,7 +5145,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5332,7 +5158,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5345,7 +5171,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5358,7 +5184,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5371,7 +5197,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5384,7 +5210,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5397,7 +5223,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5410,7 +5236,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5423,7 +5249,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5436,7 +5262,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5449,7 +5275,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5462,7 +5288,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5475,7 +5301,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5488,7 +5314,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5501,7 +5327,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5514,7 +5340,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5527,7 +5353,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5540,7 +5366,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5553,7 +5379,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5566,7 +5392,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5579,7 +5405,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5592,7 +5418,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5605,7 +5431,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5618,7 +5444,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5631,7 +5457,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5644,7 +5470,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5657,7 +5483,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5670,7 +5496,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5683,7 +5509,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5696,7 +5522,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5709,7 +5535,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5722,7 +5548,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5735,7 +5561,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5748,7 +5574,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5761,7 +5587,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5774,7 +5600,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5787,7 +5613,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5800,7 +5626,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5813,7 +5639,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5826,7 +5652,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5839,7 +5665,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5852,7 +5678,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5865,7 +5691,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5878,7 +5704,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5891,7 +5717,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5904,7 +5730,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5917,7 +5743,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5928,7 +5754,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5939,7 +5765,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5950,7 +5776,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5961,7 +5787,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5972,7 +5798,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5983,7 +5809,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5994,7 +5820,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -6005,7 +5831,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -6016,7 +5842,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -6027,7 +5853,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -6038,182 +5864,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
@@ -6221,7 +6047,7 @@
       <c r="F101" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B5:F75" xr:uid="{A099B508-44C7-48CD-924B-201E372CDC29}">
+  <autoFilter ref="B5:F75" xr:uid="{00000000-0009-0000-0000-000007000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="Sprint 2"/>
@@ -6229,10 +6055,10 @@
     </filterColumn>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D101" xr:uid="{F51E1D81-F30A-455D-8193-BBE5DE529FFA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D101" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"Sprint 1,Sprint 2,Sprint 3,Sprint 4,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E101" xr:uid="{0A8A13BB-479E-47FC-B198-FA503076D14C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E101" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"Haute,Moyenne,Basse,"</formula1>
     </dataValidation>
   </dataValidations>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86B1876-8C49-4207-9813-D509DE7E0027}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B23B575-F3C4-4EF7-AD9B-6AC688A0A80F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17730" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="168">
   <si>
     <t>Planification globale</t>
   </si>
@@ -541,6 +541,9 @@
 navbar conditionnelle (visible si connecté)
 , fond d'écran dynamique,
  conteneur principal</t>
+  </si>
+  <si>
+    <t>Page index.jsx: ajut : background ,logo,boutons</t>
   </si>
 </sst>
 </file>
@@ -1081,6 +1084,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1107,9 +1113,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2410,7 +2413,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="B2:L37"/>
+  <dimension ref="B2:L38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.54296875" customWidth="1"/>
@@ -2429,26 +2432,26 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="64"/>
     </row>
     <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="57" t="s">
@@ -2457,7 +2460,7 @@
       <c r="E5" s="58">
         <v>46083</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="69" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="60" t="s">
@@ -2466,7 +2469,7 @@
       <c r="H5" s="58">
         <v>46090</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="69" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="60" t="s">
@@ -2475,34 +2478,34 @@
       <c r="K5" s="58">
         <v>46104</v>
       </c>
-      <c r="L5" s="68" t="s">
+      <c r="L5" s="69" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="65"/>
-      <c r="C6" s="67"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="68"/>
       <c r="D6" s="57" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="69"/>
+      <c r="F6" s="70"/>
       <c r="G6" s="59" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="69"/>
+      <c r="I6" s="70"/>
       <c r="J6" s="59" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="69"/>
+      <c r="L6" s="70"/>
     </row>
     <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
@@ -2756,7 +2759,7 @@
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="61" t="s">
         <v>166</v>
       </c>
       <c r="C20" s="36" t="s">
@@ -2945,8 +2948,12 @@
       <c r="D30" s="31"/>
       <c r="E30" s="40"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="31">
+        <v>2</v>
+      </c>
+      <c r="H30" s="40">
+        <v>100</v>
+      </c>
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
@@ -2960,14 +2967,18 @@
       <c r="D31" s="31"/>
       <c r="E31" s="40"/>
       <c r="F31" s="14"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="40"/>
+      <c r="G31" s="31">
+        <v>1.3</v>
+      </c>
+      <c r="H31" s="40">
+        <v>100</v>
+      </c>
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>106</v>
@@ -2975,14 +2986,18 @@
       <c r="D32" s="31"/>
       <c r="E32" s="40"/>
       <c r="F32" s="14"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="40"/>
+      <c r="G32" s="31">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="40">
+        <v>100</v>
+      </c>
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36" t="s">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>106</v>
@@ -2997,7 +3012,7 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>106</v>
@@ -3012,7 +3027,7 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>106</v>
@@ -3027,7 +3042,7 @@
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="36" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>106</v>
@@ -3040,22 +3055,37 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="37" t="s">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B37" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="31"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="14"/>
+      <c r="L37" s="14"/>
+    </row>
+    <row r="38" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C38" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="17"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="B5:L6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86B1876-8C49-4207-9813-D509DE7E0027}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F84E09F-2AB3-4EF4-9310-5BE65899CF3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17730" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="168">
   <si>
     <t>Planification globale</t>
   </si>
@@ -541,6 +541,9 @@
 navbar conditionnelle (visible si connecté)
 , fond d'écran dynamique,
  conteneur principal</t>
+  </si>
+  <si>
+    <t>Création de toutes les tables</t>
   </si>
 </sst>
 </file>
@@ -1081,6 +1084,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1107,9 +1113,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2429,26 +2432,26 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="64"/>
     </row>
     <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="57" t="s">
@@ -2457,7 +2460,7 @@
       <c r="E5" s="58">
         <v>46083</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="69" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="60" t="s">
@@ -2466,7 +2469,7 @@
       <c r="H5" s="58">
         <v>46090</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="69" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="60" t="s">
@@ -2475,34 +2478,34 @@
       <c r="K5" s="58">
         <v>46104</v>
       </c>
-      <c r="L5" s="68" t="s">
+      <c r="L5" s="69" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="65"/>
-      <c r="C6" s="67"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="68"/>
       <c r="D6" s="57" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="69"/>
+      <c r="F6" s="70"/>
       <c r="G6" s="59" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="69"/>
+      <c r="I6" s="70"/>
       <c r="J6" s="59" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="69"/>
+      <c r="L6" s="70"/>
     </row>
     <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
@@ -2756,7 +2759,7 @@
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="2:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="61" t="s">
         <v>166</v>
       </c>
       <c r="C20" s="36" t="s">
@@ -2824,9 +2827,7 @@
       <c r="D23" s="31"/>
       <c r="E23" s="40"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="31" t="s">
-        <v>89</v>
-      </c>
+      <c r="G23" s="31"/>
       <c r="H23" s="40"/>
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
@@ -2879,9 +2880,15 @@
       <c r="D26" s="31"/>
       <c r="E26" s="40"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="14"/>
+      <c r="G26" s="31">
+        <v>1</v>
+      </c>
+      <c r="H26" s="40">
+        <v>100</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>167</v>
+      </c>
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F84E09F-2AB3-4EF4-9310-5BE65899CF3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9F194-8782-451D-9518-91862A3A7CC4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17730" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -27,17 +27,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="169">
   <si>
     <t>Planification globale</t>
   </si>
@@ -544,6 +549,9 @@
   </si>
   <si>
     <t>Création de toutes les tables</t>
+  </si>
+  <si>
+    <t>Gerer les erreurs dans page index</t>
   </si>
 </sst>
 </file>
@@ -1500,26 +1508,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="42.81640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="2:5" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1533,7 +1541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
         <v>152</v>
       </c>
@@ -1547,7 +1555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>122</v>
       </c>
@@ -1561,7 +1569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>123</v>
       </c>
@@ -1575,7 +1583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
         <v>124</v>
       </c>
@@ -1589,7 +1597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>125</v>
       </c>
@@ -1603,7 +1611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
         <v>127</v>
       </c>
@@ -1617,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>128</v>
       </c>
@@ -1631,7 +1639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>129</v>
       </c>
@@ -1645,7 +1653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="18" t="s">
         <v>156</v>
       </c>
@@ -1659,7 +1667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
         <v>132</v>
       </c>
@@ -1673,7 +1681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
         <v>133</v>
       </c>
@@ -1687,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
         <v>135</v>
       </c>
@@ -1701,7 +1709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
         <v>141</v>
       </c>
@@ -1715,7 +1723,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
         <v>130</v>
       </c>
@@ -1729,7 +1737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
         <v>131</v>
       </c>
@@ -1743,7 +1751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="18" t="s">
         <v>136</v>
       </c>
@@ -1757,7 +1765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
         <v>137</v>
       </c>
@@ -1771,7 +1779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
         <v>138</v>
       </c>
@@ -1785,7 +1793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
         <v>140</v>
       </c>
@@ -1799,7 +1807,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
         <v>144</v>
       </c>
@@ -1813,7 +1821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
         <v>145</v>
       </c>
@@ -1827,7 +1835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>146</v>
       </c>
@@ -1841,7 +1849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="18" t="s">
         <v>139</v>
       </c>
@@ -1855,7 +1863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
         <v>142</v>
       </c>
@@ -1869,7 +1877,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="18" t="s">
         <v>134</v>
       </c>
@@ -1883,7 +1891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
         <v>143</v>
       </c>
@@ -1897,7 +1905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="18" t="s">
         <v>147</v>
       </c>
@@ -1911,7 +1919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="18" t="s">
         <v>148</v>
       </c>
@@ -1925,7 +1933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="18" t="s">
         <v>149</v>
       </c>
@@ -1939,7 +1947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="18" t="s">
         <v>150</v>
       </c>
@@ -1953,7 +1961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="18" t="s">
         <v>151</v>
       </c>
@@ -1967,7 +1975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="22" t="s">
         <v>126</v>
       </c>
@@ -1981,8 +1989,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D39" s="41" t="s">
         <v>157</v>
       </c>
@@ -2011,32 +2019,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
-    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2066,7 +2074,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2120,7 +2128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -2147,7 +2155,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2169,7 +2177,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2196,7 +2204,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2229,7 +2237,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2266,7 +2274,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2303,7 +2311,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2335,7 +2343,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2363,7 +2371,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2390,15 +2398,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2413,25 +2421,25 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="B2:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:L38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.54296875" customWidth="1"/>
-    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.26953125" customWidth="1"/>
-    <col min="10" max="10" width="16.6328125" customWidth="1"/>
-    <col min="11" max="11" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.81640625" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.21875" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:12" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B3" s="62" t="s">
         <v>6</v>
       </c>
@@ -2446,8 +2454,8 @@
       <c r="K3" s="63"/>
       <c r="L3" s="64"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B5" s="65" t="s">
         <v>1</v>
       </c>
@@ -2482,7 +2490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="66"/>
       <c r="C6" s="68"/>
       <c r="D6" s="57" t="s">
@@ -2507,7 +2515,7 @@
       </c>
       <c r="L6" s="70"/>
     </row>
-    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2530,7 +2538,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -2549,7 +2557,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -2568,7 +2576,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -2587,7 +2595,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="36" t="s">
         <v>165</v>
       </c>
@@ -2606,7 +2614,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -2625,7 +2633,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -2644,7 +2652,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -2663,7 +2671,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="36" t="s">
         <v>163</v>
       </c>
@@ -2682,7 +2690,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="36" t="s">
         <v>29</v>
       </c>
@@ -2701,7 +2709,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="36" t="s">
         <v>30</v>
       </c>
@@ -2720,7 +2728,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
         <v>161</v>
       </c>
@@ -2739,7 +2747,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="36" t="s">
         <v>162</v>
       </c>
@@ -2758,7 +2766,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B20" s="61" t="s">
         <v>166</v>
       </c>
@@ -2777,7 +2785,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="36" t="s">
         <v>92</v>
       </c>
@@ -2798,7 +2806,7 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
         <v>51</v>
       </c>
@@ -2817,7 +2825,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="36" t="s">
         <v>90</v>
       </c>
@@ -2832,7 +2840,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
         <v>74</v>
       </c>
@@ -2851,7 +2859,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
@@ -2870,7 +2878,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="36" t="s">
         <v>93</v>
       </c>
@@ -2891,7 +2899,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="36" t="s">
         <v>94</v>
       </c>
@@ -2906,7 +2914,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
         <v>79</v>
       </c>
@@ -2927,7 +2935,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
         <v>76</v>
       </c>
@@ -2942,7 +2950,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="36" t="s">
         <v>42</v>
       </c>
@@ -2952,12 +2960,16 @@
       <c r="D30" s="31"/>
       <c r="E30" s="40"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="31">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="40">
+        <v>100</v>
+      </c>
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="36" t="s">
         <v>43</v>
       </c>
@@ -2967,12 +2979,16 @@
       <c r="D31" s="31"/>
       <c r="E31" s="40"/>
       <c r="F31" s="14"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="40"/>
+      <c r="G31" s="31">
+        <v>0.75</v>
+      </c>
+      <c r="H31" s="40">
+        <v>100</v>
+      </c>
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="36" t="s">
         <v>164</v>
       </c>
@@ -2987,9 +3003,9 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="36" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>106</v>
@@ -2997,14 +3013,18 @@
       <c r="D33" s="31"/>
       <c r="E33" s="40"/>
       <c r="F33" s="14"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="40"/>
+      <c r="G33" s="31">
+        <v>0.25</v>
+      </c>
+      <c r="H33" s="40">
+        <v>100</v>
+      </c>
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="36" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>106</v>
@@ -3017,9 +3037,9 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>106</v>
@@ -3032,9 +3052,9 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="36" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>106</v>
@@ -3047,22 +3067,37 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="37" t="s">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="31"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="14"/>
+      <c r="L37" s="14"/>
+    </row>
+    <row r="38" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C38" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="17"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="B5:L6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -3101,21 +3136,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="70.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" customWidth="1"/>
-    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3129,151 +3164,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -3289,28 +3324,28 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="21.1796875" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3335,7 +3370,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3370,7 +3405,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="50"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
@@ -3383,7 +3418,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="51"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -3392,7 +3427,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -3401,7 +3436,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -3410,7 +3445,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -3419,7 +3454,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -3428,7 +3463,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -3437,7 +3472,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -3446,7 +3481,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -3455,7 +3490,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="51"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -3464,7 +3499,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -3473,7 +3508,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -3482,7 +3517,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3491,7 +3526,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3500,7 +3535,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3509,7 +3544,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3518,7 +3553,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3527,7 +3562,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3536,7 +3571,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3545,7 +3580,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3554,7 +3589,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3563,7 +3598,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3572,7 +3607,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3581,7 +3616,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3590,7 +3625,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3599,7 +3634,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3608,7 +3643,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3617,7 +3652,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -3626,7 +3661,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3635,7 +3670,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3644,7 +3679,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3653,7 +3688,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3662,7 +3697,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3671,7 +3706,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3680,7 +3715,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3689,7 +3724,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="52"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3722,18 +3757,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3757,7 +3792,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3801,7 +3836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3823,7 +3858,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3841,7 +3876,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -3859,7 +3894,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3877,7 +3912,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -3895,7 +3930,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -3913,7 +3948,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -3931,7 +3966,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -3949,7 +3984,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -3967,7 +4002,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -3985,7 +4020,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4003,7 +4038,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4021,7 +4056,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4039,7 +4074,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4057,7 +4092,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4075,7 +4110,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4093,7 +4128,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4111,7 +4146,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4129,7 +4164,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4147,7 +4182,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4165,7 +4200,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4183,7 +4218,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4201,7 +4236,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4219,7 +4254,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4237,7 +4272,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4255,7 +4290,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4273,7 +4308,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4291,7 +4326,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4309,7 +4344,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4327,7 +4362,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4349,47 +4384,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4401,29 +4436,29 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="51.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4455,7 +4490,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4499,7 +4534,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="50"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
@@ -4515,7 +4550,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -4525,7 +4560,7 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -4535,7 +4570,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -4545,7 +4580,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -4555,7 +4590,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -4565,7 +4600,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -4575,7 +4610,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -4585,7 +4620,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="51"/>
       <c r="C14" s="14"/>
       <c r="D14" s="49"/>
@@ -4595,7 +4630,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -4605,7 +4640,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -4615,7 +4650,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -4625,7 +4660,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -4635,7 +4670,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -4645,7 +4680,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -4655,7 +4690,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -4665,7 +4700,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -4675,7 +4710,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -4685,7 +4720,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -4695,7 +4730,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -4705,7 +4740,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -4715,7 +4750,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -4725,7 +4760,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -4735,7 +4770,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -4745,7 +4780,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -4755,7 +4790,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -4765,7 +4800,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -4775,7 +4810,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -4785,7 +4820,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -4795,7 +4830,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -4805,7 +4840,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -4815,7 +4850,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -4825,7 +4860,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -4835,7 +4870,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -4845,7 +4880,7 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" s="51"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
@@ -4855,7 +4890,7 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="52"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
@@ -4871,7 +4906,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -4880,7 +4915,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -4889,7 +4924,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -4898,7 +4933,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -4907,17 +4942,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -4945,28 +4980,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="93.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="2" max="2" width="93.21875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="42.81640625" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -4983,7 +5018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -4996,7 +5031,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5009,7 +5044,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5022,7 +5057,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5035,7 +5070,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5048,7 +5083,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5061,7 +5096,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5074,7 +5109,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5087,7 +5122,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5100,7 +5135,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5113,7 +5148,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5126,7 +5161,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5139,7 +5174,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5152,7 +5187,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5165,7 +5200,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5178,7 +5213,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5191,7 +5226,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5204,7 +5239,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5217,7 +5252,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5230,7 +5265,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5243,7 +5278,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5256,7 +5291,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5269,7 +5304,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5282,7 +5317,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5295,7 +5330,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5308,7 +5343,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5321,7 +5356,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5334,7 +5369,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5347,7 +5382,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5360,7 +5395,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5373,7 +5408,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5386,7 +5421,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5399,7 +5434,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5412,7 +5447,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5425,7 +5460,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5438,7 +5473,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5451,7 +5486,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5464,7 +5499,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5477,7 +5512,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5490,7 +5525,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5503,7 +5538,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5516,7 +5551,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5529,7 +5564,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5542,7 +5577,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5555,7 +5590,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5568,7 +5603,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5581,7 +5616,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5594,7 +5629,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5607,7 +5642,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5620,7 +5655,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5633,7 +5668,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5646,7 +5681,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5659,7 +5694,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5672,7 +5707,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5685,7 +5720,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5698,7 +5733,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5711,7 +5746,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5724,7 +5759,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5737,7 +5772,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5750,7 +5785,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5761,7 +5796,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5772,7 +5807,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5783,7 +5818,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5794,7 +5829,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5805,7 +5840,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5816,7 +5851,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5827,7 +5862,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -5838,7 +5873,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -5849,7 +5884,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -5860,7 +5895,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -5871,182 +5906,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9F194-8782-451D-9518-91862A3A7CC4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773CBCD3-7D1C-471B-A490-96D1864AC313}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -27,22 +27,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="171">
   <si>
     <t>Planification globale</t>
   </si>
@@ -552,6 +547,12 @@
   </si>
   <si>
     <t>Gerer les erreurs dans page index</t>
+  </si>
+  <si>
+    <t>Creation page administration liste les comptes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajouter permettre la supression d un compte </t>
   </si>
 </sst>
 </file>
@@ -1508,26 +1509,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1541,7 +1542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
         <v>152</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="18" t="s">
         <v>122</v>
       </c>
@@ -1569,7 +1570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="18" t="s">
         <v>123</v>
       </c>
@@ -1583,7 +1584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
         <v>124</v>
       </c>
@@ -1597,7 +1598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="18" t="s">
         <v>125</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
         <v>127</v>
       </c>
@@ -1625,7 +1626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
         <v>128</v>
       </c>
@@ -1639,7 +1640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="18" t="s">
         <v>129</v>
       </c>
@@ -1653,7 +1654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
         <v>156</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
         <v>132</v>
       </c>
@@ -1681,7 +1682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
         <v>133</v>
       </c>
@@ -1695,7 +1696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="18" t="s">
         <v>135</v>
       </c>
@@ -1709,7 +1710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="18" t="s">
         <v>141</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="18" t="s">
         <v>130</v>
       </c>
@@ -1737,7 +1738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="18" t="s">
         <v>131</v>
       </c>
@@ -1751,7 +1752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="18" t="s">
         <v>136</v>
       </c>
@@ -1765,7 +1766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
         <v>137</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
         <v>138</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
         <v>140</v>
       </c>
@@ -1807,7 +1808,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
         <v>144</v>
       </c>
@@ -1821,7 +1822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
         <v>145</v>
       </c>
@@ -1835,7 +1836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
         <v>146</v>
       </c>
@@ -1849,7 +1850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="18" t="s">
         <v>139</v>
       </c>
@@ -1863,7 +1864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
         <v>142</v>
       </c>
@@ -1877,7 +1878,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
         <v>134</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="18" t="s">
         <v>143</v>
       </c>
@@ -1905,7 +1906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="18" t="s">
         <v>147</v>
       </c>
@@ -1919,7 +1920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
         <v>148</v>
       </c>
@@ -1933,7 +1934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
         <v>149</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="18" t="s">
         <v>150</v>
       </c>
@@ -1961,7 +1962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="18" t="s">
         <v>151</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="22" t="s">
         <v>126</v>
       </c>
@@ -1989,8 +1990,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D39" s="41" t="s">
         <v>157</v>
       </c>
@@ -2019,32 +2020,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2074,7 +2075,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2128,7 +2129,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -2155,7 +2156,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2177,7 +2178,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2204,7 +2205,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2237,7 +2238,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2274,7 +2275,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2311,7 +2312,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2343,7 +2344,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2371,7 +2372,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2398,15 +2399,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2421,25 +2422,25 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="B2:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.21875" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.1796875" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
       <c r="B3" s="62" t="s">
         <v>6</v>
       </c>
@@ -2454,8 +2455,8 @@
       <c r="K3" s="63"/>
       <c r="L3" s="64"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="65" t="s">
         <v>1</v>
       </c>
@@ -2490,7 +2491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="66"/>
       <c r="C6" s="68"/>
       <c r="D6" s="57" t="s">
@@ -2515,7 +2516,7 @@
       </c>
       <c r="L6" s="70"/>
     </row>
-    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2538,7 +2539,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -2557,7 +2558,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -2576,7 +2577,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -2595,7 +2596,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36" t="s">
         <v>165</v>
       </c>
@@ -2614,7 +2615,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -2633,7 +2634,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -2652,7 +2653,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -2671,7 +2672,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36" t="s">
         <v>163</v>
       </c>
@@ -2690,7 +2691,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
         <v>29</v>
       </c>
@@ -2709,7 +2710,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36" t="s">
         <v>30</v>
       </c>
@@ -2728,7 +2729,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
         <v>161</v>
       </c>
@@ -2747,7 +2748,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36" t="s">
         <v>162</v>
       </c>
@@ -2766,7 +2767,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="58" x14ac:dyDescent="0.35">
       <c r="B20" s="61" t="s">
         <v>166</v>
       </c>
@@ -2785,7 +2786,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="36" t="s">
         <v>92</v>
       </c>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36" t="s">
         <v>51</v>
       </c>
@@ -2825,7 +2826,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36" t="s">
         <v>90</v>
       </c>
@@ -2840,7 +2841,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36" t="s">
         <v>74</v>
       </c>
@@ -2859,7 +2860,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
@@ -2878,7 +2879,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36" t="s">
         <v>93</v>
       </c>
@@ -2899,7 +2900,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="36" t="s">
         <v>94</v>
       </c>
@@ -2914,7 +2915,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B28" s="36" t="s">
         <v>79</v>
       </c>
@@ -2935,7 +2936,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
         <v>76</v>
       </c>
@@ -2950,7 +2951,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
         <v>42</v>
       </c>
@@ -2969,7 +2970,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="36" t="s">
         <v>43</v>
       </c>
@@ -2988,7 +2989,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36" t="s">
         <v>164</v>
       </c>
@@ -3003,7 +3004,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36" t="s">
         <v>168</v>
       </c>
@@ -3020,9 +3021,15 @@
         <v>100</v>
       </c>
       <c r="I33" s="14"/>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36" t="s">
         <v>73</v>
       </c>
@@ -3035,9 +3042,15 @@
       <c r="G34" s="31"/>
       <c r="H34" s="40"/>
       <c r="I34" s="14"/>
+      <c r="J34">
+        <v>1.5</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="36" t="s">
         <v>38</v>
       </c>
@@ -3050,9 +3063,15 @@
       <c r="G35" s="31"/>
       <c r="H35" s="40"/>
       <c r="I35" s="14"/>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="36" t="s">
         <v>39</v>
       </c>
@@ -3065,9 +3084,15 @@
       <c r="G36" s="31"/>
       <c r="H36" s="40"/>
       <c r="I36" s="14"/>
+      <c r="J36">
+        <v>0.75</v>
+      </c>
+      <c r="K36">
+        <v>100</v>
+      </c>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="36" t="s">
         <v>61</v>
       </c>
@@ -3080,24 +3105,68 @@
       <c r="G37" s="31"/>
       <c r="H37" s="40"/>
       <c r="I37" s="14"/>
+      <c r="J37">
+        <v>1.5</v>
+      </c>
+      <c r="K37">
+        <v>100</v>
+      </c>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="37" t="s">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B38" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="17"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="14"/>
+      <c r="J38">
+        <v>1.3</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38" s="14"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B39" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="31"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="14"/>
+      <c r="J39">
+        <v>0.75</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39" s="14"/>
+    </row>
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="B5:L6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -3136,21 +3205,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3164,151 +3233,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -3324,28 +3393,28 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3370,7 +3439,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3405,7 +3474,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="50"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
@@ -3418,7 +3487,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="51"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -3427,7 +3496,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -3436,7 +3505,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -3445,7 +3514,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -3454,7 +3523,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -3463,7 +3532,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -3472,7 +3541,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -3481,7 +3550,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -3490,7 +3559,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="51"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -3499,7 +3568,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -3508,7 +3577,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -3517,7 +3586,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3526,7 +3595,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3535,7 +3604,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3544,7 +3613,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3553,7 +3622,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3562,7 +3631,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3571,7 +3640,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3580,7 +3649,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3589,7 +3658,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3598,7 +3667,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3607,7 +3676,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3616,7 +3685,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3625,7 +3694,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3634,7 +3703,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3643,7 +3712,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3652,7 +3721,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -3661,7 +3730,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3670,7 +3739,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3679,7 +3748,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3688,7 +3757,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3697,7 +3766,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3706,7 +3775,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3715,7 +3784,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3724,7 +3793,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="52"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3757,18 +3826,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3792,7 +3861,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3836,7 +3905,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3858,7 +3927,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3876,7 +3945,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -3894,7 +3963,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3912,7 +3981,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -3930,7 +3999,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -3948,7 +4017,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -3966,7 +4035,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -3984,7 +4053,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4002,7 +4071,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -4020,7 +4089,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4038,7 +4107,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4056,7 +4125,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4074,7 +4143,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4092,7 +4161,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4110,7 +4179,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4128,7 +4197,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4146,7 +4215,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4164,7 +4233,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4182,7 +4251,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4200,7 +4269,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4218,7 +4287,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4236,7 +4305,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4254,7 +4323,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4272,7 +4341,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4290,7 +4359,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4308,7 +4377,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4326,7 +4395,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4344,7 +4413,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4362,7 +4431,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4384,47 +4453,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4436,29 +4505,29 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4490,7 +4559,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4534,7 +4603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="50"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
@@ -4550,7 +4619,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -4560,7 +4629,7 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -4570,7 +4639,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -4580,7 +4649,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -4590,7 +4659,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -4600,7 +4669,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -4610,7 +4679,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -4620,7 +4689,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="51"/>
       <c r="C14" s="14"/>
       <c r="D14" s="49"/>
@@ -4630,7 +4699,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -4640,7 +4709,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -4650,7 +4719,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -4660,7 +4729,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -4670,7 +4739,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -4680,7 +4749,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -4690,7 +4759,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -4700,7 +4769,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -4710,7 +4779,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -4720,7 +4789,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -4730,7 +4799,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -4740,7 +4809,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -4750,7 +4819,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -4760,7 +4829,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -4770,7 +4839,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -4780,7 +4849,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -4790,7 +4859,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -4800,7 +4869,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -4810,7 +4879,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -4820,7 +4889,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -4830,7 +4899,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -4840,7 +4909,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -4850,7 +4919,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -4860,7 +4929,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -4870,7 +4939,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -4880,7 +4949,7 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B40" s="51"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
@@ -4890,7 +4959,7 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="52"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
@@ -4906,7 +4975,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -4915,7 +4984,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -4924,7 +4993,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -4933,7 +5002,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -4942,17 +5011,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -4980,28 +5049,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="93.1796875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5018,7 +5087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5031,7 +5100,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5044,7 +5113,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5057,7 +5126,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5070,7 +5139,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5083,7 +5152,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5096,7 +5165,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5109,7 +5178,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5122,7 +5191,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5135,7 +5204,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5148,7 +5217,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5161,7 +5230,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5174,7 +5243,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5187,7 +5256,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5200,7 +5269,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5213,7 +5282,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5226,7 +5295,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5239,7 +5308,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5252,7 +5321,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5265,7 +5334,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5278,7 +5347,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5291,7 +5360,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5304,7 +5373,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5317,7 +5386,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5330,7 +5399,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5343,7 +5412,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5356,7 +5425,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5369,7 +5438,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5382,7 +5451,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5395,7 +5464,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5408,7 +5477,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5421,7 +5490,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5434,7 +5503,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5447,7 +5516,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5460,7 +5529,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5473,7 +5542,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5486,7 +5555,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5499,7 +5568,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5512,7 +5581,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5525,7 +5594,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5538,7 +5607,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5551,7 +5620,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5564,7 +5633,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5577,7 +5646,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5590,7 +5659,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5603,7 +5672,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5616,7 +5685,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5629,7 +5698,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5642,7 +5711,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5655,7 +5724,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5668,7 +5737,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5681,7 +5750,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5694,7 +5763,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5707,7 +5776,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5720,7 +5789,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5733,7 +5802,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5746,7 +5815,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5759,7 +5828,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5772,7 +5841,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5785,7 +5854,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5796,7 +5865,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5807,7 +5876,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5818,7 +5887,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5829,7 +5898,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5840,7 +5909,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5851,7 +5920,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5862,7 +5931,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -5873,7 +5942,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -5884,7 +5953,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -5895,7 +5964,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -5906,182 +5975,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9F194-8782-451D-9518-91862A3A7CC4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BEE6A3-0D8D-43F6-9F53-BC93A3B7AF5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -27,22 +27,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="171">
   <si>
     <t>Planification globale</t>
   </si>
@@ -552,6 +547,12 @@
   </si>
   <si>
     <t>Gerer les erreurs dans page index</t>
+  </si>
+  <si>
+    <t>À tester avec le jeu, mais devrait marcher</t>
+  </si>
+  <si>
+    <t>Connection avec une session_key unique</t>
   </si>
 </sst>
 </file>
@@ -1508,26 +1509,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1541,7 +1542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
         <v>152</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="18" t="s">
         <v>122</v>
       </c>
@@ -1569,7 +1570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="18" t="s">
         <v>123</v>
       </c>
@@ -1583,7 +1584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
         <v>124</v>
       </c>
@@ -1597,7 +1598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="18" t="s">
         <v>125</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
         <v>127</v>
       </c>
@@ -1625,7 +1626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
         <v>128</v>
       </c>
@@ -1639,7 +1640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="18" t="s">
         <v>129</v>
       </c>
@@ -1653,7 +1654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
         <v>156</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
         <v>132</v>
       </c>
@@ -1681,7 +1682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
         <v>133</v>
       </c>
@@ -1695,7 +1696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="18" t="s">
         <v>135</v>
       </c>
@@ -1709,7 +1710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="18" t="s">
         <v>141</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="18" t="s">
         <v>130</v>
       </c>
@@ -1737,7 +1738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="18" t="s">
         <v>131</v>
       </c>
@@ -1751,7 +1752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="18" t="s">
         <v>136</v>
       </c>
@@ -1765,7 +1766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
         <v>137</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
         <v>138</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
         <v>140</v>
       </c>
@@ -1807,7 +1808,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
         <v>144</v>
       </c>
@@ -1821,7 +1822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
         <v>145</v>
       </c>
@@ -1835,7 +1836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
         <v>146</v>
       </c>
@@ -1849,7 +1850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="18" t="s">
         <v>139</v>
       </c>
@@ -1863,7 +1864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
         <v>142</v>
       </c>
@@ -1877,7 +1878,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
         <v>134</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="18" t="s">
         <v>143</v>
       </c>
@@ -1905,7 +1906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="18" t="s">
         <v>147</v>
       </c>
@@ -1919,7 +1920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
         <v>148</v>
       </c>
@@ -1933,7 +1934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
         <v>149</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="18" t="s">
         <v>150</v>
       </c>
@@ -1961,7 +1962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="18" t="s">
         <v>151</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="22" t="s">
         <v>126</v>
       </c>
@@ -1989,8 +1990,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D39" s="41" t="s">
         <v>157</v>
       </c>
@@ -2019,32 +2020,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2074,7 +2075,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2128,7 +2129,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -2155,7 +2156,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2177,7 +2178,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2204,7 +2205,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2237,7 +2238,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2274,7 +2275,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2311,7 +2312,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2343,7 +2344,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2371,7 +2372,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2398,15 +2399,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2422,24 +2423,24 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B2:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.21875" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.1796875" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
       <c r="B3" s="62" t="s">
         <v>6</v>
       </c>
@@ -2454,8 +2455,8 @@
       <c r="K3" s="63"/>
       <c r="L3" s="64"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="65" t="s">
         <v>1</v>
       </c>
@@ -2490,7 +2491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="66"/>
       <c r="C6" s="68"/>
       <c r="D6" s="57" t="s">
@@ -2515,7 +2516,7 @@
       </c>
       <c r="L6" s="70"/>
     </row>
-    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2538,7 +2539,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -2557,7 +2558,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -2576,7 +2577,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -2595,7 +2596,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36" t="s">
         <v>165</v>
       </c>
@@ -2614,7 +2615,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -2633,7 +2634,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -2652,7 +2653,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -2671,7 +2672,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36" t="s">
         <v>163</v>
       </c>
@@ -2690,7 +2691,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
         <v>29</v>
       </c>
@@ -2709,7 +2710,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36" t="s">
         <v>30</v>
       </c>
@@ -2728,7 +2729,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
         <v>161</v>
       </c>
@@ -2747,7 +2748,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36" t="s">
         <v>162</v>
       </c>
@@ -2766,7 +2767,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="58" x14ac:dyDescent="0.35">
       <c r="B20" s="61" t="s">
         <v>166</v>
       </c>
@@ -2785,7 +2786,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="36" t="s">
         <v>92</v>
       </c>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36" t="s">
         <v>51</v>
       </c>
@@ -2825,7 +2826,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36" t="s">
         <v>90</v>
       </c>
@@ -2835,12 +2836,18 @@
       <c r="D23" s="31"/>
       <c r="E23" s="40"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="14"/>
+      <c r="G23" s="31">
+        <v>2</v>
+      </c>
+      <c r="H23" s="40">
+        <v>100</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>169</v>
+      </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36" t="s">
         <v>74</v>
       </c>
@@ -2859,7 +2866,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
@@ -2878,7 +2885,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36" t="s">
         <v>93</v>
       </c>
@@ -2899,7 +2906,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="36" t="s">
         <v>94</v>
       </c>
@@ -2909,12 +2916,18 @@
       <c r="D27" s="31"/>
       <c r="E27" s="40"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="14"/>
+      <c r="G27" s="31">
+        <v>1</v>
+      </c>
+      <c r="H27" s="40">
+        <v>100</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>170</v>
+      </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B28" s="36" t="s">
         <v>79</v>
       </c>
@@ -2928,14 +2941,14 @@
         <v>0.5</v>
       </c>
       <c r="H28" s="40">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I28" s="54" t="s">
         <v>160</v>
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
         <v>76</v>
       </c>
@@ -2945,12 +2958,16 @@
       <c r="D29" s="31"/>
       <c r="E29" s="40"/>
       <c r="F29" s="14"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="40"/>
+      <c r="G29" s="31">
+        <v>1</v>
+      </c>
+      <c r="H29" s="40">
+        <v>100</v>
+      </c>
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
         <v>42</v>
       </c>
@@ -2969,7 +2986,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="36" t="s">
         <v>43</v>
       </c>
@@ -2988,7 +3005,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="36" t="s">
         <v>164</v>
       </c>
@@ -3003,7 +3020,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="36" t="s">
         <v>168</v>
       </c>
@@ -3022,7 +3039,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="36" t="s">
         <v>73</v>
       </c>
@@ -3037,7 +3054,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="36" t="s">
         <v>38</v>
       </c>
@@ -3052,7 +3069,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="36" t="s">
         <v>39</v>
       </c>
@@ -3067,7 +3084,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="36" t="s">
         <v>61</v>
       </c>
@@ -3082,7 +3099,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="37" t="s">
         <v>56</v>
       </c>
@@ -3136,21 +3153,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3164,151 +3181,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -3324,28 +3341,28 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
@@ -3370,7 +3387,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3405,7 +3422,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="50"/>
       <c r="C5" s="12"/>
       <c r="D5" s="21"/>
@@ -3418,7 +3435,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="51"/>
       <c r="C6" s="14"/>
       <c r="D6" s="18"/>
@@ -3427,7 +3444,7 @@
       <c r="I6" s="14"/>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -3436,7 +3453,7 @@
       <c r="I7" s="14"/>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -3445,7 +3462,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -3454,7 +3471,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -3463,7 +3480,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -3472,7 +3489,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -3481,7 +3498,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -3490,7 +3507,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="51"/>
       <c r="C14" s="14"/>
       <c r="D14" s="18"/>
@@ -3499,7 +3516,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -3508,7 +3525,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -3517,7 +3534,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -3526,7 +3543,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -3535,7 +3552,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -3544,7 +3561,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -3553,7 +3570,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -3562,7 +3579,7 @@
       <c r="I21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -3571,7 +3588,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -3580,7 +3597,7 @@
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -3589,7 +3606,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -3598,7 +3615,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -3607,7 +3624,7 @@
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -3616,7 +3633,7 @@
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -3625,7 +3642,7 @@
       <c r="I28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -3634,7 +3651,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -3643,7 +3660,7 @@
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -3652,7 +3669,7 @@
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -3661,7 +3678,7 @@
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -3670,7 +3687,7 @@
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -3679,7 +3696,7 @@
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -3688,7 +3705,7 @@
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -3697,7 +3714,7 @@
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -3706,7 +3723,7 @@
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -3715,7 +3732,7 @@
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -3724,7 +3741,7 @@
       <c r="I39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="52"/>
       <c r="C40" s="17"/>
       <c r="D40" s="22"/>
@@ -3757,18 +3774,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3792,7 +3809,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3836,7 +3853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3858,7 +3875,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3876,7 +3893,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -3894,7 +3911,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3912,7 +3929,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -3930,7 +3947,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -3948,7 +3965,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -3966,7 +3983,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -3984,7 +4001,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4002,7 +4019,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -4020,7 +4037,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4038,7 +4055,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4056,7 +4073,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4074,7 +4091,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4092,7 +4109,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4110,7 +4127,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4128,7 +4145,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4146,7 +4163,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4164,7 +4181,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4182,7 +4199,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4200,7 +4217,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4218,7 +4235,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4236,7 +4253,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4254,7 +4271,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4272,7 +4289,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4290,7 +4307,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4308,7 +4325,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4326,7 +4343,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4344,7 +4361,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4362,7 +4379,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4384,47 +4401,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4436,29 +4453,29 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4490,7 +4507,7 @@
       </c>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4534,7 +4551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="50"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21"/>
@@ -4550,7 +4567,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="51"/>
       <c r="C7" s="14"/>
       <c r="D7" s="18"/>
@@ -4560,7 +4577,7 @@
       <c r="L7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="51"/>
       <c r="C8" s="14"/>
       <c r="D8" s="18"/>
@@ -4570,7 +4587,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="51"/>
       <c r="C9" s="14"/>
       <c r="D9" s="18"/>
@@ -4580,7 +4597,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="51"/>
       <c r="C10" s="14"/>
       <c r="D10" s="18"/>
@@ -4590,7 +4607,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="51"/>
       <c r="C11" s="14"/>
       <c r="D11" s="18"/>
@@ -4600,7 +4617,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="51"/>
       <c r="C12" s="14"/>
       <c r="D12" s="18"/>
@@ -4610,7 +4627,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="51"/>
       <c r="C13" s="14"/>
       <c r="D13" s="18"/>
@@ -4620,7 +4637,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="51"/>
       <c r="C14" s="14"/>
       <c r="D14" s="49"/>
@@ -4630,7 +4647,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="51"/>
       <c r="C15" s="14"/>
       <c r="D15" s="18"/>
@@ -4640,7 +4657,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="51"/>
       <c r="C16" s="14"/>
       <c r="D16" s="18"/>
@@ -4650,7 +4667,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="51"/>
       <c r="C17" s="14"/>
       <c r="D17" s="18"/>
@@ -4660,7 +4677,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="51"/>
       <c r="C18" s="14"/>
       <c r="D18" s="18"/>
@@ -4670,7 +4687,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="51"/>
       <c r="C19" s="14"/>
       <c r="D19" s="18"/>
@@ -4680,7 +4697,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="51"/>
       <c r="C20" s="14"/>
       <c r="D20" s="18"/>
@@ -4690,7 +4707,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="51"/>
       <c r="C21" s="14"/>
       <c r="D21" s="18"/>
@@ -4700,7 +4717,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="51"/>
       <c r="C22" s="14"/>
       <c r="D22" s="18"/>
@@ -4710,7 +4727,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="51"/>
       <c r="C23" s="14"/>
       <c r="D23" s="18"/>
@@ -4720,7 +4737,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="51"/>
       <c r="C24" s="14"/>
       <c r="D24" s="18"/>
@@ -4730,7 +4747,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="51"/>
       <c r="C25" s="14"/>
       <c r="D25" s="18"/>
@@ -4740,7 +4757,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="51"/>
       <c r="C26" s="14"/>
       <c r="D26" s="18"/>
@@ -4750,7 +4767,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="51"/>
       <c r="C27" s="14"/>
       <c r="D27" s="18"/>
@@ -4760,7 +4777,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="51"/>
       <c r="C28" s="14"/>
       <c r="D28" s="18"/>
@@ -4770,7 +4787,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="51"/>
       <c r="C29" s="14"/>
       <c r="D29" s="18"/>
@@ -4780,7 +4797,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="51"/>
       <c r="C30" s="14"/>
       <c r="D30" s="18"/>
@@ -4790,7 +4807,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="51"/>
       <c r="C31" s="14"/>
       <c r="D31" s="18"/>
@@ -4800,7 +4817,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="51"/>
       <c r="C32" s="14"/>
       <c r="D32" s="18"/>
@@ -4810,7 +4827,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="51"/>
       <c r="C33" s="14"/>
       <c r="D33" s="18"/>
@@ -4820,7 +4837,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="51"/>
       <c r="C34" s="14"/>
       <c r="D34" s="18"/>
@@ -4830,7 +4847,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="51"/>
       <c r="C35" s="14"/>
       <c r="D35" s="18"/>
@@ -4840,7 +4857,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36" s="51"/>
       <c r="C36" s="14"/>
       <c r="D36" s="18"/>
@@ -4850,7 +4867,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37" s="51"/>
       <c r="C37" s="14"/>
       <c r="D37" s="18"/>
@@ -4860,7 +4877,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38" s="51"/>
       <c r="C38" s="14"/>
       <c r="D38" s="18"/>
@@ -4870,7 +4887,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B39" s="51"/>
       <c r="C39" s="14"/>
       <c r="D39" s="18"/>
@@ -4880,7 +4897,7 @@
       <c r="L39" s="14"/>
       <c r="O39" s="14"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B40" s="51"/>
       <c r="C40" s="14"/>
       <c r="D40" s="18"/>
@@ -4890,7 +4907,7 @@
       <c r="L40" s="14"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="52"/>
       <c r="C41" s="17"/>
       <c r="D41" s="22"/>
@@ -4906,7 +4923,7 @@
       <c r="N41" s="16"/>
       <c r="O41" s="17"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" t="s">
@@ -4915,7 +4932,7 @@
       <c r="J64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" t="s">
@@ -4924,7 +4941,7 @@
       <c r="J65" s="5"/>
       <c r="M65" s="5"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" t="s">
@@ -4933,7 +4950,7 @@
       <c r="J67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D68" s="5"/>
       <c r="G68" s="5"/>
       <c r="J68" s="5"/>
@@ -4942,17 +4959,17 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
       <c r="H71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
       <c r="K72" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D73" s="5"/>
       <c r="G73" s="5"/>
       <c r="J73" s="5"/>
@@ -4980,28 +4997,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="93.1796875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5018,7 +5035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5031,7 +5048,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5044,7 +5061,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5057,7 +5074,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5070,7 +5087,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5083,7 +5100,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5096,7 +5113,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5109,7 +5126,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5122,7 +5139,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5135,7 +5152,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5148,7 +5165,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5161,7 +5178,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5174,7 +5191,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5187,7 +5204,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5200,7 +5217,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5213,7 +5230,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5226,7 +5243,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5239,7 +5256,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5252,7 +5269,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5265,7 +5282,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5278,7 +5295,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5291,7 +5308,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5304,7 +5321,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5317,7 +5334,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5330,7 +5347,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5343,7 +5360,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5356,7 +5373,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5369,7 +5386,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5382,7 +5399,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5395,7 +5412,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5408,7 +5425,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5421,7 +5438,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5434,7 +5451,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5447,7 +5464,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5460,7 +5477,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5473,7 +5490,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5486,7 +5503,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5499,7 +5516,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5512,7 +5529,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5525,7 +5542,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5538,7 +5555,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5551,7 +5568,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5564,7 +5581,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5577,7 +5594,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5590,7 +5607,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5603,7 +5620,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5616,7 +5633,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5629,7 +5646,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5642,7 +5659,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5655,7 +5672,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5668,7 +5685,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5681,7 +5698,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5694,7 +5711,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5707,7 +5724,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5720,7 +5737,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5733,7 +5750,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5746,7 +5763,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5759,7 +5776,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5772,7 +5789,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5785,7 +5802,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5796,7 +5813,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5807,7 +5824,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5818,7 +5835,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5829,7 +5846,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5840,7 +5857,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5851,7 +5868,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5862,7 +5879,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -5873,7 +5890,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -5884,7 +5901,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -5895,7 +5912,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -5906,182 +5923,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BEE6A3-0D8D-43F6-9F53-BC93A3B7AF5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0B622C-6B22-4FCB-A772-0DFA05757C5B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 1" sheetId="2" r:id="rId2"/>
     <sheet name=" Sprint 2" sheetId="8" r:id="rId3"/>
-    <sheet name="Mi-mandat" sheetId="7" r:id="rId4"/>
-    <sheet name="Sprint 3" sheetId="4" r:id="rId5"/>
+    <sheet name="Sprint 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Mi-mandat" sheetId="7" r:id="rId5"/>
     <sheet name="Planif Sprint 3" sheetId="9" r:id="rId6"/>
     <sheet name="Sprint 4" sheetId="5" r:id="rId7"/>
     <sheet name="Planification trop détaillée" sheetId="11" r:id="rId8"/>
@@ -26,18 +26,24 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Sprint 2'!$B$5:$L$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planification!$B$5:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sprint 3'!$B$4:$L$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="200">
   <si>
     <t>Planification globale</t>
   </si>
@@ -537,12 +543,6 @@
     <t xml:space="preserve">Communication entre le Serveur et le Client (envois/réceptions): test  simple </t>
   </si>
   <si>
-    <t>Créer le composant : MainLayout : 
-navbar conditionnelle (visible si connecté)
-, fond d'écran dynamique,
- conteneur principal</t>
-  </si>
-  <si>
     <t>Création de toutes les tables</t>
   </si>
   <si>
@@ -553,6 +553,96 @@
   </si>
   <si>
     <t>Connection avec une session_key unique</t>
+  </si>
+  <si>
+    <t>Créer le composant : MainLayout : navbar conditionnelle, fond d'écran dynamique</t>
+  </si>
+  <si>
+    <t>Ajout useState pour toggle entre login et register sur index.jsx</t>
+  </si>
+  <si>
+    <t>Retirer font-family et intégration dans le CSS global</t>
+  </si>
+  <si>
+    <t>GameAction complété pour envoi du board</t>
+  </si>
+  <si>
+    <t>Ajout des boutons de pool: valider annuler</t>
+  </si>
+  <si>
+    <t>Ajout Double-clic la même case → retour au pool</t>
+  </si>
+  <si>
+    <t>Nouveau composant Panel avec notification et gameMessage</t>
+  </si>
+  <si>
+    <t>Correction couleur button success + changement aspect boutons game.jsx</t>
+  </si>
+  <si>
+    <t>Board vide en début de partie</t>
+  </si>
+  <si>
+    <t>Ajout fonction deplacer piece entre pool et board</t>
+  </si>
+  <si>
+    <t>Ajout fonction créer un random pool et l afficher</t>
+  </si>
+  <si>
+    <t>Client/frontend/game.jsx  ajout grille + fonction cell selected</t>
+  </si>
+  <si>
+    <t>Creation  du pool pour  phase de placement initial</t>
+  </si>
+  <si>
+    <t>GameAction complété pour envoi du board initial</t>
+  </si>
+  <si>
+    <t>Ajout fonction inversion pièce entre board et pool</t>
+  </si>
+  <si>
+    <t>Créer la page lobby</t>
+  </si>
+  <si>
+    <t>Mise à jour game.jsx en fonction des phases de jeu (statut récupéré  toutes les 1 secondes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création de gameService.jsx pour centraliser les emvoi  API de GameAction </t>
+  </si>
+  <si>
+    <t>Création d un component cell</t>
+  </si>
+  <si>
+    <t>Création d un component loading</t>
+  </si>
+  <si>
+    <t>Création d un component piece</t>
+  </si>
+  <si>
+    <t>Mise à jour  aspect game,jsx en fonction  du getGameStatus( ) : afficher le board avec les pieces des 2 joueurs et du tour de jeu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Afficher le tour de jeu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer le composant PlayerInfo  pour afficher les informations des joueurs (noms, avatars, scores,tour)  </t>
+  </si>
+  <si>
+    <t>Implémentation de la logique  ecran combat des pieces</t>
+  </si>
+  <si>
+    <t>Régler l affichage du board selon la phase de jeu suite a mise en place des phases de jeu</t>
+  </si>
+  <si>
+    <t>Ajout des assets des pieces dans dossier src</t>
+  </si>
+  <si>
+    <t>Créer une page administration:gestion des utilisateurs</t>
+  </si>
+  <si>
+    <t>Permettre le drag and drop sur les pieces</t>
+  </si>
+  <si>
+    <t>Importation des svg en tant que Composant pour les pieces</t>
   </si>
 </sst>
 </file>
@@ -603,7 +693,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,8 +724,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -899,51 +1013,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
@@ -1005,7 +1074,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1070,11 +1139,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1087,28 +1151,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="5" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="5" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1117,42 +1227,27 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="48">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1180,6 +1275,347 @@
             <color rgb="FFCCFFFF"/>
           </stop>
         </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -1509,26 +1945,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="42.81640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="2:5" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1542,11 +1978,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="21" t="s">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="61" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="35" t="s">
@@ -1556,11 +1992,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B7" s="18" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="36" t="s">
@@ -1570,11 +2006,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="18" t="s">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="36" t="s">
@@ -1584,11 +2020,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="18" t="s">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="36" t="s">
@@ -1598,11 +2034,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="18" t="s">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="36" t="s">
@@ -1612,11 +2048,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B11" s="18" t="s">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="36" t="s">
@@ -1626,11 +2062,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B12" s="18" t="s">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="36" t="s">
@@ -1640,11 +2076,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B13" s="18" t="s">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="36" t="s">
@@ -1654,11 +2090,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B14" s="18" t="s">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="36" t="s">
@@ -1668,11 +2104,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B15" s="18" t="s">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="36" t="s">
@@ -1682,11 +2118,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B16" s="18" t="s">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="63" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="36" t="s">
@@ -1696,11 +2132,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="18" t="s">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="36" t="s">
@@ -1710,11 +2146,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="18" t="s">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="62" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="36" t="s">
@@ -1724,11 +2160,11 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="18" t="s">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="36" t="s">
@@ -1738,11 +2174,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="18" t="s">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="36" t="s">
@@ -1752,11 +2188,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="18" t="s">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="36" t="s">
@@ -1766,11 +2202,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="18" t="s">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="36" t="s">
@@ -1780,11 +2216,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="18" t="s">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="36" t="s">
@@ -1794,11 +2230,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="18" t="s">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="36" t="s">
@@ -1808,11 +2244,11 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="18" t="s">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="36" t="s">
@@ -1822,11 +2258,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="18" t="s">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D26" s="36" t="s">
@@ -1836,11 +2272,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B27" s="18" t="s">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="60" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="36" t="s">
@@ -1850,11 +2286,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B28" s="18" t="s">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="36" t="s">
@@ -1864,11 +2300,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="18" t="s">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="36" t="s">
@@ -1878,11 +2314,11 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="18" t="s">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="36" t="s">
@@ -1892,11 +2328,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B31" s="18" t="s">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="36" t="s">
@@ -1906,11 +2342,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B32" s="18" t="s">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="36" t="s">
@@ -1920,11 +2356,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B33" s="18" t="s">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="36" t="s">
@@ -1934,11 +2370,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B34" s="18" t="s">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="36" t="s">
@@ -1948,11 +2384,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B35" s="18" t="s">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="36" t="s">
@@ -1962,11 +2398,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B36" s="18" t="s">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="65" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="36" t="s">
@@ -1976,11 +2412,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="22" t="s">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="67" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="37" t="s">
@@ -1990,8 +2426,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D39" s="41" t="s">
         <v>157</v>
       </c>
@@ -2001,6 +2437,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B5:E37" xr:uid="{93133217-C8F5-4788-AEEB-7509B70AEF5D}"/>
+  <conditionalFormatting sqref="B6:B7">
+    <cfRule type="expression" dxfId="47" priority="1">
+      <formula>MAX($E6,$H6,$K6)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D20 D21:D37" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Haute,Moyenne,Basse,"</formula1>
@@ -2020,32 +2462,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
-    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2075,7 +2517,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2129,7 +2571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -2156,7 +2598,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2178,7 +2620,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2205,7 +2647,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2238,7 +2680,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2275,7 +2717,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2312,7 +2754,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2344,7 +2786,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2372,7 +2814,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2399,15 +2841,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2422,101 +2864,101 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="B2:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:M48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.54296875" customWidth="1"/>
-    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.1796875" customWidth="1"/>
-    <col min="10" max="10" width="16.6328125" customWidth="1"/>
-    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.81640625" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B3" s="62" t="s">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:12" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B3" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="64"/>
-    </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="65" t="s">
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="87"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="53">
         <v>46083</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="60" t="s">
+      <c r="G5" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="58">
+      <c r="H5" s="53">
         <v>46090</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="60" t="s">
+      <c r="J5" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="58">
+      <c r="K5" s="53">
         <v>46104</v>
       </c>
-      <c r="L5" s="69" t="s">
+      <c r="L5" s="92" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="66"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="57" t="s">
+    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="89"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="70"/>
-      <c r="G6" s="59" t="s">
+      <c r="F6" s="93"/>
+      <c r="G6" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="59" t="s">
+      <c r="I6" s="93"/>
+      <c r="J6" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="59" t="s">
+      <c r="K6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="70"/>
-    </row>
-    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="L6" s="93"/>
+    </row>
+    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2526,20 +2968,20 @@
       <c r="D7" s="33">
         <v>3.5</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="50">
         <v>100</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="48" t="s">
         <v>158</v>
       </c>
       <c r="G7" s="33"/>
-      <c r="H7" s="55"/>
+      <c r="H7" s="50"/>
       <c r="I7" s="12"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -2558,7 +3000,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -2577,7 +3019,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -2596,7 +3038,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="36" t="s">
         <v>165</v>
       </c>
@@ -2615,7 +3057,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -2634,7 +3076,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -2653,7 +3095,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -2672,7 +3114,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="36" t="s">
         <v>163</v>
       </c>
@@ -2691,7 +3133,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="36" t="s">
         <v>29</v>
       </c>
@@ -2710,7 +3152,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="36" t="s">
         <v>30</v>
       </c>
@@ -2729,7 +3171,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
         <v>161</v>
       </c>
@@ -2748,7 +3190,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="36" t="s">
         <v>162</v>
       </c>
@@ -2767,11 +3209,11 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="B20" s="61" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="36" t="s">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="57" t="s">
         <v>106</v>
       </c>
       <c r="D20" s="31"/>
@@ -2786,7 +3228,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="36" t="s">
         <v>92</v>
       </c>
@@ -2802,12 +3244,12 @@
       <c r="H21" s="40">
         <v>100</v>
       </c>
-      <c r="I21" s="54" t="s">
+      <c r="I21" s="49" t="s">
         <v>159</v>
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
         <v>51</v>
       </c>
@@ -2826,7 +3268,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="36" t="s">
         <v>90</v>
       </c>
@@ -2843,11 +3285,11 @@
         <v>100</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
         <v>74</v>
       </c>
@@ -2866,7 +3308,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
@@ -2885,7 +3327,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="36" t="s">
         <v>93</v>
       </c>
@@ -2902,11 +3344,11 @@
         <v>100</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="36" t="s">
         <v>94</v>
       </c>
@@ -2923,12 +3365,12 @@
         <v>100</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="B28" s="36" t="s">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="77" t="s">
         <v>79</v>
       </c>
       <c r="C28" s="36" t="s">
@@ -2943,13 +3385,13 @@
       <c r="H28" s="40">
         <v>100</v>
       </c>
-      <c r="I28" s="54" t="s">
+      <c r="I28" s="49" t="s">
         <v>160</v>
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="18" t="s">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="77" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="36" t="s">
@@ -2967,28 +3409,28 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="36" t="s">
+    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="81"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="68">
+        <v>2</v>
+      </c>
+      <c r="H30" s="83">
+        <v>100</v>
+      </c>
+      <c r="I30" s="80"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="77" t="s">
         <v>42</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="H30" s="40">
-        <v>100</v>
-      </c>
-      <c r="I30" s="14"/>
-      <c r="L30" s="14"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="36" t="s">
-        <v>43</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>106</v>
@@ -2996,18 +3438,18 @@
       <c r="D31" s="31"/>
       <c r="E31" s="40"/>
       <c r="F31" s="14"/>
-      <c r="G31" s="31">
-        <v>0.75</v>
-      </c>
-      <c r="H31" s="40">
+      <c r="I31" s="14"/>
+      <c r="J31" s="31">
+        <v>1</v>
+      </c>
+      <c r="K31" s="40">
         <v>100</v>
       </c>
-      <c r="I31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="36" t="s">
-        <v>164</v>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="77" t="s">
+        <v>43</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>106</v>
@@ -3015,14 +3457,18 @@
       <c r="D32" s="31"/>
       <c r="E32" s="40"/>
       <c r="F32" s="14"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="40"/>
       <c r="I32" s="14"/>
+      <c r="J32" s="31">
+        <v>1</v>
+      </c>
+      <c r="K32" s="40">
+        <v>100</v>
+      </c>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="36" t="s">
-        <v>168</v>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B33" s="77" t="s">
+        <v>164</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>106</v>
@@ -3030,18 +3476,18 @@
       <c r="D33" s="31"/>
       <c r="E33" s="40"/>
       <c r="F33" s="14"/>
-      <c r="G33" s="31">
-        <v>0.25</v>
-      </c>
-      <c r="H33" s="40">
+      <c r="I33" s="14"/>
+      <c r="J33" s="31">
+        <v>1</v>
+      </c>
+      <c r="K33" s="40">
         <v>100</v>
       </c>
-      <c r="I33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="36" t="s">
-        <v>73</v>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B34" s="77" t="s">
+        <v>167</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>106</v>
@@ -3049,14 +3495,18 @@
       <c r="D34" s="31"/>
       <c r="E34" s="40"/>
       <c r="F34" s="14"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="40"/>
       <c r="I34" s="14"/>
+      <c r="J34" s="31">
+        <v>0.25</v>
+      </c>
+      <c r="K34" s="40">
+        <v>100</v>
+      </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35" s="36" t="s">
-        <v>38</v>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B35" s="77" t="s">
+        <v>73</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>106</v>
@@ -3064,14 +3514,18 @@
       <c r="D35" s="31"/>
       <c r="E35" s="40"/>
       <c r="F35" s="14"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="40"/>
       <c r="I35" s="14"/>
+      <c r="J35" s="31">
+        <v>1</v>
+      </c>
+      <c r="K35" s="40">
+        <v>100</v>
+      </c>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36" s="36" t="s">
-        <v>39</v>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B36" s="77" t="s">
+        <v>38</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>106</v>
@@ -3079,14 +3533,18 @@
       <c r="D36" s="31"/>
       <c r="E36" s="40"/>
       <c r="F36" s="14"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="40"/>
       <c r="I36" s="14"/>
+      <c r="J36" s="31">
+        <v>1</v>
+      </c>
+      <c r="K36" s="40">
+        <v>100</v>
+      </c>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37" s="36" t="s">
-        <v>61</v>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B37" s="77" t="s">
+        <v>39</v>
       </c>
       <c r="C37" s="36" t="s">
         <v>106</v>
@@ -3094,27 +3552,224 @@
       <c r="D37" s="31"/>
       <c r="E37" s="40"/>
       <c r="F37" s="14"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="40"/>
       <c r="I37" s="14"/>
+      <c r="J37" s="31">
+        <v>2</v>
+      </c>
+      <c r="K37" s="40">
+        <v>100</v>
+      </c>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="17"/>
+    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="82" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="81"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="81">
+        <v>1</v>
+      </c>
+      <c r="K38" s="83">
+        <v>100</v>
+      </c>
+      <c r="L38" s="80"/>
+    </row>
+    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="82" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="81"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="81">
+        <v>1</v>
+      </c>
+      <c r="K39" s="83">
+        <v>100</v>
+      </c>
+      <c r="L39" s="80"/>
+    </row>
+    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="82" t="s">
+        <v>179</v>
+      </c>
+      <c r="C40" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="81"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="K40" s="83">
+        <v>100</v>
+      </c>
+      <c r="L40" s="80"/>
+    </row>
+    <row r="41" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="82" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="81"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="80"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="81">
+        <v>1</v>
+      </c>
+      <c r="K41" s="83">
+        <v>100</v>
+      </c>
+      <c r="L41" s="80"/>
+    </row>
+    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="82" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="81"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="80"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="K42" s="83">
+        <v>100</v>
+      </c>
+      <c r="L42" s="80"/>
+    </row>
+    <row r="43" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="82" t="s">
+        <v>176</v>
+      </c>
+      <c r="C43" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="81"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="K43" s="83">
+        <v>100</v>
+      </c>
+      <c r="L43" s="80"/>
+    </row>
+    <row r="44" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="81"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="80"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="81">
+        <v>1</v>
+      </c>
+      <c r="K44" s="83">
+        <v>100</v>
+      </c>
+      <c r="L44" s="80"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B45" s="77" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="31"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="31">
+        <v>0.75</v>
+      </c>
+      <c r="K45" s="40">
+        <v>100</v>
+      </c>
+      <c r="L45" s="14"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B46" s="82" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="71"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71">
+        <v>0.75</v>
+      </c>
+      <c r="K46" s="72">
+        <v>100</v>
+      </c>
+      <c r="L46" s="70"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B47" s="77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="71"/>
+      <c r="E47" s="72"/>
+      <c r="F47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="71">
+        <v>2</v>
+      </c>
+      <c r="K47" s="72">
+        <v>100</v>
+      </c>
+      <c r="L47" s="70"/>
+      <c r="M47" s="69"/>
+    </row>
+    <row r="48" spans="2:13" s="73" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="76"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="75"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="76">
+        <v>1</v>
+      </c>
+      <c r="K48" s="78">
+        <v>100</v>
+      </c>
+      <c r="L48" s="75"/>
     </row>
   </sheetData>
   <autoFilter ref="B5:L6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -3126,20 +3781,83 @@
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="L5:L6"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="7" priority="6">
+  <conditionalFormatting sqref="B45 B47:B1048576 B1:B42">
+    <cfRule type="expression" dxfId="46" priority="28">
       <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="expression" dxfId="6" priority="1">
+  <conditionalFormatting sqref="C49:C1048576 C1:C45">
+    <cfRule type="expression" dxfId="45" priority="23">
       <formula>$C1="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="44" priority="25">
       <formula>$C1="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="43" priority="27">
       <formula>$C1="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47">
+    <cfRule type="expression" dxfId="42" priority="19">
+      <formula>$C47="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="20">
+      <formula>$C47="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="21">
+      <formula>$C47="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48">
+    <cfRule type="expression" dxfId="39" priority="8">
+      <formula>$C48="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="9">
+      <formula>$C48="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="10">
+      <formula>$C48="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C42:C48">
+    <cfRule type="expression" dxfId="36" priority="12">
+      <formula>$C42="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="13">
+      <formula>$C42="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="14">
+      <formula>$C42="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B48 B45 B31:B42">
+    <cfRule type="expression" dxfId="33" priority="30">
+      <formula>MAX($E31,$K31,#REF!)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" dxfId="32" priority="7">
+      <formula>MAX($E43,$H43,$K43)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" dxfId="31" priority="32">
+      <formula>MAX($E46,$H46,$K46)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" dxfId="30" priority="38">
+      <formula>MAX($E46,$K46,#REF!)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" dxfId="29" priority="6">
+      <formula>MAX($E46,$H46,$K46)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="expression" dxfId="28" priority="1">
+      <formula>MAX($E30,$K30,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3148,26 +3866,868 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A181AE-6DCE-4F2E-9BC3-78C1EB9A33C7}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
+  <dimension ref="B1:M43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B1" s="85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="87"/>
+    </row>
+    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.4">
+      <c r="B4" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="53">
+        <v>46111</v>
+      </c>
+      <c r="F4" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="53">
+        <v>46125</v>
+      </c>
+      <c r="I4" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="53">
+        <v>46132</v>
+      </c>
+      <c r="L4" s="92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="89"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="93"/>
+      <c r="G5" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="93"/>
+      <c r="J5" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="93"/>
+    </row>
+    <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="82" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="83">
+        <v>100</v>
+      </c>
+      <c r="F6" s="80"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="80"/>
+      <c r="L6" s="80"/>
+    </row>
+    <row r="7" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="82" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="83">
+        <v>100</v>
+      </c>
+      <c r="F7" s="80"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="80"/>
+      <c r="L7" s="80"/>
+    </row>
+    <row r="8" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="82" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="E8" s="83">
+        <v>100</v>
+      </c>
+      <c r="F8" s="80"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="80"/>
+      <c r="L8" s="80"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="82" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="83">
+        <v>100</v>
+      </c>
+      <c r="F9" s="80"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="80"/>
+    </row>
+    <row r="10" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="82" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="E10" s="83">
+        <v>100</v>
+      </c>
+      <c r="F10" s="80"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="80"/>
+      <c r="L10" s="80"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="82" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="31">
+        <v>1.5</v>
+      </c>
+      <c r="E11" s="83">
+        <v>100</v>
+      </c>
+      <c r="F11" s="80"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="79"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="82" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="31">
+        <v>1</v>
+      </c>
+      <c r="E12" s="83">
+        <v>100</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="79"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="82" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="E13" s="83">
+        <v>100</v>
+      </c>
+      <c r="F13" s="80"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="79"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="82" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="31">
+        <v>1</v>
+      </c>
+      <c r="E14" s="83">
+        <v>100</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="79"/>
+    </row>
+    <row r="15" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="82" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="81"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="80"/>
+      <c r="L15" s="80"/>
+    </row>
+    <row r="16" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="82" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="81">
+        <v>0.05</v>
+      </c>
+      <c r="E16" s="83">
+        <v>100</v>
+      </c>
+      <c r="F16" s="80"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="80"/>
+      <c r="L16" s="80"/>
+    </row>
+    <row r="17" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="82" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="81"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="80"/>
+      <c r="L17" s="80"/>
+    </row>
+    <row r="18" spans="2:13" s="79" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="81"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="80"/>
+      <c r="L18" s="80"/>
+    </row>
+    <row r="19" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="82" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="81"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="80"/>
+      <c r="L19" s="80"/>
+    </row>
+    <row r="20" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="82" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="81"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="80"/>
+      <c r="L20" s="80"/>
+    </row>
+    <row r="21" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="81"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="80"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="80"/>
+      <c r="L22" s="80"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B23" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="81"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="79"/>
+    </row>
+    <row r="24" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="82" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="80"/>
+      <c r="L24" s="80"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B25" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="81"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="79"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B26" s="82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="81"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="80"/>
+      <c r="M26" s="79"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B27" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="81"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="79"/>
+      <c r="K27" s="79"/>
+      <c r="L27" s="80"/>
+      <c r="M27" s="79"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B28" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="81"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="80"/>
+      <c r="M28" s="79"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B29" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="79"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="81"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="79"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B31" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="81"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="79"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="81"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="79"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B33" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="81"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="80"/>
+      <c r="M33" s="79"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B34" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="81"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="79"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B35" s="82" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="81"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="80"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="80"/>
+      <c r="M35" s="79"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B36" s="82"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="79"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="80"/>
+      <c r="M36" s="79"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B37" s="82"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="79"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="80"/>
+      <c r="M37" s="79"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B38" s="82"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="80"/>
+      <c r="M38" s="79"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B39" s="82"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="80"/>
+      <c r="M39" s="79"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B40" s="82"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="79"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B41" s="82"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="79"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="80"/>
+      <c r="M41" s="79"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B42" s="82"/>
+      <c r="C42" s="82"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="79"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="80"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B43" s="82"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="80"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B4:L5" xr:uid="{2EE69061-1192-400C-B500-1B4897FD0585}"/>
+  <mergeCells count="6">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="L4:L5"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="B4:B18 B25:B43">
+    <cfRule type="expression" dxfId="27" priority="28">
+      <formula>MAX($E4,$H4,$K4)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C5 C9:C43">
+    <cfRule type="expression" dxfId="26" priority="25">
+      <formula>$C4="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="26">
+      <formula>$C4="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="27">
+      <formula>$C4="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>MAX($E1,$H1,$K1)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="expression" dxfId="22" priority="21">
+      <formula>$C1="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>$C1="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="23">
+      <formula>$C1="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:B10">
+    <cfRule type="expression" dxfId="19" priority="17">
+      <formula>MAX($E9,$H9,$K9)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="18" priority="11">
+      <formula>MAX($E12,$H12,$K12)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="expression" dxfId="17" priority="10">
+      <formula>MAX($E11,$H11,$K11)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="expression" dxfId="16" priority="9">
+      <formula>MAX($E11,$H11,$K11)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="expression" dxfId="15" priority="64">
+      <formula>MAX(#REF!,#REF!,#REF!)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B12">
+    <cfRule type="expression" dxfId="14" priority="6">
+      <formula>MAX($E6,$H6,$K6)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:C8">
+    <cfRule type="expression" dxfId="13" priority="3">
+      <formula>$C6="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>$C6="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="5">
+      <formula>$C6="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B24">
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>MAX($E19,$H19,$K19)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B24">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>MAX($E19,$H19,$K19)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE02E41-CCB4-4A52-8A11-897838372758}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="70.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" customWidth="1"/>
-    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -3181,590 +4741,157 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A181AE-6DCE-4F2E-9BC3-78C1EB9A33C7}">
-  <sheetPr>
-    <tabColor theme="8"/>
-  </sheetPr>
-  <dimension ref="B1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="21.1796875" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" ht="46" x14ac:dyDescent="1">
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.5">
-      <c r="B3" s="7"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="48">
-        <v>46111</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="48">
-        <v>46125</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="48">
-        <v>46132</v>
-      </c>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="50"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="51"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="18"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="18"/>
-      <c r="I6" s="14"/>
-      <c r="L6" s="14"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="51"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="18"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="18"/>
-      <c r="I7" s="14"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="51"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="18"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="18"/>
-      <c r="I8" s="14"/>
-      <c r="L8" s="14"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="51"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="18"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="18"/>
-      <c r="I9" s="14"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="51"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="18"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="14"/>
-      <c r="L10" s="14"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="51"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="18"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="18"/>
-      <c r="I11" s="14"/>
-      <c r="L11" s="14"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="51"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="18"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="18"/>
-      <c r="I12" s="14"/>
-      <c r="L12" s="14"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="51"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="18"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="18"/>
-      <c r="I13" s="14"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="51"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="18"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="18"/>
-      <c r="I14" s="14"/>
-      <c r="L14" s="14"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="51"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="18"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="14"/>
-      <c r="L15" s="14"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="51"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="18"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="18"/>
-      <c r="I16" s="14"/>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="51"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="18"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="18"/>
-      <c r="I17" s="14"/>
-      <c r="L17" s="14"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" s="51"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="18"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="18"/>
-      <c r="I18" s="14"/>
-      <c r="L18" s="14"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B19" s="51"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="18"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="18"/>
-      <c r="I19" s="14"/>
-      <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B20" s="51"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="18"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="18"/>
-      <c r="I20" s="14"/>
-      <c r="L20" s="14"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="51"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="18"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="18"/>
-      <c r="I21" s="14"/>
-      <c r="L21" s="14"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="51"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="18"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="18"/>
-      <c r="I22" s="14"/>
-      <c r="L22" s="14"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="51"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="18"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="18"/>
-      <c r="I23" s="14"/>
-      <c r="L23" s="14"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="51"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="18"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="18"/>
-      <c r="I24" s="14"/>
-      <c r="L24" s="14"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="51"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="18"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="18"/>
-      <c r="I25" s="14"/>
-      <c r="L25" s="14"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" s="51"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="18"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="18"/>
-      <c r="I26" s="14"/>
-      <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="51"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="18"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="18"/>
-      <c r="I27" s="14"/>
-      <c r="L27" s="14"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="51"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="18"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="18"/>
-      <c r="I28" s="14"/>
-      <c r="L28" s="14"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29" s="51"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="18"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="18"/>
-      <c r="I29" s="14"/>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="51"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="18"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="18"/>
-      <c r="I30" s="14"/>
-      <c r="L30" s="14"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="51"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="18"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="18"/>
-      <c r="I31" s="14"/>
-      <c r="L31" s="14"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32" s="51"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="18"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="18"/>
-      <c r="I32" s="14"/>
-      <c r="L32" s="14"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33" s="51"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="18"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="18"/>
-      <c r="I33" s="14"/>
-      <c r="L33" s="14"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34" s="51"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="18"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="18"/>
-      <c r="I34" s="14"/>
-      <c r="L34" s="14"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35" s="51"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="18"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="18"/>
-      <c r="I35" s="14"/>
-      <c r="L35" s="14"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36" s="51"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="18"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="18"/>
-      <c r="I36" s="14"/>
-      <c r="L36" s="14"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37" s="51"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="18"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="18"/>
-      <c r="I37" s="14"/>
-      <c r="L37" s="14"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38" s="51"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="18"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="18"/>
-      <c r="I38" s="14"/>
-      <c r="L38" s="14"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39" s="51"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="18"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="18"/>
-      <c r="I39" s="14"/>
-      <c r="L39" s="14"/>
-    </row>
-    <row r="40" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="52"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="17"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B5:B40">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>COUNTIF(D5:L5,100%)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>COUNTIF(D5:L5,100%)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3774,18 +4901,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -3809,7 +4936,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -3853,7 +4980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -3875,7 +5002,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3893,7 +5020,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -3911,7 +5038,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3929,7 +5056,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -3947,7 +5074,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -3965,7 +5092,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -3983,7 +5110,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -4001,7 +5128,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4019,7 +5146,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -4037,7 +5164,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -4055,7 +5182,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -4073,7 +5200,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -4091,7 +5218,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -4109,7 +5236,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4127,7 +5254,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -4145,7 +5272,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -4163,7 +5290,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -4181,7 +5308,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4199,7 +5326,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -4217,7 +5344,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -4235,7 +5362,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4253,7 +5380,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4271,7 +5398,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -4289,7 +5416,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
@@ -4307,7 +5434,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -4325,7 +5452,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -4343,7 +5470,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -4361,7 +5488,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4379,7 +5506,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -4401,47 +5528,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4452,539 +5579,569 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="B2:O73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:O39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="51.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+      <c r="B2" s="94" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
-      <c r="B4" s="7"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+    </row>
+    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E5" s="53">
         <v>46139</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="F5" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="48">
+      <c r="H5" s="53">
         <v>46146</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="I5" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="48">
+      <c r="K5" s="53">
         <v>46153</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="4" t="s">
+      <c r="L5" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="48">
+      <c r="N5" s="53">
         <v>46161</v>
       </c>
-      <c r="O4" s="6"/>
-    </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="O5" s="92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="89"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="50"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="12"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="51"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="18"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="18"/>
-      <c r="I7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="O7" s="14"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="51"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="18"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="93"/>
+      <c r="J6" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="93"/>
+      <c r="M6" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="93"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="14"/>
-      <c r="G8" s="18"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B9" s="51"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="18"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="40"/>
       <c r="F9" s="14"/>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="51"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="18"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="40"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="18"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="51"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="18"/>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="40"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="18"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="40"/>
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="51"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="18"/>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="18"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="40"/>
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="51"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="18"/>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="40"/>
       <c r="F13" s="14"/>
-      <c r="G13" s="18"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="40"/>
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="51"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="49"/>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="18"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="51"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="18"/>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="18"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="51"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="18"/>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="40"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="18"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="40"/>
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="51"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="18"/>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="14"/>
-      <c r="G17" s="18"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="40"/>
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B18" s="51"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="18"/>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="18"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="40"/>
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="51"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="18"/>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="40"/>
       <c r="F19" s="14"/>
-      <c r="G19" s="18"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="40"/>
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="51"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="18"/>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" s="56"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="18"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="40"/>
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B21" s="51"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="18"/>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="40"/>
       <c r="F21" s="14"/>
-      <c r="G21" s="18"/>
-      <c r="I21" s="14"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="49"/>
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="51"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="18"/>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="18"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B23" s="51"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="18"/>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="18"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="40"/>
       <c r="I23" s="14"/>
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="51"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="18"/>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="14"/>
-      <c r="G24" s="18"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="40"/>
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="51"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="18"/>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="40"/>
       <c r="F25" s="14"/>
-      <c r="G25" s="18"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="40"/>
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="51"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="18"/>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="18"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="40"/>
       <c r="I26" s="14"/>
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B27" s="51"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="18"/>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="40"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="18"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="40"/>
       <c r="I27" s="14"/>
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="51"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="18"/>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="40"/>
       <c r="F28" s="14"/>
-      <c r="G28" s="18"/>
-      <c r="I28" s="14"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="49"/>
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="51"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="18"/>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B29" s="18"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="14"/>
-      <c r="G29" s="18"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="40"/>
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B30" s="51"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="18"/>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="18"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="40"/>
       <c r="I30" s="14"/>
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="51"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="18"/>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="40"/>
       <c r="F31" s="14"/>
-      <c r="G31" s="18"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="40"/>
       <c r="I31" s="14"/>
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B32" s="51"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="18"/>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="14"/>
-      <c r="G32" s="18"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="40"/>
       <c r="I32" s="14"/>
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="51"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="18"/>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="40"/>
       <c r="F33" s="14"/>
-      <c r="G33" s="18"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="40"/>
       <c r="I33" s="14"/>
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="51"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="18"/>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="40"/>
       <c r="F34" s="14"/>
-      <c r="G34" s="18"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="40"/>
       <c r="I34" s="14"/>
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="51"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="18"/>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="14"/>
-      <c r="G35" s="18"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="40"/>
       <c r="I35" s="14"/>
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B36" s="51"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="18"/>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="40"/>
       <c r="F36" s="14"/>
-      <c r="G36" s="18"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="40"/>
       <c r="I36" s="14"/>
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="51"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="18"/>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="40"/>
       <c r="F37" s="14"/>
-      <c r="G37" s="18"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="40"/>
       <c r="I37" s="14"/>
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="51"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="18"/>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="40"/>
       <c r="F38" s="14"/>
-      <c r="G38" s="18"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="40"/>
       <c r="I38" s="14"/>
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B39" s="51"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="18"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="18"/>
-      <c r="I39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="O39" s="14"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="51"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="18"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="18"/>
-      <c r="I40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="O40" s="14"/>
-    </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="52"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="17"/>
-    </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="D64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" t="s">
-        <v>89</v>
-      </c>
-      <c r="J64" s="5"/>
-      <c r="M64" s="5"/>
-    </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="D65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" t="s">
-        <v>89</v>
-      </c>
-      <c r="J65" s="5"/>
-      <c r="M65" s="5"/>
-    </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="D67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" t="s">
-        <v>89</v>
-      </c>
-      <c r="J67" s="5"/>
-      <c r="M67" s="5"/>
-    </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="D68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" t="s">
-        <v>89</v>
-      </c>
-      <c r="M68" s="5"/>
-    </row>
-    <row r="71" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="H71" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="72" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="K72" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="D73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" t="s">
-        <v>89</v>
-      </c>
-      <c r="M73" s="5"/>
+    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B6:B41">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>COUNTIF(D6:L6,100%)=0</formula>
+  <mergeCells count="7">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="O5:O6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5:B36">
+    <cfRule type="expression" dxfId="8" priority="12">
+      <formula>MAX($E5,$H5,$K5)=100</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>COUNTIF(D6:L6,100%)&gt;0</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C36">
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>$C5="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="10">
+      <formula>$C5="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="11">
+      <formula>$C5="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>MAX($E2,$H2,$K2)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:C39">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$C37="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$C37="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>$C37="Eddy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37:B39">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MAX($E37,$H37,$K37)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4997,28 +6154,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="93.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="2" max="2" width="93.21875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="42.81640625" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -5035,7 +6192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5048,7 +6205,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -5061,7 +6218,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -5074,7 +6231,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5087,7 +6244,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -5100,7 +6257,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -5113,7 +6270,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -5126,7 +6283,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -5139,7 +6296,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -5152,7 +6309,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -5165,7 +6322,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -5178,7 +6335,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -5191,7 +6348,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -5204,7 +6361,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -5217,7 +6374,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -5230,7 +6387,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -5243,7 +6400,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -5256,7 +6413,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -5269,7 +6426,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -5282,7 +6439,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -5295,7 +6452,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -5308,7 +6465,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -5321,7 +6478,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -5334,7 +6491,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5347,7 +6504,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -5360,7 +6517,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -5373,7 +6530,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -5386,7 +6543,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -5399,7 +6556,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -5412,7 +6569,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5425,7 +6582,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -5438,7 +6595,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -5451,7 +6608,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -5464,7 +6621,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -5477,7 +6634,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -5490,7 +6647,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -5503,7 +6660,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -5516,7 +6673,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -5529,7 +6686,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -5542,7 +6699,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -5555,7 +6712,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -5568,7 +6725,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -5581,7 +6738,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -5594,7 +6751,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -5607,7 +6764,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -5620,7 +6777,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -5633,7 +6790,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -5646,7 +6803,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -5659,7 +6816,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -5672,7 +6829,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -5685,7 +6842,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -5698,7 +6855,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -5711,7 +6868,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -5724,7 +6881,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -5737,7 +6894,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -5750,7 +6907,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -5763,7 +6920,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -5776,7 +6933,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5789,7 +6946,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -5802,7 +6959,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -5813,7 +6970,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -5824,7 +6981,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -5835,7 +6992,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -5846,7 +7003,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -5857,7 +7014,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -5868,7 +7025,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -5879,7 +7036,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -5890,7 +7047,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -5901,7 +7058,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -5912,7 +7069,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -5923,182 +7080,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0B622C-6B22-4FCB-A772-0DFA05757C5B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7850D64E-5424-4209-B7DC-D8BA41625DDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -28,22 +28,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sprint 3'!$B$4:$L$5</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="204">
   <si>
     <t>Planification globale</t>
   </si>
@@ -643,6 +638,18 @@
   </si>
   <si>
     <t>Importation des svg en tant que Composant pour les pieces</t>
+  </si>
+  <si>
+    <t>Implémentation du chat entre joueurs: création de la base de donnée</t>
+  </si>
+  <si>
+    <t>Implémenter le MCTS</t>
+  </si>
+  <si>
+    <t>Créer table pour les chats entre joueurs</t>
+  </si>
+  <si>
+    <t>Créer la classe Piece/BeliefPiece</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1239,11 +1246,48 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="68">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1282,6 +1326,143 @@
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color rgb="FFFCFDCF"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFCCFFFF"/>
+          </stop>
+        </gradientFill>
       </fill>
     </dxf>
     <dxf>
@@ -1945,26 +2126,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1978,7 +2159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="58" t="s">
         <v>152</v>
       </c>
@@ -1992,7 +2173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="62" t="s">
         <v>122</v>
       </c>
@@ -2006,7 +2187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="63" t="s">
         <v>123</v>
       </c>
@@ -2020,7 +2201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="63" t="s">
         <v>124</v>
       </c>
@@ -2034,7 +2215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="63" t="s">
         <v>125</v>
       </c>
@@ -2048,7 +2229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="63" t="s">
         <v>127</v>
       </c>
@@ -2062,7 +2243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="63" t="s">
         <v>128</v>
       </c>
@@ -2076,7 +2257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="63" t="s">
         <v>129</v>
       </c>
@@ -2090,7 +2271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="63" t="s">
         <v>156</v>
       </c>
@@ -2104,7 +2285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="63" t="s">
         <v>132</v>
       </c>
@@ -2118,7 +2299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="63" t="s">
         <v>133</v>
       </c>
@@ -2132,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="63" t="s">
         <v>135</v>
       </c>
@@ -2146,7 +2327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="63" t="s">
         <v>141</v>
       </c>
@@ -2160,7 +2341,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="59" t="s">
         <v>130</v>
       </c>
@@ -2174,7 +2355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="59" t="s">
         <v>131</v>
       </c>
@@ -2188,7 +2369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="59" t="s">
         <v>136</v>
       </c>
@@ -2202,7 +2383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="59" t="s">
         <v>137</v>
       </c>
@@ -2216,7 +2397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="59" t="s">
         <v>138</v>
       </c>
@@ -2230,7 +2411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="59" t="s">
         <v>140</v>
       </c>
@@ -2244,7 +2425,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="59" t="s">
         <v>144</v>
       </c>
@@ -2258,7 +2439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="59" t="s">
         <v>145</v>
       </c>
@@ -2272,7 +2453,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="59" t="s">
         <v>146</v>
       </c>
@@ -2286,7 +2467,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="64" t="s">
         <v>139</v>
       </c>
@@ -2300,7 +2481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="64" t="s">
         <v>142</v>
       </c>
@@ -2314,7 +2495,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="64" t="s">
         <v>134</v>
       </c>
@@ -2328,7 +2509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="64" t="s">
         <v>143</v>
       </c>
@@ -2342,7 +2523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="64" t="s">
         <v>147</v>
       </c>
@@ -2356,7 +2537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="64" t="s">
         <v>148</v>
       </c>
@@ -2370,7 +2551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="64" t="s">
         <v>149</v>
       </c>
@@ -2384,7 +2565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="64" t="s">
         <v>150</v>
       </c>
@@ -2398,7 +2579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="64" t="s">
         <v>151</v>
       </c>
@@ -2412,7 +2593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="66" t="s">
         <v>126</v>
       </c>
@@ -2426,8 +2607,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D39" s="41" t="s">
         <v>157</v>
       </c>
@@ -2439,7 +2620,7 @@
   </sheetData>
   <autoFilter ref="B5:E37" xr:uid="{93133217-C8F5-4788-AEEB-7509B70AEF5D}"/>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>MAX($E6,$H6,$K6)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2462,32 +2643,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2517,7 +2698,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2571,7 +2752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -2598,7 +2779,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2620,7 +2801,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2647,7 +2828,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2680,7 +2861,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2717,7 +2898,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2754,7 +2935,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2786,7 +2967,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2814,7 +2995,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2841,15 +3022,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2865,24 +3046,24 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B2:M48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="74" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
       <c r="B3" s="85" t="s">
         <v>6</v>
       </c>
@@ -2897,8 +3078,8 @@
       <c r="K3" s="86"/>
       <c r="L3" s="87"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="88" t="s">
         <v>1</v>
       </c>
@@ -2933,7 +3114,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="89"/>
       <c r="C6" s="91"/>
       <c r="D6" s="52" t="s">
@@ -2958,7 +3139,7 @@
       </c>
       <c r="L6" s="93"/>
     </row>
-    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -2981,7 +3162,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -3000,7 +3181,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -3019,7 +3200,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -3038,7 +3219,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36" t="s">
         <v>165</v>
       </c>
@@ -3057,7 +3238,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -3076,7 +3257,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -3095,7 +3276,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -3114,7 +3295,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36" t="s">
         <v>163</v>
       </c>
@@ -3133,7 +3314,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
         <v>29</v>
       </c>
@@ -3152,7 +3333,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36" t="s">
         <v>30</v>
       </c>
@@ -3171,7 +3352,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
         <v>161</v>
       </c>
@@ -3190,7 +3371,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36" t="s">
         <v>162</v>
       </c>
@@ -3209,7 +3390,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="56" t="s">
         <v>170</v>
       </c>
@@ -3228,7 +3409,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="36" t="s">
         <v>92</v>
       </c>
@@ -3249,7 +3430,7 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36" t="s">
         <v>51</v>
       </c>
@@ -3268,7 +3449,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36" t="s">
         <v>90</v>
       </c>
@@ -3289,7 +3470,7 @@
       </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36" t="s">
         <v>74</v>
       </c>
@@ -3308,7 +3489,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
@@ -3327,7 +3508,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36" t="s">
         <v>93</v>
       </c>
@@ -3348,7 +3529,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="36" t="s">
         <v>94</v>
       </c>
@@ -3369,7 +3550,7 @@
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="77" t="s">
         <v>79</v>
       </c>
@@ -3390,7 +3571,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="77" t="s">
         <v>76</v>
       </c>
@@ -3409,7 +3590,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B30" s="82" t="s">
         <v>185</v>
       </c>
@@ -3428,7 +3609,7 @@
       <c r="I30" s="80"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="77" t="s">
         <v>42</v>
       </c>
@@ -3447,7 +3628,7 @@
       </c>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="77" t="s">
         <v>43</v>
       </c>
@@ -3466,7 +3647,7 @@
       </c>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="77" t="s">
         <v>164</v>
       </c>
@@ -3485,7 +3666,7 @@
       </c>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="77" t="s">
         <v>167</v>
       </c>
@@ -3504,7 +3685,7 @@
       </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="77" t="s">
         <v>73</v>
       </c>
@@ -3523,7 +3704,7 @@
       </c>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="77" t="s">
         <v>38</v>
       </c>
@@ -3542,7 +3723,7 @@
       </c>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="77" t="s">
         <v>39</v>
       </c>
@@ -3561,7 +3742,7 @@
       </c>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B38" s="82" t="s">
         <v>181</v>
       </c>
@@ -3580,7 +3761,7 @@
       </c>
       <c r="L38" s="80"/>
     </row>
-    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B39" s="82" t="s">
         <v>182</v>
       </c>
@@ -3599,7 +3780,7 @@
       </c>
       <c r="L39" s="80"/>
     </row>
-    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
         <v>179</v>
       </c>
@@ -3618,7 +3799,7 @@
       </c>
       <c r="L40" s="80"/>
     </row>
-    <row r="41" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B41" s="82" t="s">
         <v>180</v>
       </c>
@@ -3637,7 +3818,7 @@
       </c>
       <c r="L41" s="80"/>
     </row>
-    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B42" s="82" t="s">
         <v>177</v>
       </c>
@@ -3656,7 +3837,7 @@
       </c>
       <c r="L42" s="80"/>
     </row>
-    <row r="43" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B43" s="82" t="s">
         <v>176</v>
       </c>
@@ -3675,7 +3856,7 @@
       </c>
       <c r="L43" s="80"/>
     </row>
-    <row r="44" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B44" s="77" t="s">
         <v>172</v>
       </c>
@@ -3694,7 +3875,7 @@
       </c>
       <c r="L44" s="80"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="77" t="s">
         <v>171</v>
       </c>
@@ -3713,7 +3894,7 @@
       </c>
       <c r="L45" s="14"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="82" t="s">
         <v>175</v>
       </c>
@@ -3732,7 +3913,7 @@
       </c>
       <c r="L46" s="70"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="77" t="s">
         <v>183</v>
       </c>
@@ -3752,7 +3933,7 @@
       <c r="L47" s="70"/>
       <c r="M47" s="69"/>
     </row>
-    <row r="48" spans="2:13" s="73" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B48" s="74" t="s">
         <v>174</v>
       </c>
@@ -3782,81 +3963,81 @@
     <mergeCell ref="L5:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B45 B47:B1048576 B1:B42">
-    <cfRule type="expression" dxfId="46" priority="28">
+    <cfRule type="expression" dxfId="66" priority="28">
       <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C49:C1048576 C1:C45">
-    <cfRule type="expression" dxfId="45" priority="23">
+    <cfRule type="expression" dxfId="65" priority="23">
       <formula>$C1="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="25">
+    <cfRule type="expression" dxfId="64" priority="25">
       <formula>$C1="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="27">
+    <cfRule type="expression" dxfId="63" priority="27">
       <formula>$C1="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="expression" dxfId="42" priority="19">
+    <cfRule type="expression" dxfId="62" priority="19">
       <formula>$C47="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="20">
+    <cfRule type="expression" dxfId="61" priority="20">
       <formula>$C47="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="21">
+    <cfRule type="expression" dxfId="60" priority="21">
       <formula>$C47="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
-    <cfRule type="expression" dxfId="39" priority="8">
+    <cfRule type="expression" dxfId="59" priority="8">
       <formula>$C48="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="9">
+    <cfRule type="expression" dxfId="58" priority="9">
       <formula>$C48="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="10">
+    <cfRule type="expression" dxfId="57" priority="10">
       <formula>$C48="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42:C48">
-    <cfRule type="expression" dxfId="36" priority="12">
+    <cfRule type="expression" dxfId="56" priority="12">
       <formula>$C42="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="13">
+    <cfRule type="expression" dxfId="55" priority="13">
       <formula>$C42="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="14">
+    <cfRule type="expression" dxfId="54" priority="14">
       <formula>$C42="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:B48 B45 B31:B42">
-    <cfRule type="expression" dxfId="33" priority="30">
+    <cfRule type="expression" dxfId="53" priority="30">
       <formula>MAX($E31,$K31,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="32" priority="7">
+    <cfRule type="expression" dxfId="52" priority="7">
       <formula>MAX($E43,$H43,$K43)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" dxfId="31" priority="32">
+    <cfRule type="expression" dxfId="51" priority="32">
       <formula>MAX($E46,$H46,$K46)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" dxfId="30" priority="38">
+    <cfRule type="expression" dxfId="50" priority="38">
       <formula>MAX($E46,$K46,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" dxfId="29" priority="6">
+    <cfRule type="expression" dxfId="49" priority="6">
       <formula>MAX($E46,$H46,$K46)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>MAX($E30,$K30,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3870,24 +4051,24 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B1:M43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:M60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="21.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="11" max="11" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="2:13" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
       <c r="B1" s="85" t="s">
         <v>16</v>
       </c>
@@ -3902,8 +4083,8 @@
       <c r="K1" s="86"/>
       <c r="L1" s="87"/>
     </row>
-    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="88" t="s">
         <v>1</v>
       </c>
@@ -3938,7 +4119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="89"/>
       <c r="C5" s="91"/>
       <c r="D5" s="52" t="s">
@@ -3963,7 +4144,7 @@
       </c>
       <c r="L5" s="93"/>
     </row>
-    <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B6" s="82" t="s">
         <v>188</v>
       </c>
@@ -3982,7 +4163,7 @@
       <c r="I6" s="80"/>
       <c r="L6" s="80"/>
     </row>
-    <row r="7" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B7" s="82" t="s">
         <v>189</v>
       </c>
@@ -4001,7 +4182,7 @@
       <c r="I7" s="80"/>
       <c r="L7" s="80"/>
     </row>
-    <row r="8" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B8" s="82" t="s">
         <v>190</v>
       </c>
@@ -4020,7 +4201,7 @@
       <c r="I8" s="80"/>
       <c r="L8" s="80"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="82" t="s">
         <v>173</v>
       </c>
@@ -4041,7 +4222,7 @@
       <c r="K9" s="79"/>
       <c r="L9" s="80"/>
     </row>
-    <row r="10" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B10" s="82" t="s">
         <v>187</v>
       </c>
@@ -4060,7 +4241,7 @@
       <c r="I10" s="80"/>
       <c r="L10" s="80"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="82" t="s">
         <v>186</v>
       </c>
@@ -4082,7 +4263,7 @@
       <c r="L11" s="80"/>
       <c r="M11" s="79"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
         <v>178</v>
       </c>
@@ -4102,7 +4283,7 @@
       <c r="L12" s="14"/>
       <c r="M12" s="79"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="82" t="s">
         <v>184</v>
       </c>
@@ -4124,7 +4305,7 @@
       <c r="L13" s="80"/>
       <c r="M13" s="79"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="82" t="s">
         <v>195</v>
       </c>
@@ -4144,7 +4325,7 @@
       <c r="L14" s="14"/>
       <c r="M14" s="79"/>
     </row>
-    <row r="15" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B15" s="82" t="s">
         <v>197</v>
       </c>
@@ -4159,7 +4340,7 @@
       <c r="I15" s="80"/>
       <c r="L15" s="80"/>
     </row>
-    <row r="16" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B16" s="82" t="s">
         <v>196</v>
       </c>
@@ -4178,7 +4359,7 @@
       <c r="I16" s="80"/>
       <c r="L16" s="80"/>
     </row>
-    <row r="17" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B17" s="82" t="s">
         <v>199</v>
       </c>
@@ -4193,7 +4374,7 @@
       <c r="I17" s="80"/>
       <c r="L17" s="80"/>
     </row>
-    <row r="18" spans="2:13" s="79" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" s="79" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="B18" s="84" t="s">
         <v>191</v>
       </c>
@@ -4208,7 +4389,7 @@
       <c r="I18" s="80"/>
       <c r="L18" s="80"/>
     </row>
-    <row r="19" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B19" s="82" t="s">
         <v>193</v>
       </c>
@@ -4223,7 +4404,7 @@
       <c r="I19" s="80"/>
       <c r="L19" s="80"/>
     </row>
-    <row r="20" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B20" s="82" t="s">
         <v>192</v>
       </c>
@@ -4238,7 +4419,7 @@
       <c r="I20" s="80"/>
       <c r="L20" s="80"/>
     </row>
-    <row r="21" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B21" s="82" t="s">
         <v>54</v>
       </c>
@@ -4253,7 +4434,7 @@
       <c r="I21" s="80"/>
       <c r="L21" s="80"/>
     </row>
-    <row r="22" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B22" s="82" t="s">
         <v>72</v>
       </c>
@@ -4268,7 +4449,7 @@
       <c r="I22" s="80"/>
       <c r="L22" s="80"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="82" t="s">
         <v>91</v>
       </c>
@@ -4286,7 +4467,7 @@
       <c r="L23" s="80"/>
       <c r="M23" s="79"/>
     </row>
-    <row r="24" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
         <v>194</v>
       </c>
@@ -4301,7 +4482,7 @@
       <c r="I24" s="80"/>
       <c r="L24" s="80"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="82" t="s">
         <v>54</v>
       </c>
@@ -4319,7 +4500,7 @@
       <c r="L25" s="80"/>
       <c r="M25" s="79"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="82" t="s">
         <v>46</v>
       </c>
@@ -4337,7 +4518,7 @@
       <c r="L26" s="80"/>
       <c r="M26" s="79"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="82" t="s">
         <v>45</v>
       </c>
@@ -4355,7 +4536,7 @@
       <c r="L27" s="80"/>
       <c r="M27" s="79"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="82" t="s">
         <v>41</v>
       </c>
@@ -4373,7 +4554,7 @@
       <c r="L28" s="80"/>
       <c r="M28" s="79"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="82" t="s">
         <v>53</v>
       </c>
@@ -4391,7 +4572,7 @@
       <c r="L29" s="80"/>
       <c r="M29" s="79"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B30" s="82" t="s">
         <v>57</v>
       </c>
@@ -4409,7 +4590,7 @@
       <c r="L30" s="80"/>
       <c r="M30" s="79"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
         <v>71</v>
       </c>
@@ -4427,7 +4608,7 @@
       <c r="L31" s="80"/>
       <c r="M31" s="79"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="82" t="s">
         <v>114</v>
       </c>
@@ -4445,7 +4626,7 @@
       <c r="L32" s="80"/>
       <c r="M32" s="79"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="82" t="s">
         <v>70</v>
       </c>
@@ -4463,7 +4644,7 @@
       <c r="L33" s="80"/>
       <c r="M33" s="79"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="82" t="s">
         <v>56</v>
       </c>
@@ -4481,7 +4662,7 @@
       <c r="L34" s="80"/>
       <c r="M34" s="79"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="82" t="s">
         <v>198</v>
       </c>
@@ -4499,11 +4680,19 @@
       <c r="L35" s="80"/>
       <c r="M35" s="79"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="82"/>
-      <c r="C36" s="82"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="83"/>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="83">
+        <v>100</v>
+      </c>
       <c r="F36" s="80"/>
       <c r="G36" s="81"/>
       <c r="H36" s="83"/>
@@ -4513,11 +4702,19 @@
       <c r="L36" s="80"/>
       <c r="M36" s="79"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B37" s="82"/>
-      <c r="C37" s="82"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="83"/>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B37" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="81">
+        <v>1</v>
+      </c>
+      <c r="E37" s="83">
+        <v>100</v>
+      </c>
       <c r="F37" s="80"/>
       <c r="G37" s="81"/>
       <c r="H37" s="83"/>
@@ -4527,11 +4724,19 @@
       <c r="L37" s="80"/>
       <c r="M37" s="79"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B38" s="82"/>
-      <c r="C38" s="82"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="83"/>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B38" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E38" s="83">
+        <v>100</v>
+      </c>
       <c r="F38" s="80"/>
       <c r="G38" s="81"/>
       <c r="H38" s="83"/>
@@ -4541,11 +4746,19 @@
       <c r="L38" s="80"/>
       <c r="M38" s="79"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B39" s="82"/>
-      <c r="C39" s="82"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="83"/>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B39" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="E39" s="83">
+        <v>100</v>
+      </c>
       <c r="F39" s="80"/>
       <c r="G39" s="81"/>
       <c r="H39" s="83"/>
@@ -4555,23 +4768,32 @@
       <c r="L39" s="80"/>
       <c r="M39" s="79"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="83"/>
+    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="74" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="83">
+        <v>100</v>
+      </c>
       <c r="F40" s="80"/>
       <c r="G40" s="81"/>
       <c r="H40" s="83"/>
       <c r="I40" s="80"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="79"/>
       <c r="L40" s="80"/>
-      <c r="M40" s="79"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B41" s="82"/>
-      <c r="C41" s="82"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B41" s="96" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="D41" s="81"/>
       <c r="E41" s="83"/>
       <c r="F41" s="80"/>
@@ -4583,11 +4805,19 @@
       <c r="L41" s="80"/>
       <c r="M41" s="79"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B42" s="82"/>
-      <c r="C42" s="82"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="83"/>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B42" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E42" s="83">
+        <v>100</v>
+      </c>
       <c r="F42" s="80"/>
       <c r="G42" s="81"/>
       <c r="H42" s="83"/>
@@ -4595,12 +4825,21 @@
       <c r="J42" s="79"/>
       <c r="K42" s="79"/>
       <c r="L42" s="80"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B43" s="82"/>
-      <c r="C43" s="82"/>
-      <c r="D43" s="81"/>
-      <c r="E43" s="83"/>
+      <c r="M42" s="79"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B43" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="E43" s="83">
+        <v>100</v>
+      </c>
       <c r="F43" s="80"/>
       <c r="G43" s="81"/>
       <c r="H43" s="83"/>
@@ -4608,6 +4847,139 @@
       <c r="J43" s="79"/>
       <c r="K43" s="79"/>
       <c r="L43" s="80"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B44" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="83">
+        <v>100</v>
+      </c>
+      <c r="F44" s="80"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="79"/>
+      <c r="K44" s="79"/>
+      <c r="L44" s="80"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B45" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="97">
+        <v>1</v>
+      </c>
+      <c r="E45" s="83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B46" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="97">
+        <v>0.25</v>
+      </c>
+      <c r="E46" s="83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" s="97"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B48" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="97"/>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B49" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="97"/>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B50" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="97"/>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B51" s="74"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="97"/>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B52" s="74"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="97"/>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B53" s="74"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="97"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="74"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="97"/>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B55" s="74"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="97"/>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B56" s="74"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="97"/>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B57" s="74"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="97"/>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B58" s="74"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="97"/>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B59" s="74"/>
+      <c r="D59" s="97"/>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B60" s="74"/>
+      <c r="D60" s="97"/>
     </row>
   </sheetData>
   <autoFilter ref="B4:L5" xr:uid="{2EE69061-1192-400C-B500-1B4897FD0585}"/>
@@ -4620,87 +4992,108 @@
     <mergeCell ref="L4:L5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B4:B18 B25:B43">
-    <cfRule type="expression" dxfId="27" priority="28">
+  <conditionalFormatting sqref="B4:B18 B25:B39 B41:B44">
+    <cfRule type="expression" dxfId="47" priority="47">
       <formula>MAX($E4,$H4,$K4)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C5 C9:C43">
-    <cfRule type="expression" dxfId="26" priority="25">
+  <conditionalFormatting sqref="C4:C5 C9:C44">
+    <cfRule type="expression" dxfId="46" priority="44">
       <formula>$C4="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="26">
+    <cfRule type="expression" dxfId="45" priority="45">
       <formula>$C4="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="27">
+    <cfRule type="expression" dxfId="44" priority="46">
       <formula>$C4="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="43" priority="43">
       <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="22" priority="21">
+    <cfRule type="expression" dxfId="42" priority="40">
       <formula>$C1="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="41" priority="41">
       <formula>$C1="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="23">
+    <cfRule type="expression" dxfId="40" priority="42">
       <formula>$C1="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:B10">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="39" priority="36">
       <formula>MAX($E9,$H9,$K9)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" dxfId="18" priority="11">
+    <cfRule type="expression" dxfId="38" priority="30">
       <formula>MAX($E12,$H12,$K12)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="expression" dxfId="17" priority="10">
+    <cfRule type="expression" dxfId="37" priority="29">
       <formula>MAX($E11,$H11,$K11)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="expression" dxfId="16" priority="9">
+    <cfRule type="expression" dxfId="36" priority="28">
       <formula>MAX($E11,$H11,$K11)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="expression" dxfId="15" priority="64">
+    <cfRule type="expression" dxfId="35" priority="83">
       <formula>MAX(#REF!,#REF!,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B12">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="34" priority="25">
       <formula>MAX($E6,$H6,$K6)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C8">
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="33" priority="22">
       <formula>$C6="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="32" priority="23">
       <formula>$C6="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="31" priority="24">
       <formula>$C6="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:B24">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="30" priority="21">
       <formula>MAX($E19,$H19,$K19)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:B24">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="29" priority="20">
       <formula>MAX($E19,$H19,$K19)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="expression" dxfId="28" priority="85">
+      <formula>MAX($E41,$H41,$K41)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:B60">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>MAX($E45,$H45,$K45)=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45:C58">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$C45="Charlotte/Eddy"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$C45="Charlotte"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>$C45="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4713,21 +5106,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -4741,151 +5134,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -4901,18 +5294,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -4936,7 +5329,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -4980,7 +5373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -5002,7 +5395,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -5020,7 +5413,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -5038,7 +5431,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -5056,7 +5449,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -5074,7 +5467,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -5092,7 +5485,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -5110,7 +5503,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -5128,7 +5521,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -5146,7 +5539,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -5164,7 +5557,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -5182,7 +5575,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -5200,7 +5593,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -5218,7 +5611,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -5236,7 +5629,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -5254,7 +5647,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -5272,7 +5665,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -5290,7 +5683,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -5308,7 +5701,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -5326,7 +5719,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -5344,7 +5737,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -5362,7 +5755,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -5380,7 +5773,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -5398,7 +5791,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -5416,9 +5809,9 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>107</v>
@@ -5434,7 +5827,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -5452,7 +5845,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -5470,7 +5863,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -5488,7 +5881,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -5506,7 +5899,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -5528,47 +5921,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5580,25 +5973,25 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="94" t="s">
         <v>17</v>
       </c>
@@ -5616,8 +6009,8 @@
       <c r="N2" s="95"/>
       <c r="O2" s="95"/>
     </row>
-    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="88" t="s">
         <v>1</v>
       </c>
@@ -5661,7 +6054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="89"/>
       <c r="C6" s="91"/>
       <c r="D6" s="52" t="s">
@@ -5693,7 +6086,7 @@
       </c>
       <c r="O6" s="93"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
       <c r="D7" s="33"/>
@@ -5709,7 +6102,7 @@
       <c r="N7" s="11"/>
       <c r="O7" s="12"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
       <c r="D8" s="31"/>
@@ -5721,7 +6114,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
       <c r="D9" s="31"/>
@@ -5733,7 +6126,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="36"/>
       <c r="C10" s="36"/>
       <c r="D10" s="31"/>
@@ -5745,7 +6138,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="31"/>
@@ -5757,7 +6150,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
       <c r="D12" s="31"/>
@@ -5769,7 +6162,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
       <c r="D13" s="31"/>
@@ -5781,7 +6174,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
       <c r="D14" s="31"/>
@@ -5793,7 +6186,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
       <c r="D15" s="31"/>
@@ -5805,7 +6198,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
       <c r="D16" s="31"/>
@@ -5817,7 +6210,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="31"/>
@@ -5829,7 +6222,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
       <c r="D18" s="31"/>
@@ -5841,7 +6234,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
       <c r="D19" s="31"/>
@@ -5853,7 +6246,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="56"/>
       <c r="C20" s="36"/>
       <c r="D20" s="31"/>
@@ -5865,7 +6258,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
       <c r="D21" s="31"/>
@@ -5877,7 +6270,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="36"/>
       <c r="C22" s="36"/>
       <c r="D22" s="31"/>
@@ -5889,7 +6282,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
       <c r="D23" s="31"/>
@@ -5901,7 +6294,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="36"/>
       <c r="C24" s="36"/>
       <c r="D24" s="40"/>
@@ -5913,7 +6306,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
       <c r="D25" s="31"/>
@@ -5925,7 +6318,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
       <c r="D26" s="31"/>
@@ -5937,7 +6330,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="36"/>
       <c r="C27" s="36"/>
       <c r="D27" s="31"/>
@@ -5949,7 +6342,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="36"/>
       <c r="C28" s="36"/>
       <c r="D28" s="31"/>
@@ -5961,7 +6354,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="18"/>
       <c r="C29" s="36"/>
       <c r="D29" s="31"/>
@@ -5973,7 +6366,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="36"/>
       <c r="C30" s="36"/>
       <c r="D30" s="31"/>
@@ -5985,7 +6378,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="36"/>
       <c r="C31" s="36"/>
       <c r="D31" s="31"/>
@@ -5997,7 +6390,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
       <c r="D32" s="31"/>
@@ -6009,7 +6402,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="36"/>
       <c r="C33" s="36"/>
       <c r="D33" s="31"/>
@@ -6021,7 +6414,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
       <c r="D34" s="31"/>
@@ -6033,7 +6426,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
       <c r="D35" s="31"/>
@@ -6045,7 +6438,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36" s="36"/>
       <c r="C36" s="36"/>
       <c r="D36" s="31"/>
@@ -6057,7 +6450,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37" s="36"/>
       <c r="C37" s="36"/>
       <c r="D37" s="31"/>
@@ -6069,7 +6462,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
       <c r="D38" s="31"/>
@@ -6081,7 +6474,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
       <c r="D39" s="32"/>
@@ -6108,39 +6501,39 @@
     <mergeCell ref="O5:O6"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B36">
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>MAX($E5,$H5,$K5)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C36">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>$C5="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$C5="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$C5="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="expression" dxfId="4" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>MAX($E2,$H2,$K2)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37:C39">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$C37="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$C37="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>$C37="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:B39">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MAX($E37,$H37,$K37)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6154,28 +6547,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="93.1796875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -6192,7 +6585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -6205,7 +6598,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -6218,7 +6611,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -6231,7 +6624,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -6244,7 +6637,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -6257,7 +6650,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -6270,7 +6663,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -6283,7 +6676,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -6296,7 +6689,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -6309,7 +6702,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -6322,7 +6715,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -6335,7 +6728,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -6348,7 +6741,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -6361,7 +6754,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -6374,7 +6767,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -6387,7 +6780,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -6400,7 +6793,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -6413,7 +6806,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -6426,7 +6819,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -6439,7 +6832,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -6452,7 +6845,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -6465,7 +6858,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -6478,7 +6871,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -6491,7 +6884,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -6504,7 +6897,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -6517,7 +6910,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -6530,7 +6923,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -6543,7 +6936,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -6556,7 +6949,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -6569,7 +6962,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -6582,7 +6975,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -6595,7 +6988,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -6608,7 +7001,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -6621,7 +7014,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -6634,7 +7027,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -6647,7 +7040,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -6660,7 +7053,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -6673,7 +7066,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -6686,7 +7079,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -6699,7 +7092,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -6712,7 +7105,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -6725,7 +7118,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -6738,7 +7131,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -6751,7 +7144,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -6764,7 +7157,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -6777,7 +7170,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -6790,7 +7183,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -6803,7 +7196,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -6816,7 +7209,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -6829,7 +7222,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -6842,7 +7235,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -6855,7 +7248,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -6868,7 +7261,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -6881,7 +7274,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -6894,7 +7287,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -6907,7 +7300,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -6920,7 +7313,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -6933,7 +7326,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -6946,7 +7339,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -6959,7 +7352,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -6970,7 +7363,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -6981,7 +7374,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -6992,7 +7385,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -7003,7 +7396,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -7014,7 +7407,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -7025,7 +7418,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -7036,7 +7429,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -7047,7 +7440,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -7058,7 +7451,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -7069,7 +7462,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -7080,182 +7473,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7850D64E-5424-4209-B7DC-D8BA41625DDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA97923-ADCA-40DF-898B-D1D1361BED22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA97923-ADCA-40DF-898B-D1D1361BED22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C656DC3A-7DC7-42ED-992D-71563A94710B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="206">
   <si>
     <t>Planification globale</t>
   </si>
@@ -650,6 +650,12 @@
   </si>
   <si>
     <t>Créer la classe Piece/BeliefPiece</t>
+  </si>
+  <si>
+    <t>Centrage + scale des svg</t>
+  </si>
+  <si>
+    <t>Changer aspect des pieces du pool</t>
   </si>
 </sst>
 </file>
@@ -1213,6 +1219,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1246,48 +1256,11 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill>
@@ -1416,79 +1389,8 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
       </fill>
     </dxf>
     <dxf>
@@ -2620,7 +2522,7 @@
   </sheetData>
   <autoFilter ref="B5:E37" xr:uid="{93133217-C8F5-4788-AEEB-7509B70AEF5D}"/>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>MAX($E6,$H6,$K6)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3064,26 +2966,26 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="87"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="89"/>
     </row>
     <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="92" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="52" t="s">
@@ -3092,7 +2994,7 @@
       <c r="E5" s="53">
         <v>46083</v>
       </c>
-      <c r="F5" s="92" t="s">
+      <c r="F5" s="94" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="55" t="s">
@@ -3101,7 +3003,7 @@
       <c r="H5" s="53">
         <v>46090</v>
       </c>
-      <c r="I5" s="92" t="s">
+      <c r="I5" s="94" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="55" t="s">
@@ -3110,34 +3012,34 @@
       <c r="K5" s="53">
         <v>46104</v>
       </c>
-      <c r="L5" s="92" t="s">
+      <c r="L5" s="94" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="89"/>
-      <c r="C6" s="91"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="93"/>
       <c r="D6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="93"/>
+      <c r="F6" s="95"/>
       <c r="G6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="93"/>
+      <c r="I6" s="95"/>
       <c r="J6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="93"/>
+      <c r="L6" s="95"/>
     </row>
     <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
@@ -3963,81 +3865,81 @@
     <mergeCell ref="L5:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B45 B47:B1048576 B1:B42">
-    <cfRule type="expression" dxfId="66" priority="28">
+    <cfRule type="expression" dxfId="54" priority="28">
       <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C49:C1048576 C1:C45">
-    <cfRule type="expression" dxfId="65" priority="23">
+    <cfRule type="expression" dxfId="53" priority="23">
       <formula>$C1="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="25">
+    <cfRule type="expression" dxfId="52" priority="25">
       <formula>$C1="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="27">
+    <cfRule type="expression" dxfId="51" priority="27">
       <formula>$C1="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="expression" dxfId="62" priority="19">
+    <cfRule type="expression" dxfId="50" priority="19">
       <formula>$C47="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="20">
+    <cfRule type="expression" dxfId="49" priority="20">
       <formula>$C47="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="21">
+    <cfRule type="expression" dxfId="48" priority="21">
       <formula>$C47="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
-    <cfRule type="expression" dxfId="59" priority="8">
+    <cfRule type="expression" dxfId="47" priority="8">
       <formula>$C48="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="9">
+    <cfRule type="expression" dxfId="46" priority="9">
       <formula>$C48="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="10">
+    <cfRule type="expression" dxfId="45" priority="10">
       <formula>$C48="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42:C48">
-    <cfRule type="expression" dxfId="56" priority="12">
+    <cfRule type="expression" dxfId="44" priority="12">
       <formula>$C42="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="13">
+    <cfRule type="expression" dxfId="43" priority="13">
       <formula>$C42="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="14">
+    <cfRule type="expression" dxfId="42" priority="14">
       <formula>$C42="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:B48 B45 B31:B42">
-    <cfRule type="expression" dxfId="53" priority="30">
+    <cfRule type="expression" dxfId="41" priority="30">
       <formula>MAX($E31,$K31,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="52" priority="7">
+    <cfRule type="expression" dxfId="40" priority="7">
       <formula>MAX($E43,$H43,$K43)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" dxfId="51" priority="32">
+    <cfRule type="expression" dxfId="39" priority="32">
       <formula>MAX($E46,$H46,$K46)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" dxfId="50" priority="38">
+    <cfRule type="expression" dxfId="38" priority="38">
       <formula>MAX($E46,$K46,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" dxfId="49" priority="6">
+    <cfRule type="expression" dxfId="37" priority="6">
       <formula>MAX($E46,$H46,$K46)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>MAX($E30,$K30,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4051,7 +3953,7 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B1:M60"/>
+  <dimension ref="B1:M62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.81640625" customWidth="1"/>
@@ -4069,26 +3971,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="89"/>
     </row>
     <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.5">
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="92" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="52" t="s">
@@ -4097,7 +3999,7 @@
       <c r="E4" s="53">
         <v>46111</v>
       </c>
-      <c r="F4" s="92" t="s">
+      <c r="F4" s="94" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="55" t="s">
@@ -4106,7 +4008,7 @@
       <c r="H4" s="53">
         <v>46125</v>
       </c>
-      <c r="I4" s="92" t="s">
+      <c r="I4" s="94" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="55" t="s">
@@ -4115,34 +4017,34 @@
       <c r="K4" s="53">
         <v>46132</v>
       </c>
-      <c r="L4" s="92" t="s">
+      <c r="L4" s="94" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="89"/>
-      <c r="C5" s="91"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="93"/>
       <c r="D5" s="52" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="93"/>
+      <c r="F5" s="95"/>
       <c r="G5" s="54" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="93"/>
+      <c r="I5" s="95"/>
       <c r="J5" s="54" t="s">
         <v>10</v>
       </c>
       <c r="K5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="93"/>
+      <c r="L5" s="95"/>
     </row>
     <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B6" s="82" t="s">
@@ -4366,23 +4268,31 @@
       <c r="C17" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="83"/>
+      <c r="D17" s="81">
+        <v>2</v>
+      </c>
+      <c r="E17" s="83">
+        <v>100</v>
+      </c>
       <c r="F17" s="80"/>
       <c r="G17" s="81"/>
       <c r="H17" s="83"/>
       <c r="I17" s="80"/>
       <c r="L17" s="80"/>
     </row>
-    <row r="18" spans="2:13" s="79" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="84" t="s">
-        <v>191</v>
+    <row r="18" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="82" t="s">
+        <v>204</v>
       </c>
       <c r="C18" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="83"/>
+      <c r="D18" s="81">
+        <v>1</v>
+      </c>
+      <c r="E18" s="83">
+        <v>100</v>
+      </c>
       <c r="F18" s="80"/>
       <c r="G18" s="81"/>
       <c r="H18" s="83"/>
@@ -4391,22 +4301,26 @@
     </row>
     <row r="19" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B19" s="82" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C19" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="83"/>
+      <c r="D19" s="81">
+        <v>0.25</v>
+      </c>
+      <c r="E19" s="83">
+        <v>100</v>
+      </c>
       <c r="F19" s="80"/>
       <c r="G19" s="81"/>
       <c r="H19" s="83"/>
       <c r="I19" s="80"/>
       <c r="L19" s="80"/>
     </row>
-    <row r="20" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="82" t="s">
-        <v>192</v>
+    <row r="20" spans="2:13" s="79" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="B20" s="84" t="s">
+        <v>191</v>
       </c>
       <c r="C20" s="82" t="s">
         <v>106</v>
@@ -4421,7 +4335,7 @@
     </row>
     <row r="21" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B21" s="82" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="C21" s="82" t="s">
         <v>106</v>
@@ -4436,7 +4350,7 @@
     </row>
     <row r="22" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B22" s="82" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="C22" s="82" t="s">
         <v>106</v>
@@ -4449,9 +4363,9 @@
       <c r="I22" s="80"/>
       <c r="L22" s="80"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B23" s="82" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="C23" s="82" t="s">
         <v>106</v>
@@ -4462,14 +4376,11 @@
       <c r="G23" s="81"/>
       <c r="H23" s="83"/>
       <c r="I23" s="80"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="79"/>
       <c r="L23" s="80"/>
-      <c r="M23" s="79"/>
     </row>
     <row r="24" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="C24" s="82" t="s">
         <v>106</v>
@@ -4484,7 +4395,7 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="82" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C25" s="82" t="s">
         <v>106</v>
@@ -4500,9 +4411,9 @@
       <c r="L25" s="80"/>
       <c r="M25" s="79"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B26" s="82" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="C26" s="82" t="s">
         <v>106</v>
@@ -4513,14 +4424,11 @@
       <c r="G26" s="81"/>
       <c r="H26" s="83"/>
       <c r="I26" s="80"/>
-      <c r="J26" s="79"/>
-      <c r="K26" s="79"/>
       <c r="L26" s="80"/>
-      <c r="M26" s="79"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="82" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C27" s="82" t="s">
         <v>106</v>
@@ -4538,7 +4446,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="82" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C28" s="82" t="s">
         <v>106</v>
@@ -4556,7 +4464,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="82" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C29" s="82" t="s">
         <v>106</v>
@@ -4574,7 +4482,7 @@
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B30" s="82" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C30" s="82" t="s">
         <v>106</v>
@@ -4592,7 +4500,7 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C31" s="82" t="s">
         <v>106</v>
@@ -4610,7 +4518,7 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="82" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="C32" s="82" t="s">
         <v>106</v>
@@ -4628,7 +4536,7 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="82" t="s">
         <v>106</v>
@@ -4646,7 +4554,7 @@
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="82" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C34" s="82" t="s">
         <v>106</v>
@@ -4664,7 +4572,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="82" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="C35" s="82" t="s">
         <v>106</v>
@@ -4681,18 +4589,14 @@
       <c r="M35" s="79"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B36" s="74" t="s">
-        <v>203</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" s="81">
-        <v>0.5</v>
-      </c>
-      <c r="E36" s="83">
-        <v>100</v>
-      </c>
+      <c r="B36" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="81"/>
+      <c r="E36" s="83"/>
       <c r="F36" s="80"/>
       <c r="G36" s="81"/>
       <c r="H36" s="83"/>
@@ -4703,18 +4607,14 @@
       <c r="M36" s="79"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B37" s="74" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" s="81">
-        <v>1</v>
-      </c>
-      <c r="E37" s="83">
-        <v>100</v>
-      </c>
+      <c r="B37" s="82" t="s">
+        <v>198</v>
+      </c>
+      <c r="C37" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="81"/>
+      <c r="E37" s="83"/>
       <c r="F37" s="80"/>
       <c r="G37" s="81"/>
       <c r="H37" s="83"/>
@@ -4726,7 +4626,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="74" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>107</v>
@@ -4748,13 +4648,13 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="74" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D39" s="81">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E39" s="83">
         <v>100</v>
@@ -4768,9 +4668,9 @@
       <c r="L39" s="80"/>
       <c r="M39" s="79"/>
     </row>
-    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="74" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>107</v>
@@ -4785,17 +4685,24 @@
       <c r="G40" s="81"/>
       <c r="H40" s="83"/>
       <c r="I40" s="80"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="79"/>
       <c r="L40" s="80"/>
+      <c r="M40" s="79"/>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B41" s="96" t="s">
-        <v>201</v>
+      <c r="B41" s="74" t="s">
+        <v>62</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="81"/>
-      <c r="E41" s="83"/>
+      <c r="D41" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="E41" s="83">
+        <v>100</v>
+      </c>
       <c r="F41" s="80"/>
       <c r="G41" s="81"/>
       <c r="H41" s="83"/>
@@ -4805,9 +4712,9 @@
       <c r="L41" s="80"/>
       <c r="M41" s="79"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B42" s="74" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>107</v>
@@ -4822,24 +4729,17 @@
       <c r="G42" s="81"/>
       <c r="H42" s="83"/>
       <c r="I42" s="80"/>
-      <c r="J42" s="79"/>
-      <c r="K42" s="79"/>
       <c r="L42" s="80"/>
-      <c r="M42" s="79"/>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B43" s="74" t="s">
-        <v>59</v>
+      <c r="B43" s="85" t="s">
+        <v>201</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="81">
-        <v>0.75</v>
-      </c>
-      <c r="E43" s="83">
-        <v>100</v>
-      </c>
+      <c r="D43" s="81"/>
+      <c r="E43" s="83"/>
       <c r="F43" s="80"/>
       <c r="G43" s="81"/>
       <c r="H43" s="83"/>
@@ -4847,10 +4747,11 @@
       <c r="J43" s="79"/>
       <c r="K43" s="79"/>
       <c r="L43" s="80"/>
+      <c r="M43" s="79"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="74" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>107</v>
@@ -4868,118 +4769,161 @@
       <c r="J44" s="79"/>
       <c r="K44" s="79"/>
       <c r="L44" s="80"/>
+      <c r="M44" s="79"/>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="74" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D45" s="97">
-        <v>1</v>
+      <c r="D45" s="81">
+        <v>0.75</v>
       </c>
       <c r="E45" s="83">
         <v>100</v>
       </c>
+      <c r="F45" s="80"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="80"/>
+      <c r="J45" s="79"/>
+      <c r="K45" s="79"/>
+      <c r="L45" s="80"/>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="74" t="s">
-        <v>202</v>
+        <v>60</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D46" s="97">
-        <v>0.25</v>
+      <c r="D46" s="81">
+        <v>0.5</v>
       </c>
       <c r="E46" s="83">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F46" s="80"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="83"/>
+      <c r="I46" s="80"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="79"/>
+      <c r="L46" s="80"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="74" t="s">
-        <v>200</v>
+        <v>57</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="97"/>
+      <c r="D47" s="86">
+        <v>1</v>
+      </c>
+      <c r="E47" s="83">
+        <v>100</v>
+      </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="74" t="s">
-        <v>65</v>
+        <v>202</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="97"/>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D48" s="86">
+        <v>0.25</v>
+      </c>
+      <c r="E48" s="83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B49" s="74" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="97"/>
+      <c r="D49" s="86"/>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B50" s="74" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="97"/>
+      <c r="D50" s="86"/>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B51" s="74"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="97"/>
+      <c r="B51" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="86"/>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B52" s="74"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="97"/>
+      <c r="B52" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="86"/>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B53" s="74"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="97"/>
+      <c r="D53" s="86"/>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B54" s="74"/>
       <c r="C54" s="8"/>
-      <c r="D54" s="97"/>
+      <c r="D54" s="86"/>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B55" s="74"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="97"/>
+      <c r="D55" s="86"/>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B56" s="74"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="97"/>
+      <c r="D56" s="86"/>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B57" s="74"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="97"/>
+      <c r="D57" s="86"/>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B58" s="74"/>
       <c r="C58" s="8"/>
-      <c r="D58" s="97"/>
+      <c r="D58" s="86"/>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B59" s="74"/>
-      <c r="D59" s="97"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="86"/>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B60" s="74"/>
-      <c r="D60" s="97"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="86"/>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B61" s="74"/>
+      <c r="D61" s="86"/>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B62" s="74"/>
+      <c r="D62" s="86"/>
     </row>
   </sheetData>
   <autoFilter ref="B4:L5" xr:uid="{2EE69061-1192-400C-B500-1B4897FD0585}"/>
@@ -4992,108 +4936,108 @@
     <mergeCell ref="L4:L5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B4:B18 B25:B39 B41:B44">
-    <cfRule type="expression" dxfId="47" priority="47">
+  <conditionalFormatting sqref="B27:B41 B43:B46 B4:B20">
+    <cfRule type="expression" dxfId="35" priority="47">
       <formula>MAX($E4,$H4,$K4)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C5 C9:C44">
-    <cfRule type="expression" dxfId="46" priority="44">
+  <conditionalFormatting sqref="C4:C5 C9:C46">
+    <cfRule type="expression" dxfId="34" priority="44">
       <formula>$C4="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="45">
+    <cfRule type="expression" dxfId="33" priority="45">
       <formula>$C4="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="46">
+    <cfRule type="expression" dxfId="32" priority="46">
       <formula>$C4="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="43" priority="43">
+    <cfRule type="expression" dxfId="31" priority="43">
       <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="42" priority="40">
+    <cfRule type="expression" dxfId="30" priority="40">
       <formula>$C1="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="41">
+    <cfRule type="expression" dxfId="29" priority="41">
       <formula>$C1="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="42">
+    <cfRule type="expression" dxfId="28" priority="42">
       <formula>$C1="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:B10">
-    <cfRule type="expression" dxfId="39" priority="36">
+    <cfRule type="expression" dxfId="27" priority="36">
       <formula>MAX($E9,$H9,$K9)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" dxfId="38" priority="30">
+    <cfRule type="expression" dxfId="26" priority="30">
       <formula>MAX($E12,$H12,$K12)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="expression" dxfId="37" priority="29">
+    <cfRule type="expression" dxfId="25" priority="29">
       <formula>MAX($E11,$H11,$K11)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="expression" dxfId="36" priority="28">
+    <cfRule type="expression" dxfId="24" priority="28">
       <formula>MAX($E11,$H11,$K11)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="expression" dxfId="35" priority="83">
+  <conditionalFormatting sqref="B36">
+    <cfRule type="expression" dxfId="23" priority="83">
       <formula>MAX(#REF!,#REF!,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B12">
-    <cfRule type="expression" dxfId="34" priority="25">
+    <cfRule type="expression" dxfId="22" priority="25">
       <formula>MAX($E6,$H6,$K6)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C8">
-    <cfRule type="expression" dxfId="33" priority="22">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>$C6="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="23">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>$C6="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="24">
+    <cfRule type="expression" dxfId="19" priority="24">
       <formula>$C6="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B24">
-    <cfRule type="expression" dxfId="30" priority="21">
-      <formula>MAX($E19,$H19,$K19)=100</formula>
+  <conditionalFormatting sqref="B21:B26">
+    <cfRule type="expression" dxfId="18" priority="21">
+      <formula>MAX($E21,$H21,$K21)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B24">
-    <cfRule type="expression" dxfId="29" priority="20">
-      <formula>MAX($E19,$H19,$K19)=100</formula>
+  <conditionalFormatting sqref="B21:B26">
+    <cfRule type="expression" dxfId="17" priority="20">
+      <formula>MAX($E21,$H21,$K21)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40">
-    <cfRule type="expression" dxfId="28" priority="85">
-      <formula>MAX($E41,$H41,$K41)=100</formula>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="expression" dxfId="16" priority="85">
+      <formula>MAX($E43,$H43,$K43)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B60">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>MAX($E45,$H45,$K45)=100</formula>
+  <conditionalFormatting sqref="B47:B62">
+    <cfRule type="expression" dxfId="15" priority="4">
+      <formula>MAX($E47,$H47,$K47)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C45:C58">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$C45="Charlotte/Eddy"</formula>
+  <conditionalFormatting sqref="C47:C60">
+    <cfRule type="expression" dxfId="14" priority="1">
+      <formula>$C47="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$C45="Charlotte"</formula>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>$C47="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>$C45="Eddy"</formula>
+    <cfRule type="expression" dxfId="12" priority="3">
+      <formula>$C47="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5992,29 +5936,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="92" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="52" t="s">
@@ -6023,7 +5967,7 @@
       <c r="E5" s="53">
         <v>46139</v>
       </c>
-      <c r="F5" s="92" t="s">
+      <c r="F5" s="94" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="55" t="s">
@@ -6032,7 +5976,7 @@
       <c r="H5" s="53">
         <v>46146</v>
       </c>
-      <c r="I5" s="92" t="s">
+      <c r="I5" s="94" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="55" t="s">
@@ -6041,7 +5985,7 @@
       <c r="K5" s="53">
         <v>46153</v>
       </c>
-      <c r="L5" s="92" t="s">
+      <c r="L5" s="94" t="s">
         <v>12</v>
       </c>
       <c r="M5" s="55" t="s">
@@ -6050,41 +5994,41 @@
       <c r="N5" s="53">
         <v>46161</v>
       </c>
-      <c r="O5" s="92" t="s">
+      <c r="O5" s="94" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="89"/>
-      <c r="C6" s="91"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="93"/>
       <c r="D6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="93"/>
+      <c r="F6" s="95"/>
       <c r="G6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="93"/>
+      <c r="I6" s="95"/>
       <c r="J6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="93"/>
+      <c r="L6" s="95"/>
       <c r="M6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="N6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="93"/>
+      <c r="O6" s="95"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="35"/>
@@ -6501,39 +6445,39 @@
     <mergeCell ref="O5:O6"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B36">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="8" priority="12">
       <formula>MAX($E5,$H5,$K5)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C36">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>$C5="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>$C5="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="5" priority="11">
       <formula>$C5="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>MAX($E2,$H2,$K2)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37:C39">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$C37="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$C37="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$C37="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:B39">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MAX($E37,$H37,$K37)=100</formula>
     </cfRule>
   </conditionalFormatting>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C656DC3A-7DC7-42ED-992D-71563A94710B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D705F6C-2928-4869-872A-EF1631713E7F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -28,17 +28,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sprint 3'!$B$4:$L$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="219">
   <si>
     <t>Planification globale</t>
   </si>
@@ -613,18 +618,6 @@
     <t>Création d un component piece</t>
   </si>
   <si>
-    <t>Mise à jour  aspect game,jsx en fonction  du getGameStatus( ) : afficher le board avec les pieces des 2 joueurs et du tour de jeu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Afficher le tour de jeu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créer le composant PlayerInfo  pour afficher les informations des joueurs (noms, avatars, scores,tour)  </t>
-  </si>
-  <si>
-    <t>Implémentation de la logique  ecran combat des pieces</t>
-  </si>
-  <si>
     <t>Régler l affichage du board selon la phase de jeu suite a mise en place des phases de jeu</t>
   </si>
   <si>
@@ -634,9 +627,6 @@
     <t>Créer une page administration:gestion des utilisateurs</t>
   </si>
   <si>
-    <t>Permettre le drag and drop sur les pieces</t>
-  </si>
-  <si>
     <t>Importation des svg en tant que Composant pour les pieces</t>
   </si>
   <si>
@@ -655,7 +645,61 @@
     <t>Centrage + scale des svg</t>
   </si>
   <si>
-    <t>Changer aspect des pieces du pool</t>
+    <t>Changer aspect des pieces du pool avec des components svg</t>
+  </si>
+  <si>
+    <t>Ajout component Timer non full complete</t>
+  </si>
+  <si>
+    <t>Ajout fonction transformation tableau api vers matrice React pour le Board</t>
+  </si>
+  <si>
+    <t>Modifier makeBoard pour recevoir x,y,rank,player</t>
+  </si>
+  <si>
+    <t>Ajout fonctions de drag drop dans usePlacement.js</t>
+  </si>
+  <si>
+    <t>Ajout drag drop dans useCellClick.js</t>
+  </si>
+  <si>
+    <t>Ajout drag drop dans cell.jsx</t>
+  </si>
+  <si>
+    <t>AJout Drag drop dans game.jsx</t>
+  </si>
+  <si>
+    <t>Ajout pieceCard + debut battle screen</t>
+  </si>
+  <si>
+    <t>Modifier timer avec un timer local pour l affichage et compenser la latence reseau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise a jour affichage suite à combat: ajout  battle.jsx </t>
+  </si>
+  <si>
+    <t>Mise a jour board suite a un deplacement</t>
+  </si>
+  <si>
+    <t>Ajout component TurnIndicator pour signifier le tour</t>
+  </si>
+  <si>
+    <t>Ajout du Timer depuis api  (Compte à rebourd)</t>
+  </si>
+  <si>
+    <t>Afficher le tour de jeu message a u centre de l écran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajouter  end.jsx victoire ou defaite avec bouton recommencer </t>
+  </si>
+  <si>
+    <t>Ajouter le score de chaque joueur</t>
+  </si>
+  <si>
+    <t>Refactoriser game.jsx( redecouapge en differents components)</t>
+  </si>
+  <si>
+    <t>Implémentation du Factory Pattern pour les aspects des pièces(couleur + divers apects,,)</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1216,9 +1260,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1260,7 +1301,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="51">
     <dxf>
       <fill>
         <patternFill>
@@ -1358,46 +1399,6 @@
             <color rgb="FFCCFFFF"/>
           </stop>
         </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -2028,26 +2029,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="42.81640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="2:5" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2061,7 +2062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="58" t="s">
         <v>152</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="62" t="s">
         <v>122</v>
       </c>
@@ -2089,7 +2090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="63" t="s">
         <v>123</v>
       </c>
@@ -2103,7 +2104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="63" t="s">
         <v>124</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="63" t="s">
         <v>125</v>
       </c>
@@ -2131,7 +2132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="63" t="s">
         <v>127</v>
       </c>
@@ -2145,7 +2146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="63" t="s">
         <v>128</v>
       </c>
@@ -2159,7 +2160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="63" t="s">
         <v>129</v>
       </c>
@@ -2173,7 +2174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="63" t="s">
         <v>156</v>
       </c>
@@ -2187,7 +2188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="63" t="s">
         <v>132</v>
       </c>
@@ -2201,7 +2202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="63" t="s">
         <v>133</v>
       </c>
@@ -2215,7 +2216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="63" t="s">
         <v>135</v>
       </c>
@@ -2229,7 +2230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="63" t="s">
         <v>141</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="59" t="s">
         <v>130</v>
       </c>
@@ -2257,7 +2258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="59" t="s">
         <v>131</v>
       </c>
@@ -2271,7 +2272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="59" t="s">
         <v>136</v>
       </c>
@@ -2285,7 +2286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="59" t="s">
         <v>137</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="59" t="s">
         <v>138</v>
       </c>
@@ -2313,7 +2314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="59" t="s">
         <v>140</v>
       </c>
@@ -2327,7 +2328,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="59" t="s">
         <v>144</v>
       </c>
@@ -2341,7 +2342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="59" t="s">
         <v>145</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="59" t="s">
         <v>146</v>
       </c>
@@ -2369,7 +2370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="64" t="s">
         <v>139</v>
       </c>
@@ -2383,7 +2384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="64" t="s">
         <v>142</v>
       </c>
@@ -2397,7 +2398,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
         <v>134</v>
       </c>
@@ -2411,7 +2412,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="64" t="s">
         <v>143</v>
       </c>
@@ -2425,7 +2426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="64" t="s">
         <v>147</v>
       </c>
@@ -2439,7 +2440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="64" t="s">
         <v>148</v>
       </c>
@@ -2453,7 +2454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="64" t="s">
         <v>149</v>
       </c>
@@ -2467,7 +2468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="64" t="s">
         <v>150</v>
       </c>
@@ -2481,7 +2482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="64" t="s">
         <v>151</v>
       </c>
@@ -2495,7 +2496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="66" t="s">
         <v>126</v>
       </c>
@@ -2509,8 +2510,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D39" s="41" t="s">
         <v>157</v>
       </c>
@@ -2522,7 +2523,7 @@
   </sheetData>
   <autoFilter ref="B5:E37" xr:uid="{93133217-C8F5-4788-AEEB-7509B70AEF5D}"/>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>MAX($E6,$H6,$K6)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2545,32 +2546,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
-    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2600,7 +2601,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2654,7 +2655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -2681,7 +2682,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2703,7 +2704,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2730,7 +2731,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2763,7 +2764,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2800,7 +2801,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2837,7 +2838,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2869,7 +2870,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2897,7 +2898,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2924,15 +2925,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2948,44 +2949,44 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B2:M48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.54296875" customWidth="1"/>
-    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="74" customWidth="1"/>
-    <col min="10" max="10" width="16.6328125" customWidth="1"/>
-    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.81640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B3" s="87" t="s">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:12" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B3" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="89"/>
-    </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="90" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="88"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="91" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="52" t="s">
@@ -2994,7 +2995,7 @@
       <c r="E5" s="53">
         <v>46083</v>
       </c>
-      <c r="F5" s="94" t="s">
+      <c r="F5" s="93" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="55" t="s">
@@ -3003,7 +3004,7 @@
       <c r="H5" s="53">
         <v>46090</v>
       </c>
-      <c r="I5" s="94" t="s">
+      <c r="I5" s="93" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="55" t="s">
@@ -3012,36 +3013,36 @@
       <c r="K5" s="53">
         <v>46104</v>
       </c>
-      <c r="L5" s="94" t="s">
+      <c r="L5" s="93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="91"/>
-      <c r="C6" s="93"/>
+    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="90"/>
+      <c r="C6" s="92"/>
       <c r="D6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="95"/>
+      <c r="F6" s="94"/>
       <c r="G6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="95"/>
+      <c r="I6" s="94"/>
       <c r="J6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="95"/>
-    </row>
-    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="L6" s="94"/>
+    </row>
+    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -3064,7 +3065,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -3083,7 +3084,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -3102,7 +3103,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -3121,7 +3122,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="36" t="s">
         <v>165</v>
       </c>
@@ -3140,7 +3141,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -3159,7 +3160,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -3178,7 +3179,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -3197,7 +3198,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="36" t="s">
         <v>163</v>
       </c>
@@ -3216,7 +3217,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="36" t="s">
         <v>29</v>
       </c>
@@ -3235,7 +3236,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="36" t="s">
         <v>30</v>
       </c>
@@ -3254,7 +3255,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
         <v>161</v>
       </c>
@@ -3273,7 +3274,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="36" t="s">
         <v>162</v>
       </c>
@@ -3292,7 +3293,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="56" t="s">
         <v>170</v>
       </c>
@@ -3311,7 +3312,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="36" t="s">
         <v>92</v>
       </c>
@@ -3332,7 +3333,7 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
         <v>51</v>
       </c>
@@ -3351,7 +3352,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="36" t="s">
         <v>90</v>
       </c>
@@ -3372,7 +3373,7 @@
       </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
         <v>74</v>
       </c>
@@ -3391,7 +3392,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
@@ -3410,7 +3411,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="36" t="s">
         <v>93</v>
       </c>
@@ -3431,7 +3432,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="36" t="s">
         <v>94</v>
       </c>
@@ -3452,7 +3453,7 @@
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="77" t="s">
         <v>79</v>
       </c>
@@ -3473,7 +3474,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="77" t="s">
         <v>76</v>
       </c>
@@ -3492,7 +3493,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B30" s="82" t="s">
         <v>185</v>
       </c>
@@ -3511,7 +3512,7 @@
       <c r="I30" s="80"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="77" t="s">
         <v>42</v>
       </c>
@@ -3530,7 +3531,7 @@
       </c>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="77" t="s">
         <v>43</v>
       </c>
@@ -3549,7 +3550,7 @@
       </c>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="77" t="s">
         <v>164</v>
       </c>
@@ -3568,7 +3569,7 @@
       </c>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="77" t="s">
         <v>167</v>
       </c>
@@ -3587,7 +3588,7 @@
       </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="77" t="s">
         <v>73</v>
       </c>
@@ -3606,7 +3607,7 @@
       </c>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="77" t="s">
         <v>38</v>
       </c>
@@ -3625,7 +3626,7 @@
       </c>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="77" t="s">
         <v>39</v>
       </c>
@@ -3644,7 +3645,7 @@
       </c>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B38" s="82" t="s">
         <v>181</v>
       </c>
@@ -3663,7 +3664,7 @@
       </c>
       <c r="L38" s="80"/>
     </row>
-    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" s="82" t="s">
         <v>182</v>
       </c>
@@ -3682,7 +3683,7 @@
       </c>
       <c r="L39" s="80"/>
     </row>
-    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="82" t="s">
         <v>179</v>
       </c>
@@ -3701,7 +3702,7 @@
       </c>
       <c r="L40" s="80"/>
     </row>
-    <row r="41" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B41" s="82" t="s">
         <v>180</v>
       </c>
@@ -3720,7 +3721,7 @@
       </c>
       <c r="L41" s="80"/>
     </row>
-    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B42" s="82" t="s">
         <v>177</v>
       </c>
@@ -3739,7 +3740,7 @@
       </c>
       <c r="L42" s="80"/>
     </row>
-    <row r="43" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B43" s="82" t="s">
         <v>176</v>
       </c>
@@ -3758,7 +3759,7 @@
       </c>
       <c r="L43" s="80"/>
     </row>
-    <row r="44" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B44" s="77" t="s">
         <v>172</v>
       </c>
@@ -3777,7 +3778,7 @@
       </c>
       <c r="L44" s="80"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="77" t="s">
         <v>171</v>
       </c>
@@ -3796,7 +3797,7 @@
       </c>
       <c r="L45" s="14"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="82" t="s">
         <v>175</v>
       </c>
@@ -3815,7 +3816,7 @@
       </c>
       <c r="L46" s="70"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="77" t="s">
         <v>183</v>
       </c>
@@ -3835,7 +3836,7 @@
       <c r="L47" s="70"/>
       <c r="M47" s="69"/>
     </row>
-    <row r="48" spans="2:13" s="73" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13" s="73" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B48" s="74" t="s">
         <v>174</v>
       </c>
@@ -3865,81 +3866,81 @@
     <mergeCell ref="L5:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B45 B47:B1048576 B1:B42">
-    <cfRule type="expression" dxfId="54" priority="28">
+    <cfRule type="expression" dxfId="49" priority="28">
       <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C49:C1048576 C1:C45">
-    <cfRule type="expression" dxfId="53" priority="23">
+    <cfRule type="expression" dxfId="48" priority="23">
       <formula>$C1="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="25">
+    <cfRule type="expression" dxfId="47" priority="25">
       <formula>$C1="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="27">
+    <cfRule type="expression" dxfId="46" priority="27">
       <formula>$C1="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="expression" dxfId="50" priority="19">
+    <cfRule type="expression" dxfId="45" priority="19">
       <formula>$C47="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="20">
+    <cfRule type="expression" dxfId="44" priority="20">
       <formula>$C47="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="21">
+    <cfRule type="expression" dxfId="43" priority="21">
       <formula>$C47="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
-    <cfRule type="expression" dxfId="47" priority="8">
+    <cfRule type="expression" dxfId="42" priority="8">
       <formula>$C48="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="9">
+    <cfRule type="expression" dxfId="41" priority="9">
       <formula>$C48="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="10">
+    <cfRule type="expression" dxfId="40" priority="10">
       <formula>$C48="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42:C48">
-    <cfRule type="expression" dxfId="44" priority="12">
+    <cfRule type="expression" dxfId="39" priority="12">
       <formula>$C42="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="13">
+    <cfRule type="expression" dxfId="38" priority="13">
       <formula>$C42="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="14">
+    <cfRule type="expression" dxfId="37" priority="14">
       <formula>$C42="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:B48 B45 B31:B42">
-    <cfRule type="expression" dxfId="41" priority="30">
+    <cfRule type="expression" dxfId="36" priority="30">
       <formula>MAX($E31,$K31,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="40" priority="7">
+    <cfRule type="expression" dxfId="35" priority="7">
       <formula>MAX($E43,$H43,$K43)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" dxfId="39" priority="32">
+    <cfRule type="expression" dxfId="34" priority="32">
       <formula>MAX($E46,$H46,$K46)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" dxfId="38" priority="38">
+    <cfRule type="expression" dxfId="33" priority="38">
       <formula>MAX($E46,$K46,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" dxfId="37" priority="6">
+    <cfRule type="expression" dxfId="32" priority="6">
       <formula>MAX($E46,$H46,$K46)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>MAX($E30,$K30,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3953,44 +3954,44 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B1:M62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:M70"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="21.81640625" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" customWidth="1"/>
+    <col min="11" max="11" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B1" s="87" t="s">
+    <row r="1" spans="2:13" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B1" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="89"/>
-    </row>
-    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.5">
-      <c r="B4" s="90" t="s">
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="88"/>
+    </row>
+    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.4">
+      <c r="B4" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="C4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="52" t="s">
@@ -3999,7 +4000,7 @@
       <c r="E4" s="53">
         <v>46111</v>
       </c>
-      <c r="F4" s="94" t="s">
+      <c r="F4" s="93" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="55" t="s">
@@ -4008,7 +4009,7 @@
       <c r="H4" s="53">
         <v>46125</v>
       </c>
-      <c r="I4" s="94" t="s">
+      <c r="I4" s="93" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="55" t="s">
@@ -4017,36 +4018,36 @@
       <c r="K4" s="53">
         <v>46132</v>
       </c>
-      <c r="L4" s="94" t="s">
+      <c r="L4" s="93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="91"/>
-      <c r="C5" s="93"/>
+    <row r="5" spans="2:13" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="90"/>
+      <c r="C5" s="92"/>
       <c r="D5" s="52" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="95"/>
+      <c r="F5" s="94"/>
       <c r="G5" s="54" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="95"/>
+      <c r="I5" s="94"/>
       <c r="J5" s="54" t="s">
         <v>10</v>
       </c>
       <c r="K5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="95"/>
-    </row>
-    <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L5" s="94"/>
+    </row>
+    <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="82" t="s">
         <v>188</v>
       </c>
@@ -4065,7 +4066,7 @@
       <c r="I6" s="80"/>
       <c r="L6" s="80"/>
     </row>
-    <row r="7" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="82" t="s">
         <v>189</v>
       </c>
@@ -4084,7 +4085,7 @@
       <c r="I7" s="80"/>
       <c r="L7" s="80"/>
     </row>
-    <row r="8" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="82" t="s">
         <v>190</v>
       </c>
@@ -4103,7 +4104,7 @@
       <c r="I8" s="80"/>
       <c r="L8" s="80"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="82" t="s">
         <v>173</v>
       </c>
@@ -4124,7 +4125,7 @@
       <c r="K9" s="79"/>
       <c r="L9" s="80"/>
     </row>
-    <row r="10" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="82" t="s">
         <v>187</v>
       </c>
@@ -4143,7 +4144,7 @@
       <c r="I10" s="80"/>
       <c r="L10" s="80"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="82" t="s">
         <v>186</v>
       </c>
@@ -4165,7 +4166,7 @@
       <c r="L11" s="80"/>
       <c r="M11" s="79"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="82" t="s">
         <v>178</v>
       </c>
@@ -4185,7 +4186,7 @@
       <c r="L12" s="14"/>
       <c r="M12" s="79"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="82" t="s">
         <v>184</v>
       </c>
@@ -4207,9 +4208,9 @@
       <c r="L13" s="80"/>
       <c r="M13" s="79"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="82" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C14" s="82" t="s">
         <v>106</v>
@@ -4227,30 +4228,34 @@
       <c r="L14" s="14"/>
       <c r="M14" s="79"/>
     </row>
-    <row r="15" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="82" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C15" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="83"/>
+      <c r="D15" s="81">
+        <v>0.05</v>
+      </c>
+      <c r="E15" s="83">
+        <v>100</v>
+      </c>
       <c r="F15" s="80"/>
       <c r="G15" s="81"/>
       <c r="H15" s="83"/>
       <c r="I15" s="80"/>
       <c r="L15" s="80"/>
     </row>
-    <row r="16" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="82" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C16" s="82" t="s">
         <v>106</v>
       </c>
       <c r="D16" s="81">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="E16" s="83">
         <v>100</v>
@@ -4261,7 +4266,7 @@
       <c r="I16" s="80"/>
       <c r="L16" s="80"/>
     </row>
-    <row r="17" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="82" t="s">
         <v>199</v>
       </c>
@@ -4269,7 +4274,7 @@
         <v>106</v>
       </c>
       <c r="D17" s="81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="83">
         <v>100</v>
@@ -4280,15 +4285,15 @@
       <c r="I17" s="80"/>
       <c r="L17" s="80"/>
     </row>
-    <row r="18" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="82" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C18" s="82" t="s">
         <v>106</v>
       </c>
       <c r="D18" s="81">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E18" s="83">
         <v>100</v>
@@ -4299,15 +4304,15 @@
       <c r="I18" s="80"/>
       <c r="L18" s="80"/>
     </row>
-    <row r="19" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="82" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C19" s="82" t="s">
         <v>106</v>
       </c>
       <c r="D19" s="81">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E19" s="83">
         <v>100</v>
@@ -4318,9 +4323,9 @@
       <c r="I19" s="80"/>
       <c r="L19" s="80"/>
     </row>
-    <row r="20" spans="2:13" s="79" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B20" s="84" t="s">
-        <v>191</v>
+    <row r="20" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="82" t="s">
+        <v>212</v>
       </c>
       <c r="C20" s="82" t="s">
         <v>106</v>
@@ -4328,14 +4333,18 @@
       <c r="D20" s="81"/>
       <c r="E20" s="83"/>
       <c r="F20" s="80"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="83"/>
+      <c r="G20" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="83">
+        <v>100</v>
+      </c>
       <c r="I20" s="80"/>
       <c r="L20" s="80"/>
     </row>
-    <row r="21" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="82" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C21" s="82" t="s">
         <v>106</v>
@@ -4343,14 +4352,18 @@
       <c r="D21" s="81"/>
       <c r="E21" s="83"/>
       <c r="F21" s="80"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="83"/>
+      <c r="G21" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="H21" s="83">
+        <v>100</v>
+      </c>
       <c r="I21" s="80"/>
       <c r="L21" s="80"/>
     </row>
-    <row r="22" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="82" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C22" s="82" t="s">
         <v>106</v>
@@ -4358,14 +4371,18 @@
       <c r="D22" s="81"/>
       <c r="E22" s="83"/>
       <c r="F22" s="80"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="83"/>
+      <c r="G22" s="81">
+        <v>1</v>
+      </c>
+      <c r="H22" s="83">
+        <v>100</v>
+      </c>
       <c r="I22" s="80"/>
       <c r="L22" s="80"/>
     </row>
-    <row r="23" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="82" t="s">
-        <v>54</v>
+        <v>209</v>
       </c>
       <c r="C23" s="82" t="s">
         <v>106</v>
@@ -4373,14 +4390,18 @@
       <c r="D23" s="81"/>
       <c r="E23" s="83"/>
       <c r="F23" s="80"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="83"/>
+      <c r="G23" s="81">
+        <v>1</v>
+      </c>
+      <c r="H23" s="83">
+        <v>100</v>
+      </c>
       <c r="I23" s="80"/>
       <c r="L23" s="80"/>
     </row>
-    <row r="24" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="82" t="s">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="C24" s="82" t="s">
         <v>106</v>
@@ -4388,14 +4409,18 @@
       <c r="D24" s="81"/>
       <c r="E24" s="83"/>
       <c r="F24" s="80"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="83"/>
+      <c r="G24" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="83">
+        <v>100</v>
+      </c>
       <c r="I24" s="80"/>
       <c r="L24" s="80"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="82" t="s">
-        <v>91</v>
+        <v>217</v>
       </c>
       <c r="C25" s="82" t="s">
         <v>106</v>
@@ -4403,17 +4428,18 @@
       <c r="D25" s="81"/>
       <c r="E25" s="83"/>
       <c r="F25" s="80"/>
-      <c r="G25" s="81"/>
-      <c r="H25" s="83"/>
+      <c r="G25" s="81">
+        <v>3</v>
+      </c>
+      <c r="H25" s="83">
+        <v>100</v>
+      </c>
       <c r="I25" s="80"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
       <c r="L25" s="80"/>
-      <c r="M25" s="79"/>
-    </row>
-    <row r="26" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="82" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C26" s="82" t="s">
         <v>106</v>
@@ -4421,14 +4447,18 @@
       <c r="D26" s="81"/>
       <c r="E26" s="83"/>
       <c r="F26" s="80"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="83"/>
+      <c r="G26" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="H26" s="83">
+        <v>100</v>
+      </c>
       <c r="I26" s="80"/>
       <c r="L26" s="80"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="82" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="C27" s="82" t="s">
         <v>106</v>
@@ -4436,17 +4466,18 @@
       <c r="D27" s="81"/>
       <c r="E27" s="83"/>
       <c r="F27" s="80"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="83"/>
+      <c r="G27" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="83">
+        <v>100</v>
+      </c>
       <c r="I27" s="80"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="79"/>
       <c r="L27" s="80"/>
-      <c r="M27" s="79"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="82" t="s">
-        <v>46</v>
+        <v>206</v>
       </c>
       <c r="C28" s="82" t="s">
         <v>106</v>
@@ -4454,17 +4485,18 @@
       <c r="D28" s="81"/>
       <c r="E28" s="83"/>
       <c r="F28" s="80"/>
-      <c r="G28" s="81"/>
-      <c r="H28" s="83"/>
+      <c r="G28" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="H28" s="83">
+        <v>100</v>
+      </c>
       <c r="I28" s="80"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
       <c r="L28" s="80"/>
-      <c r="M28" s="79"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="82" t="s">
-        <v>45</v>
+        <v>207</v>
       </c>
       <c r="C29" s="82" t="s">
         <v>106</v>
@@ -4472,17 +4504,18 @@
       <c r="D29" s="81"/>
       <c r="E29" s="83"/>
       <c r="F29" s="80"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="83"/>
+      <c r="G29" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="H29" s="83">
+        <v>100</v>
+      </c>
       <c r="I29" s="80"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
       <c r="L29" s="80"/>
-      <c r="M29" s="79"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B30" s="82" t="s">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="C30" s="82" t="s">
         <v>106</v>
@@ -4490,17 +4523,18 @@
       <c r="D30" s="81"/>
       <c r="E30" s="83"/>
       <c r="F30" s="80"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="83"/>
+      <c r="G30" s="81">
+        <v>1.25</v>
+      </c>
+      <c r="H30" s="83">
+        <v>100</v>
+      </c>
       <c r="I30" s="80"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
       <c r="L30" s="80"/>
-      <c r="M30" s="79"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B31" s="82" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="C31" s="82" t="s">
         <v>106</v>
@@ -4508,17 +4542,18 @@
       <c r="D31" s="81"/>
       <c r="E31" s="83"/>
       <c r="F31" s="80"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="83"/>
+      <c r="G31" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="83">
+        <v>100</v>
+      </c>
       <c r="I31" s="80"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
       <c r="L31" s="80"/>
-      <c r="M31" s="79"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B32" s="82" t="s">
-        <v>57</v>
+        <v>210</v>
       </c>
       <c r="C32" s="82" t="s">
         <v>106</v>
@@ -4526,17 +4561,18 @@
       <c r="D32" s="81"/>
       <c r="E32" s="83"/>
       <c r="F32" s="80"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="83"/>
+      <c r="G32" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="H32" s="83">
+        <v>100</v>
+      </c>
       <c r="I32" s="80"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
       <c r="L32" s="80"/>
-      <c r="M32" s="79"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B33" s="82" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="C33" s="82" t="s">
         <v>106</v>
@@ -4544,17 +4580,18 @@
       <c r="D33" s="81"/>
       <c r="E33" s="83"/>
       <c r="F33" s="80"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="83"/>
+      <c r="G33" s="81">
+        <v>1.25</v>
+      </c>
+      <c r="H33" s="83">
+        <v>100</v>
+      </c>
       <c r="I33" s="80"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
       <c r="L33" s="80"/>
-      <c r="M33" s="79"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B34" s="82" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="C34" s="82" t="s">
         <v>106</v>
@@ -4565,14 +4602,11 @@
       <c r="G34" s="81"/>
       <c r="H34" s="83"/>
       <c r="I34" s="80"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
       <c r="L34" s="80"/>
-      <c r="M34" s="79"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B35" s="82" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
       <c r="C35" s="82" t="s">
         <v>106</v>
@@ -4583,14 +4617,11 @@
       <c r="G35" s="81"/>
       <c r="H35" s="83"/>
       <c r="I35" s="80"/>
-      <c r="J35" s="79"/>
-      <c r="K35" s="79"/>
       <c r="L35" s="80"/>
-      <c r="M35" s="79"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="82" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="C36" s="82" t="s">
         <v>106</v>
@@ -4601,14 +4632,11 @@
       <c r="G36" s="81"/>
       <c r="H36" s="83"/>
       <c r="I36" s="80"/>
-      <c r="J36" s="79"/>
-      <c r="K36" s="79"/>
       <c r="L36" s="80"/>
-      <c r="M36" s="79"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B37" s="82" t="s">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="C37" s="82" t="s">
         <v>106</v>
@@ -4619,46 +4647,32 @@
       <c r="G37" s="81"/>
       <c r="H37" s="83"/>
       <c r="I37" s="80"/>
-      <c r="J37" s="79"/>
-      <c r="K37" s="79"/>
       <c r="L37" s="80"/>
-      <c r="M37" s="79"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B38" s="74" t="s">
-        <v>203</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="81">
-        <v>0.5</v>
-      </c>
-      <c r="E38" s="83">
-        <v>100</v>
-      </c>
+    </row>
+    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="82" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="81"/>
+      <c r="E38" s="83"/>
       <c r="F38" s="80"/>
       <c r="G38" s="81"/>
       <c r="H38" s="83"/>
       <c r="I38" s="80"/>
-      <c r="J38" s="79"/>
-      <c r="K38" s="79"/>
       <c r="L38" s="80"/>
-      <c r="M38" s="79"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B39" s="74" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" s="81">
-        <v>1</v>
-      </c>
-      <c r="E39" s="83">
-        <v>100</v>
-      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B39" s="82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="81"/>
+      <c r="E39" s="83"/>
       <c r="F39" s="80"/>
       <c r="G39" s="81"/>
       <c r="H39" s="83"/>
@@ -4668,19 +4682,15 @@
       <c r="L39" s="80"/>
       <c r="M39" s="79"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B40" s="74" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" s="81">
-        <v>0.5</v>
-      </c>
-      <c r="E40" s="83">
-        <v>100</v>
-      </c>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B40" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="81"/>
+      <c r="E40" s="83"/>
       <c r="F40" s="80"/>
       <c r="G40" s="81"/>
       <c r="H40" s="83"/>
@@ -4690,19 +4700,15 @@
       <c r="L40" s="80"/>
       <c r="M40" s="79"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B41" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="E41" s="83">
-        <v>100</v>
-      </c>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B41" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="81"/>
+      <c r="E41" s="83"/>
       <c r="F41" s="80"/>
       <c r="G41" s="81"/>
       <c r="H41" s="83"/>
@@ -4712,31 +4718,30 @@
       <c r="L41" s="80"/>
       <c r="M41" s="79"/>
     </row>
-    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="74" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="81">
-        <v>0.5</v>
-      </c>
-      <c r="E42" s="83">
-        <v>100</v>
-      </c>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B42" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="81"/>
+      <c r="E42" s="83"/>
       <c r="F42" s="80"/>
       <c r="G42" s="81"/>
       <c r="H42" s="83"/>
       <c r="I42" s="80"/>
+      <c r="J42" s="79"/>
+      <c r="K42" s="79"/>
       <c r="L42" s="80"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B43" s="85" t="s">
-        <v>201</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>107</v>
+      <c r="M42" s="79"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B43" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="D43" s="81"/>
       <c r="E43" s="83"/>
@@ -4749,19 +4754,15 @@
       <c r="L43" s="80"/>
       <c r="M43" s="79"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B44" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D44" s="81">
-        <v>0.5</v>
-      </c>
-      <c r="E44" s="83">
-        <v>100</v>
-      </c>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B44" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="81"/>
+      <c r="E44" s="83"/>
       <c r="F44" s="80"/>
       <c r="G44" s="81"/>
       <c r="H44" s="83"/>
@@ -4771,19 +4772,15 @@
       <c r="L44" s="80"/>
       <c r="M44" s="79"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B45" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" s="81">
-        <v>0.75</v>
-      </c>
-      <c r="E45" s="83">
-        <v>100</v>
-      </c>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B45" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="81"/>
+      <c r="E45" s="83"/>
       <c r="F45" s="80"/>
       <c r="G45" s="81"/>
       <c r="H45" s="83"/>
@@ -4791,10 +4788,11 @@
       <c r="J45" s="79"/>
       <c r="K45" s="79"/>
       <c r="L45" s="80"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="M45" s="79"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="74" t="s">
-        <v>60</v>
+        <v>198</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>107</v>
@@ -4812,118 +4810,286 @@
       <c r="J46" s="79"/>
       <c r="K46" s="79"/>
       <c r="L46" s="80"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="M46" s="79"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="74" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="86">
+      <c r="D47" s="81">
         <v>1</v>
       </c>
       <c r="E47" s="83">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="F47" s="80"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="79"/>
+      <c r="L47" s="80"/>
+      <c r="M47" s="79"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B48" s="74" t="s">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="86">
-        <v>0.25</v>
+      <c r="D48" s="81">
+        <v>0.5</v>
       </c>
       <c r="E48" s="83">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="2:4" s="79" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F48" s="80"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="79"/>
+      <c r="K48" s="79"/>
+      <c r="L48" s="80"/>
+      <c r="M48" s="79"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B49" s="74" t="s">
-        <v>200</v>
+        <v>62</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="86"/>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D49" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="E49" s="83">
+        <v>100</v>
+      </c>
+      <c r="F49" s="80"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="80"/>
+      <c r="J49" s="79"/>
+      <c r="K49" s="79"/>
+      <c r="L49" s="80"/>
+      <c r="M49" s="79"/>
+    </row>
+    <row r="50" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="74" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="86"/>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B51" s="74" t="s">
-        <v>66</v>
+      <c r="D50" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E50" s="83">
+        <v>100</v>
+      </c>
+      <c r="F50" s="80"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="83"/>
+      <c r="I50" s="80"/>
+      <c r="L50" s="80"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B51" s="84" t="s">
+        <v>196</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D51" s="86"/>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D51" s="81"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="83"/>
+      <c r="I51" s="80"/>
+      <c r="J51" s="79"/>
+      <c r="K51" s="79"/>
+      <c r="L51" s="80"/>
+      <c r="M51" s="79"/>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B52" s="74" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D52" s="86"/>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B53" s="74"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="86"/>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B54" s="74"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="86"/>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B55" s="74"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="86"/>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B56" s="74"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="86"/>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B57" s="74"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="86"/>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B58" s="74"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="86"/>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B59" s="74"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="86"/>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B60" s="74"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="86"/>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D52" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E52" s="83">
+        <v>100</v>
+      </c>
+      <c r="F52" s="80"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="80"/>
+      <c r="J52" s="79"/>
+      <c r="K52" s="79"/>
+      <c r="L52" s="80"/>
+      <c r="M52" s="79"/>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B53" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="E53" s="83">
+        <v>100</v>
+      </c>
+      <c r="F53" s="80"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="80"/>
+      <c r="J53" s="79"/>
+      <c r="K53" s="79"/>
+      <c r="L53" s="80"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B54" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E54" s="83">
+        <v>100</v>
+      </c>
+      <c r="F54" s="80"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="80"/>
+      <c r="J54" s="79"/>
+      <c r="K54" s="79"/>
+      <c r="L54" s="80"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B55" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D55" s="85">
+        <v>1</v>
+      </c>
+      <c r="E55" s="83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B56" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="85">
+        <v>0.25</v>
+      </c>
+      <c r="E56" s="83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="74" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="85"/>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B58" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58" s="85"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B59" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="85"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B60" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="85"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B61" s="74"/>
-      <c r="D61" s="86"/>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C61" s="8"/>
+      <c r="D61" s="85"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B62" s="74"/>
-      <c r="D62" s="86"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="85"/>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B63" s="74"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="85"/>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B64" s="74"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="85"/>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B65" s="74"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="85"/>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B66" s="74"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="85"/>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B67" s="74"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="85"/>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B68" s="74"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="85"/>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B69" s="74"/>
+      <c r="D69" s="85"/>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B70" s="74"/>
+      <c r="D70" s="85"/>
     </row>
   </sheetData>
   <autoFilter ref="B4:L5" xr:uid="{2EE69061-1192-400C-B500-1B4897FD0585}"/>
@@ -4936,108 +5102,98 @@
     <mergeCell ref="L4:L5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B27:B41 B43:B46 B4:B20">
-    <cfRule type="expression" dxfId="35" priority="47">
+  <conditionalFormatting sqref="B51:B54 B4:B49">
+    <cfRule type="expression" dxfId="30" priority="47">
       <formula>MAX($E4,$H4,$K4)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C5 C9:C46">
-    <cfRule type="expression" dxfId="34" priority="44">
+  <conditionalFormatting sqref="C4:C5 C9:C54">
+    <cfRule type="expression" dxfId="29" priority="44">
       <formula>$C4="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="45">
+    <cfRule type="expression" dxfId="28" priority="45">
       <formula>$C4="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="46">
+    <cfRule type="expression" dxfId="27" priority="46">
       <formula>$C4="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="31" priority="43">
+    <cfRule type="expression" dxfId="26" priority="43">
       <formula>MAX($E1,$H1,$K1)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="30" priority="40">
+    <cfRule type="expression" dxfId="25" priority="40">
       <formula>$C1="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="41">
+    <cfRule type="expression" dxfId="24" priority="41">
       <formula>$C1="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="42">
+    <cfRule type="expression" dxfId="23" priority="42">
       <formula>$C1="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:B10">
-    <cfRule type="expression" dxfId="27" priority="36">
+    <cfRule type="expression" dxfId="22" priority="36">
       <formula>MAX($E9,$H9,$K9)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" dxfId="26" priority="30">
+    <cfRule type="expression" dxfId="21" priority="30">
       <formula>MAX($E12,$H12,$K12)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="expression" dxfId="25" priority="29">
+    <cfRule type="expression" dxfId="20" priority="29">
       <formula>MAX($E11,$H11,$K11)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="expression" dxfId="24" priority="28">
+    <cfRule type="expression" dxfId="19" priority="28">
       <formula>MAX($E11,$H11,$K11)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
-    <cfRule type="expression" dxfId="23" priority="83">
+  <conditionalFormatting sqref="B45">
+    <cfRule type="expression" dxfId="18" priority="83">
       <formula>MAX(#REF!,#REF!,#REF!)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B12">
-    <cfRule type="expression" dxfId="22" priority="25">
+    <cfRule type="expression" dxfId="17" priority="25">
       <formula>MAX($E6,$H6,$K6)=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C8">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="16" priority="22">
       <formula>$C6="Charlotte/Eddy"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="23">
+    <cfRule type="expression" dxfId="15" priority="23">
       <formula>$C6="Charlotte"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="24">
+    <cfRule type="expression" dxfId="14" priority="24">
       <formula>$C6="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:B26">
-    <cfRule type="expression" dxfId="18" priority="21">
-      <formula>MAX($E21,$H21,$K21)=100</formula>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="expression" dxfId="13" priority="85">
+      <formula>MAX($E51,$H51,$K51)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:B26">
-    <cfRule type="expression" dxfId="17" priority="20">
-      <formula>MAX($E21,$H21,$K21)=100</formula>
+  <conditionalFormatting sqref="B55:B70">
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>MAX($E55,$H55,$K55)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="expression" dxfId="16" priority="85">
-      <formula>MAX($E43,$H43,$K43)=100</formula>
+  <conditionalFormatting sqref="C55:C68">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>$C55="Charlotte/Eddy"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B62">
-    <cfRule type="expression" dxfId="15" priority="4">
-      <formula>MAX($E47,$H47,$K47)=100</formula>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>$C55="Charlotte"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C60">
-    <cfRule type="expression" dxfId="14" priority="1">
-      <formula>$C47="Charlotte/Eddy"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>$C47="Charlotte"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="3">
-      <formula>$C47="Eddy"</formula>
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>$C55="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5050,21 +5206,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="70.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" customWidth="1"/>
-    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -5078,151 +5234,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -5238,18 +5394,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -5273,7 +5429,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -5317,7 +5473,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -5339,7 +5495,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -5357,7 +5513,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -5375,7 +5531,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -5393,7 +5549,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -5411,7 +5567,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -5429,7 +5585,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -5447,7 +5603,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -5465,7 +5621,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -5483,7 +5639,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -5501,7 +5657,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -5519,7 +5675,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -5537,7 +5693,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -5555,7 +5711,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -5573,7 +5729,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -5591,7 +5747,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -5609,7 +5765,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -5627,7 +5783,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -5645,7 +5801,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -5663,7 +5819,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -5681,7 +5837,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -5699,7 +5855,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -5717,7 +5873,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -5735,7 +5891,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -5753,9 +5909,9 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>107</v>
@@ -5771,7 +5927,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -5789,7 +5945,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -5807,7 +5963,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -5825,7 +5981,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -5843,7 +5999,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -5865,47 +6021,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5917,48 +6073,48 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="51.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
-      <c r="B2" s="96" t="s">
+    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+      <c r="B2" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-    </row>
-    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.5">
-      <c r="B5" s="90" t="s">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+    </row>
+    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="91" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="52" t="s">
@@ -5967,7 +6123,7 @@
       <c r="E5" s="53">
         <v>46139</v>
       </c>
-      <c r="F5" s="94" t="s">
+      <c r="F5" s="93" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="55" t="s">
@@ -5976,7 +6132,7 @@
       <c r="H5" s="53">
         <v>46146</v>
       </c>
-      <c r="I5" s="94" t="s">
+      <c r="I5" s="93" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="55" t="s">
@@ -5985,7 +6141,7 @@
       <c r="K5" s="53">
         <v>46153</v>
       </c>
-      <c r="L5" s="94" t="s">
+      <c r="L5" s="93" t="s">
         <v>12</v>
       </c>
       <c r="M5" s="55" t="s">
@@ -5994,43 +6150,43 @@
       <c r="N5" s="53">
         <v>46161</v>
       </c>
-      <c r="O5" s="94" t="s">
+      <c r="O5" s="93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="91"/>
-      <c r="C6" s="93"/>
+    <row r="6" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="90"/>
+      <c r="C6" s="92"/>
       <c r="D6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="95"/>
+      <c r="F6" s="94"/>
       <c r="G6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="95"/>
+      <c r="I6" s="94"/>
       <c r="J6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="95"/>
+      <c r="L6" s="94"/>
       <c r="M6" s="54" t="s">
         <v>10</v>
       </c>
       <c r="N6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="95"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O6" s="94"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
       <c r="D7" s="33"/>
@@ -6046,7 +6202,7 @@
       <c r="N7" s="11"/>
       <c r="O7" s="12"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
       <c r="D8" s="31"/>
@@ -6058,7 +6214,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
       <c r="D9" s="31"/>
@@ -6070,7 +6226,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="36"/>
       <c r="C10" s="36"/>
       <c r="D10" s="31"/>
@@ -6082,7 +6238,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="31"/>
@@ -6094,7 +6250,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
       <c r="D12" s="31"/>
@@ -6106,7 +6262,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
       <c r="D13" s="31"/>
@@ -6118,7 +6274,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
       <c r="D14" s="31"/>
@@ -6130,7 +6286,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
       <c r="D15" s="31"/>
@@ -6142,7 +6298,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
       <c r="D16" s="31"/>
@@ -6154,7 +6310,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="31"/>
@@ -6166,7 +6322,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
       <c r="D18" s="31"/>
@@ -6178,7 +6334,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
       <c r="D19" s="31"/>
@@ -6190,7 +6346,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="56"/>
       <c r="C20" s="36"/>
       <c r="D20" s="31"/>
@@ -6202,7 +6358,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
       <c r="D21" s="31"/>
@@ -6214,7 +6370,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="36"/>
       <c r="C22" s="36"/>
       <c r="D22" s="31"/>
@@ -6226,7 +6382,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
       <c r="D23" s="31"/>
@@ -6238,7 +6394,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="36"/>
       <c r="C24" s="36"/>
       <c r="D24" s="40"/>
@@ -6250,7 +6406,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
       <c r="D25" s="31"/>
@@ -6262,7 +6418,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
       <c r="D26" s="31"/>
@@ -6274,7 +6430,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="36"/>
       <c r="C27" s="36"/>
       <c r="D27" s="31"/>
@@ -6286,7 +6442,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="36"/>
       <c r="C28" s="36"/>
       <c r="D28" s="31"/>
@@ -6298,7 +6454,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="18"/>
       <c r="C29" s="36"/>
       <c r="D29" s="31"/>
@@ -6310,7 +6466,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="36"/>
       <c r="C30" s="36"/>
       <c r="D30" s="31"/>
@@ -6322,7 +6478,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="36"/>
       <c r="C31" s="36"/>
       <c r="D31" s="31"/>
@@ -6334,7 +6490,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
       <c r="D32" s="31"/>
@@ -6346,7 +6502,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="36"/>
       <c r="C33" s="36"/>
       <c r="D33" s="31"/>
@@ -6358,7 +6514,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
       <c r="D34" s="31"/>
@@ -6370,7 +6526,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
       <c r="D35" s="31"/>
@@ -6382,7 +6538,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="36"/>
       <c r="C36" s="36"/>
       <c r="D36" s="31"/>
@@ -6394,7 +6550,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="36"/>
       <c r="C37" s="36"/>
       <c r="D37" s="31"/>
@@ -6406,7 +6562,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
       <c r="D38" s="31"/>
@@ -6418,7 +6574,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
       <c r="D39" s="32"/>
@@ -6491,28 +6647,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="93.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="2" max="2" width="93.21875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="42.81640625" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -6529,7 +6685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -6542,7 +6698,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -6555,7 +6711,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -6568,7 +6724,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -6581,7 +6737,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -6594,7 +6750,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -6607,7 +6763,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -6620,7 +6776,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -6633,7 +6789,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -6646,7 +6802,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -6659,7 +6815,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -6672,7 +6828,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -6685,7 +6841,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -6698,7 +6854,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -6711,7 +6867,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -6724,7 +6880,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -6737,7 +6893,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -6750,7 +6906,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -6763,7 +6919,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -6776,7 +6932,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -6789,7 +6945,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -6802,7 +6958,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -6815,7 +6971,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -6828,7 +6984,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -6841,7 +6997,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -6854,7 +7010,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -6867,7 +7023,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -6880,7 +7036,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -6893,7 +7049,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -6906,7 +7062,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -6919,7 +7075,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -6932,7 +7088,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -6945,7 +7101,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -6958,7 +7114,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -6971,7 +7127,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -6984,7 +7140,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -6997,7 +7153,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -7010,7 +7166,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -7023,7 +7179,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -7036,7 +7192,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -7049,7 +7205,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -7062,7 +7218,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -7075,7 +7231,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -7088,7 +7244,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -7101,7 +7257,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -7114,7 +7270,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -7127,7 +7283,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -7140,7 +7296,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -7153,7 +7309,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -7166,7 +7322,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -7179,7 +7335,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -7192,7 +7348,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -7205,7 +7361,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -7218,7 +7374,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -7231,7 +7387,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -7244,7 +7400,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -7257,7 +7413,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -7270,7 +7426,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -7283,7 +7439,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -7296,7 +7452,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -7307,7 +7463,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -7318,7 +7474,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -7329,7 +7485,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -7340,7 +7496,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -7351,7 +7507,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -7362,7 +7518,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -7373,7 +7529,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -7384,7 +7540,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -7395,7 +7551,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -7406,7 +7562,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -7417,182 +7573,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D705F6C-2928-4869-872A-EF1631713E7F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C83DF5-DA03-41A5-9BFC-2D0721530902}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -28,22 +28,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Planification trop détaillée'!$B$5:$F$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sprint 3'!$B$4:$L$5</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="221">
   <si>
     <t>Planification globale</t>
   </si>
@@ -700,6 +695,12 @@
   </si>
   <si>
     <t>Implémentation du Factory Pattern pour les aspects des pièces(couleur + divers apects,,)</t>
+  </si>
+  <si>
+    <t>Prevoir d envoyer un turn red dans statut sinon se declenche pas , prevoir un random de temps AI</t>
+  </si>
+  <si>
+    <t>Afficher le tour de jeu message au centre de l écran: Ajouter component YourTurn</t>
   </si>
 </sst>
 </file>
@@ -2029,26 +2030,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2062,7 +2063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="58" t="s">
         <v>152</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="62" t="s">
         <v>122</v>
       </c>
@@ -2090,7 +2091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="63" t="s">
         <v>123</v>
       </c>
@@ -2104,7 +2105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="63" t="s">
         <v>124</v>
       </c>
@@ -2118,7 +2119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="63" t="s">
         <v>125</v>
       </c>
@@ -2132,7 +2133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="63" t="s">
         <v>127</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="63" t="s">
         <v>128</v>
       </c>
@@ -2160,7 +2161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="63" t="s">
         <v>129</v>
       </c>
@@ -2174,7 +2175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="63" t="s">
         <v>156</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="63" t="s">
         <v>132</v>
       </c>
@@ -2202,7 +2203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="63" t="s">
         <v>133</v>
       </c>
@@ -2216,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="63" t="s">
         <v>135</v>
       </c>
@@ -2230,7 +2231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="63" t="s">
         <v>141</v>
       </c>
@@ -2244,7 +2245,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="59" t="s">
         <v>130</v>
       </c>
@@ -2258,7 +2259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="59" t="s">
         <v>131</v>
       </c>
@@ -2272,7 +2273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="59" t="s">
         <v>136</v>
       </c>
@@ -2286,7 +2287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="59" t="s">
         <v>137</v>
       </c>
@@ -2300,7 +2301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="59" t="s">
         <v>138</v>
       </c>
@@ -2314,7 +2315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="59" t="s">
         <v>140</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="59" t="s">
         <v>144</v>
       </c>
@@ -2342,7 +2343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="59" t="s">
         <v>145</v>
       </c>
@@ -2356,7 +2357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="59" t="s">
         <v>146</v>
       </c>
@@ -2370,7 +2371,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="64" t="s">
         <v>139</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="64" t="s">
         <v>142</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="64" t="s">
         <v>134</v>
       </c>
@@ -2412,7 +2413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="64" t="s">
         <v>143</v>
       </c>
@@ -2426,7 +2427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="64" t="s">
         <v>147</v>
       </c>
@@ -2440,7 +2441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="64" t="s">
         <v>148</v>
       </c>
@@ -2454,7 +2455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="64" t="s">
         <v>149</v>
       </c>
@@ -2468,7 +2469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="64" t="s">
         <v>150</v>
       </c>
@@ -2482,7 +2483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="64" t="s">
         <v>151</v>
       </c>
@@ -2496,7 +2497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="66" t="s">
         <v>126</v>
       </c>
@@ -2510,8 +2511,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D39" s="41" t="s">
         <v>157</v>
       </c>
@@ -2546,32 +2547,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2601,7 +2602,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2655,7 +2656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -2682,7 +2683,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="26" t="s">
         <v>96</v>
       </c>
@@ -2704,7 +2705,7 @@
       <c r="P6" s="31"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -2731,7 +2732,7 @@
       <c r="P7" s="31"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
@@ -2764,7 +2765,7 @@
       <c r="P8" s="31"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="26" t="s">
         <v>99</v>
       </c>
@@ -2801,7 +2802,7 @@
       </c>
       <c r="R9" s="28"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -2838,7 +2839,7 @@
       </c>
       <c r="R10" s="28"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="26" t="s">
         <v>101</v>
       </c>
@@ -2870,7 +2871,7 @@
       </c>
       <c r="R11" s="28"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="26" t="s">
         <v>102</v>
       </c>
@@ -2898,7 +2899,7 @@
       <c r="P12" s="31"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="47" t="s">
         <v>100</v>
       </c>
@@ -2925,15 +2926,15 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="17"/>
     </row>
-    <row r="21" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:19" x14ac:dyDescent="0.35">
       <c r="J21" s="20"/>
     </row>
-    <row r="25" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M25" s="20"/>
       <c r="P25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="10:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="10:19" x14ac:dyDescent="0.35">
       <c r="M26" s="20"/>
       <c r="P26" s="20"/>
       <c r="S26" s="20"/>
@@ -2949,24 +2950,24 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B2:M48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
-    <col min="2" max="2" width="77.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" customWidth="1"/>
+    <col min="2" max="2" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="74" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:12" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
       <c r="B3" s="86" t="s">
         <v>6</v>
       </c>
@@ -2981,8 +2982,8 @@
       <c r="K3" s="87"/>
       <c r="L3" s="88"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="2:12" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="89" t="s">
         <v>1</v>
       </c>
@@ -3017,7 +3018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="90"/>
       <c r="C6" s="92"/>
       <c r="D6" s="52" t="s">
@@ -3042,7 +3043,7 @@
       </c>
       <c r="L6" s="94"/>
     </row>
-    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="35" t="s">
         <v>24</v>
       </c>
@@ -3065,7 +3066,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="36" t="s">
         <v>35</v>
       </c>
@@ -3084,7 +3085,7 @@
       <c r="I8" s="14"/>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
@@ -3103,7 +3104,7 @@
       <c r="I9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="36" t="s">
         <v>75</v>
       </c>
@@ -3122,7 +3123,7 @@
       <c r="I10" s="14"/>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" s="36" t="s">
         <v>165</v>
       </c>
@@ -3141,7 +3142,7 @@
       <c r="I11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
         <v>25</v>
       </c>
@@ -3160,7 +3161,7 @@
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" s="36" t="s">
         <v>26</v>
       </c>
@@ -3179,7 +3180,7 @@
       <c r="I13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>27</v>
       </c>
@@ -3198,7 +3199,7 @@
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="36" t="s">
         <v>163</v>
       </c>
@@ -3217,7 +3218,7 @@
       <c r="I15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
         <v>29</v>
       </c>
@@ -3236,7 +3237,7 @@
       <c r="I16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" s="36" t="s">
         <v>30</v>
       </c>
@@ -3255,7 +3256,7 @@
       <c r="I17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
         <v>161</v>
       </c>
@@ -3274,7 +3275,7 @@
       <c r="I18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B19" s="36" t="s">
         <v>162</v>
       </c>
@@ -3293,7 +3294,7 @@
       <c r="I19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" s="56" t="s">
         <v>170</v>
       </c>
@@ -3312,7 +3313,7 @@
       <c r="I20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="2:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="36" t="s">
         <v>92</v>
       </c>
@@ -3333,7 +3334,7 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" s="36" t="s">
         <v>51</v>
       </c>
@@ -3352,7 +3353,7 @@
       <c r="I22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" s="36" t="s">
         <v>90</v>
       </c>
@@ -3373,7 +3374,7 @@
       </c>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="36" t="s">
         <v>74</v>
       </c>
@@ -3392,7 +3393,7 @@
       <c r="I24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
@@ -3411,7 +3412,7 @@
       <c r="I25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" s="36" t="s">
         <v>93</v>
       </c>
@@ -3432,7 +3433,7 @@
       </c>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" s="36" t="s">
         <v>94</v>
       </c>
@@ -3453,7 +3454,7 @@
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="77" t="s">
         <v>79</v>
       </c>
@@ -3474,7 +3475,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="77" t="s">
         <v>76</v>
       </c>
@@ -3493,7 +3494,7 @@
       <c r="I29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B30" s="82" t="s">
         <v>185</v>
       </c>
@@ -3512,7 +3513,7 @@
       <c r="I30" s="80"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B31" s="77" t="s">
         <v>42</v>
       </c>
@@ -3531,7 +3532,7 @@
       </c>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="77" t="s">
         <v>43</v>
       </c>
@@ -3550,7 +3551,7 @@
       </c>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="77" t="s">
         <v>164</v>
       </c>
@@ -3569,7 +3570,7 @@
       </c>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="77" t="s">
         <v>167</v>
       </c>
@@ -3588,7 +3589,7 @@
       </c>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="77" t="s">
         <v>73</v>
       </c>
@@ -3607,7 +3608,7 @@
       </c>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="77" t="s">
         <v>38</v>
       </c>
@@ -3626,7 +3627,7 @@
       </c>
       <c r="L36" s="14"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="77" t="s">
         <v>39</v>
       </c>
@@ -3645,7 +3646,7 @@
       </c>
       <c r="L37" s="14"/>
     </row>
-    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B38" s="82" t="s">
         <v>181</v>
       </c>
@@ -3664,7 +3665,7 @@
       </c>
       <c r="L38" s="80"/>
     </row>
-    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B39" s="82" t="s">
         <v>182</v>
       </c>
@@ -3683,7 +3684,7 @@
       </c>
       <c r="L39" s="80"/>
     </row>
-    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
         <v>179</v>
       </c>
@@ -3702,7 +3703,7 @@
       </c>
       <c r="L40" s="80"/>
     </row>
-    <row r="41" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B41" s="82" t="s">
         <v>180</v>
       </c>
@@ -3721,7 +3722,7 @@
       </c>
       <c r="L41" s="80"/>
     </row>
-    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B42" s="82" t="s">
         <v>177</v>
       </c>
@@ -3740,7 +3741,7 @@
       </c>
       <c r="L42" s="80"/>
     </row>
-    <row r="43" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B43" s="82" t="s">
         <v>176</v>
       </c>
@@ -3759,7 +3760,7 @@
       </c>
       <c r="L43" s="80"/>
     </row>
-    <row r="44" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B44" s="77" t="s">
         <v>172</v>
       </c>
@@ -3778,7 +3779,7 @@
       </c>
       <c r="L44" s="80"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="77" t="s">
         <v>171</v>
       </c>
@@ -3797,7 +3798,7 @@
       </c>
       <c r="L45" s="14"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="82" t="s">
         <v>175</v>
       </c>
@@ -3816,7 +3817,7 @@
       </c>
       <c r="L46" s="70"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="77" t="s">
         <v>183</v>
       </c>
@@ -3836,7 +3837,7 @@
       <c r="L47" s="70"/>
       <c r="M47" s="69"/>
     </row>
-    <row r="48" spans="2:13" s="73" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B48" s="74" t="s">
         <v>174</v>
       </c>
@@ -3954,24 +3955,24 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B1:M70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:M71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="21.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.81640625" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="11" max="11" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="46.8" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="2:13" ht="46.5" thickBot="1" x14ac:dyDescent="1.05">
       <c r="B1" s="86" t="s">
         <v>16</v>
       </c>
@@ -3986,8 +3987,8 @@
       <c r="K1" s="87"/>
       <c r="L1" s="88"/>
     </row>
-    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="2:13" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="89" t="s">
         <v>1</v>
       </c>
@@ -4022,7 +4023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="90"/>
       <c r="C5" s="92"/>
       <c r="D5" s="52" t="s">
@@ -4047,7 +4048,7 @@
       </c>
       <c r="L5" s="94"/>
     </row>
-    <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B6" s="82" t="s">
         <v>188</v>
       </c>
@@ -4066,7 +4067,7 @@
       <c r="I6" s="80"/>
       <c r="L6" s="80"/>
     </row>
-    <row r="7" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B7" s="82" t="s">
         <v>189</v>
       </c>
@@ -4085,7 +4086,7 @@
       <c r="I7" s="80"/>
       <c r="L7" s="80"/>
     </row>
-    <row r="8" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B8" s="82" t="s">
         <v>190</v>
       </c>
@@ -4104,7 +4105,7 @@
       <c r="I8" s="80"/>
       <c r="L8" s="80"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="82" t="s">
         <v>173</v>
       </c>
@@ -4125,7 +4126,7 @@
       <c r="K9" s="79"/>
       <c r="L9" s="80"/>
     </row>
-    <row r="10" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B10" s="82" t="s">
         <v>187</v>
       </c>
@@ -4144,7 +4145,7 @@
       <c r="I10" s="80"/>
       <c r="L10" s="80"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="82" t="s">
         <v>186</v>
       </c>
@@ -4166,7 +4167,7 @@
       <c r="L11" s="80"/>
       <c r="M11" s="79"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
         <v>178</v>
       </c>
@@ -4186,7 +4187,7 @@
       <c r="L12" s="14"/>
       <c r="M12" s="79"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="82" t="s">
         <v>184</v>
       </c>
@@ -4208,7 +4209,7 @@
       <c r="L13" s="80"/>
       <c r="M13" s="79"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="82" t="s">
         <v>191</v>
       </c>
@@ -4228,7 +4229,7 @@
       <c r="L14" s="14"/>
       <c r="M14" s="79"/>
     </row>
-    <row r="15" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B15" s="82" t="s">
         <v>192</v>
       </c>
@@ -4247,7 +4248,7 @@
       <c r="I15" s="80"/>
       <c r="L15" s="80"/>
     </row>
-    <row r="16" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B16" s="82" t="s">
         <v>194</v>
       </c>
@@ -4266,7 +4267,7 @@
       <c r="I16" s="80"/>
       <c r="L16" s="80"/>
     </row>
-    <row r="17" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B17" s="82" t="s">
         <v>199</v>
       </c>
@@ -4285,7 +4286,7 @@
       <c r="I17" s="80"/>
       <c r="L17" s="80"/>
     </row>
-    <row r="18" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B18" s="82" t="s">
         <v>200</v>
       </c>
@@ -4304,7 +4305,7 @@
       <c r="I18" s="80"/>
       <c r="L18" s="80"/>
     </row>
-    <row r="19" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B19" s="82" t="s">
         <v>201</v>
       </c>
@@ -4323,7 +4324,7 @@
       <c r="I19" s="80"/>
       <c r="L19" s="80"/>
     </row>
-    <row r="20" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B20" s="82" t="s">
         <v>212</v>
       </c>
@@ -4342,7 +4343,7 @@
       <c r="I20" s="80"/>
       <c r="L20" s="80"/>
     </row>
-    <row r="21" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B21" s="82" t="s">
         <v>202</v>
       </c>
@@ -4361,7 +4362,7 @@
       <c r="I21" s="80"/>
       <c r="L21" s="80"/>
     </row>
-    <row r="22" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B22" s="82" t="s">
         <v>213</v>
       </c>
@@ -4380,7 +4381,7 @@
       <c r="I22" s="80"/>
       <c r="L22" s="80"/>
     </row>
-    <row r="23" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B23" s="82" t="s">
         <v>209</v>
       </c>
@@ -4399,7 +4400,7 @@
       <c r="I23" s="80"/>
       <c r="L23" s="80"/>
     </row>
-    <row r="24" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
         <v>203</v>
       </c>
@@ -4418,7 +4419,7 @@
       <c r="I24" s="80"/>
       <c r="L24" s="80"/>
     </row>
-    <row r="25" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B25" s="82" t="s">
         <v>217</v>
       </c>
@@ -4437,7 +4438,7 @@
       <c r="I25" s="80"/>
       <c r="L25" s="80"/>
     </row>
-    <row r="26" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B26" s="82" t="s">
         <v>204</v>
       </c>
@@ -4456,7 +4457,7 @@
       <c r="I26" s="80"/>
       <c r="L26" s="80"/>
     </row>
-    <row r="27" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B27" s="82" t="s">
         <v>205</v>
       </c>
@@ -4475,7 +4476,7 @@
       <c r="I27" s="80"/>
       <c r="L27" s="80"/>
     </row>
-    <row r="28" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B28" s="82" t="s">
         <v>206</v>
       </c>
@@ -4494,7 +4495,7 @@
       <c r="I28" s="80"/>
       <c r="L28" s="80"/>
     </row>
-    <row r="29" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B29" s="82" t="s">
         <v>207</v>
       </c>
@@ -4513,7 +4514,7 @@
       <c r="I29" s="80"/>
       <c r="L29" s="80"/>
     </row>
-    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B30" s="82" t="s">
         <v>211</v>
       </c>
@@ -4532,7 +4533,7 @@
       <c r="I30" s="80"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
         <v>208</v>
       </c>
@@ -4551,7 +4552,7 @@
       <c r="I31" s="80"/>
       <c r="L31" s="80"/>
     </row>
-    <row r="32" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B32" s="82" t="s">
         <v>210</v>
       </c>
@@ -4570,7 +4571,7 @@
       <c r="I32" s="80"/>
       <c r="L32" s="80"/>
     </row>
-    <row r="33" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B33" s="82" t="s">
         <v>215</v>
       </c>
@@ -4589,9 +4590,9 @@
       <c r="I33" s="80"/>
       <c r="L33" s="80"/>
     </row>
-    <row r="34" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B34" s="82" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C34" s="82" t="s">
         <v>106</v>
@@ -4599,14 +4600,20 @@
       <c r="D34" s="81"/>
       <c r="E34" s="83"/>
       <c r="F34" s="80"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="80"/>
+      <c r="G34" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="H34" s="83">
+        <v>100</v>
+      </c>
+      <c r="I34" s="80" t="s">
+        <v>219</v>
+      </c>
       <c r="L34" s="80"/>
     </row>
-    <row r="35" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B35" s="82" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C35" s="82" t="s">
         <v>106</v>
@@ -4619,9 +4626,9 @@
       <c r="I35" s="80"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B36" s="82" t="s">
-        <v>214</v>
+        <v>54</v>
       </c>
       <c r="C36" s="82" t="s">
         <v>106</v>
@@ -4634,9 +4641,9 @@
       <c r="I36" s="80"/>
       <c r="L36" s="80"/>
     </row>
-    <row r="37" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B37" s="82" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="C37" s="82" t="s">
         <v>106</v>
@@ -4649,9 +4656,9 @@
       <c r="I37" s="80"/>
       <c r="L37" s="80"/>
     </row>
-    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B38" s="82" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C38" s="82" t="s">
         <v>106</v>
@@ -4664,9 +4671,9 @@
       <c r="I38" s="80"/>
       <c r="L38" s="80"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B39" s="82" t="s">
-        <v>46</v>
+        <v>218</v>
       </c>
       <c r="C39" s="82" t="s">
         <v>106</v>
@@ -4677,14 +4684,11 @@
       <c r="G39" s="81"/>
       <c r="H39" s="83"/>
       <c r="I39" s="80"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="79"/>
       <c r="L39" s="80"/>
-      <c r="M39" s="79"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C40" s="82" t="s">
         <v>106</v>
@@ -4700,9 +4704,9 @@
       <c r="L40" s="80"/>
       <c r="M40" s="79"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="82" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C41" s="82" t="s">
         <v>106</v>
@@ -4718,9 +4722,9 @@
       <c r="L41" s="80"/>
       <c r="M41" s="79"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="82" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C42" s="82" t="s">
         <v>106</v>
@@ -4736,9 +4740,9 @@
       <c r="L42" s="80"/>
       <c r="M42" s="79"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="82" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C43" s="82" t="s">
         <v>106</v>
@@ -4754,9 +4758,9 @@
       <c r="L43" s="80"/>
       <c r="M43" s="79"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="82" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C44" s="82" t="s">
         <v>106</v>
@@ -4772,9 +4776,9 @@
       <c r="L44" s="80"/>
       <c r="M44" s="79"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="82" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C45" s="82" t="s">
         <v>106</v>
@@ -4790,19 +4794,15 @@
       <c r="L45" s="80"/>
       <c r="M45" s="79"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B46" s="74" t="s">
-        <v>198</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" s="81">
-        <v>0.5</v>
-      </c>
-      <c r="E46" s="83">
-        <v>100</v>
-      </c>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B46" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="81"/>
+      <c r="E46" s="83"/>
       <c r="F46" s="80"/>
       <c r="G46" s="81"/>
       <c r="H46" s="83"/>
@@ -4812,15 +4812,15 @@
       <c r="L46" s="80"/>
       <c r="M46" s="79"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="74" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D47" s="81">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E47" s="83">
         <v>100</v>
@@ -4834,15 +4834,15 @@
       <c r="L47" s="80"/>
       <c r="M47" s="79"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="74" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D48" s="81">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E48" s="83">
         <v>100</v>
@@ -4856,15 +4856,15 @@
       <c r="L48" s="80"/>
       <c r="M48" s="79"/>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B49" s="74" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D49" s="81">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E49" s="83">
         <v>100</v>
@@ -4878,15 +4878,15 @@
       <c r="L49" s="80"/>
       <c r="M49" s="79"/>
     </row>
-    <row r="50" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="74" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D50" s="81">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E50" s="83">
         <v>100</v>
@@ -4895,39 +4895,39 @@
       <c r="G50" s="81"/>
       <c r="H50" s="83"/>
       <c r="I50" s="80"/>
+      <c r="J50" s="79"/>
+      <c r="K50" s="79"/>
       <c r="L50" s="80"/>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B51" s="84" t="s">
-        <v>196</v>
+      <c r="M50" s="79"/>
+    </row>
+    <row r="51" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="74" t="s">
+        <v>86</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D51" s="81"/>
-      <c r="E51" s="83"/>
+      <c r="D51" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="E51" s="83">
+        <v>100</v>
+      </c>
       <c r="F51" s="80"/>
       <c r="G51" s="81"/>
       <c r="H51" s="83"/>
       <c r="I51" s="80"/>
-      <c r="J51" s="79"/>
-      <c r="K51" s="79"/>
       <c r="L51" s="80"/>
-      <c r="M51" s="79"/>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B52" s="74" t="s">
-        <v>58</v>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B52" s="84" t="s">
+        <v>196</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D52" s="81">
-        <v>0.5</v>
-      </c>
-      <c r="E52" s="83">
-        <v>100</v>
-      </c>
+      <c r="D52" s="81"/>
+      <c r="E52" s="83"/>
       <c r="F52" s="80"/>
       <c r="G52" s="81"/>
       <c r="H52" s="83"/>
@@ -4937,15 +4937,15 @@
       <c r="L52" s="80"/>
       <c r="M52" s="79"/>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B53" s="74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D53" s="81">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E53" s="83">
         <v>100</v>
@@ -4957,16 +4957,17 @@
       <c r="J53" s="79"/>
       <c r="K53" s="79"/>
       <c r="L53" s="80"/>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M53" s="79"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D54" s="81">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E54" s="83">
         <v>100</v>
@@ -4979,117 +4980,138 @@
       <c r="K54" s="79"/>
       <c r="L54" s="80"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="74" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="85">
-        <v>1</v>
+      <c r="D55" s="81">
+        <v>0.5</v>
       </c>
       <c r="E55" s="83">
         <v>100</v>
       </c>
-    </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F55" s="80"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="80"/>
+      <c r="J55" s="79"/>
+      <c r="K55" s="79"/>
+      <c r="L55" s="80"/>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="74" t="s">
-        <v>197</v>
+        <v>57</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D56" s="85">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E56" s="83">
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="74" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D57" s="85"/>
-    </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D57" s="85">
+        <v>0.25</v>
+      </c>
+      <c r="E57" s="83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" s="79" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B58" s="74" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D58" s="85"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B59" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D59" s="85"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="74" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D60" s="85"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B61" s="74"/>
-      <c r="C61" s="8"/>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B61" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="D61" s="85"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="74"/>
       <c r="C62" s="8"/>
       <c r="D62" s="85"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="74"/>
       <c r="C63" s="8"/>
       <c r="D63" s="85"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="74"/>
       <c r="C64" s="8"/>
       <c r="D64" s="85"/>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B65" s="74"/>
       <c r="C65" s="8"/>
       <c r="D65" s="85"/>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B66" s="74"/>
       <c r="C66" s="8"/>
       <c r="D66" s="85"/>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B67" s="74"/>
       <c r="C67" s="8"/>
       <c r="D67" s="85"/>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B68" s="74"/>
       <c r="C68" s="8"/>
       <c r="D68" s="85"/>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B69" s="74"/>
+      <c r="C69" s="8"/>
       <c r="D69" s="85"/>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B70" s="74"/>
       <c r="D70" s="85"/>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B71" s="74"/>
+      <c r="D71" s="85"/>
     </row>
   </sheetData>
   <autoFilter ref="B4:L5" xr:uid="{2EE69061-1192-400C-B500-1B4897FD0585}"/>
@@ -5102,12 +5124,12 @@
     <mergeCell ref="L4:L5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B51:B54 B4:B49">
+  <conditionalFormatting sqref="B52:B55 B4:B50">
     <cfRule type="expression" dxfId="30" priority="47">
       <formula>MAX($E4,$H4,$K4)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C5 C9:C54">
+  <conditionalFormatting sqref="C4:C5 C9:C55">
     <cfRule type="expression" dxfId="29" priority="44">
       <formula>$C4="Charlotte/Eddy"</formula>
     </cfRule>
@@ -5154,7 +5176,7 @@
       <formula>MAX($E11,$H11,$K11)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
+  <conditionalFormatting sqref="B46">
     <cfRule type="expression" dxfId="18" priority="83">
       <formula>MAX(#REF!,#REF!,#REF!)=100</formula>
     </cfRule>
@@ -5175,25 +5197,25 @@
       <formula>$C6="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B51">
     <cfRule type="expression" dxfId="13" priority="85">
-      <formula>MAX($E51,$H51,$K51)=100</formula>
+      <formula>MAX($E52,$H52,$K52)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B70">
+  <conditionalFormatting sqref="B56:B71">
     <cfRule type="expression" dxfId="12" priority="4">
-      <formula>MAX($E55,$H55,$K55)=100</formula>
+      <formula>MAX($E56,$H56,$K56)=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C55:C68">
+  <conditionalFormatting sqref="C56:C69">
     <cfRule type="expression" dxfId="11" priority="1">
-      <formula>$C55="Charlotte/Eddy"</formula>
+      <formula>$C56="Charlotte/Eddy"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>$C55="Charlotte"</formula>
+      <formula>$C56="Charlotte"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="3">
-      <formula>$C55="Eddy"</formula>
+      <formula>$C56="Eddy"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5206,21 +5228,21 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="70.81640625" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:5" ht="46" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
@@ -5234,151 +5256,151 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
@@ -5394,18 +5416,18 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B2:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
@@ -5429,7 +5451,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
@@ -5473,7 +5495,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>95</v>
       </c>
@@ -5495,7 +5517,7 @@
       <c r="N6" s="11"/>
       <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -5513,7 +5535,7 @@
       <c r="M7" s="18"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
@@ -5531,7 +5553,7 @@
       <c r="M8" s="18"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>85</v>
       </c>
@@ -5549,7 +5571,7 @@
       <c r="M9" s="18"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>83</v>
       </c>
@@ -5567,7 +5589,7 @@
       <c r="M10" s="18"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>62</v>
       </c>
@@ -5585,7 +5607,7 @@
       <c r="M11" s="18"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>91</v>
       </c>
@@ -5603,7 +5625,7 @@
       <c r="M12" s="18"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
@@ -5621,7 +5643,7 @@
       <c r="M13" s="18"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
         <v>54</v>
       </c>
@@ -5639,7 +5661,7 @@
       <c r="M14" s="18"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
@@ -5657,7 +5679,7 @@
       <c r="M15" s="18"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>59</v>
       </c>
@@ -5675,7 +5697,7 @@
       <c r="M16" s="18"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
@@ -5693,7 +5715,7 @@
       <c r="M17" s="18"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="13" t="s">
         <v>63</v>
       </c>
@@ -5711,7 +5733,7 @@
       <c r="M18" s="18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
@@ -5729,7 +5751,7 @@
       <c r="M19" s="18"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -5747,7 +5769,7 @@
       <c r="M20" s="18"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
@@ -5765,7 +5787,7 @@
       <c r="M21" s="18"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>40</v>
       </c>
@@ -5783,7 +5805,7 @@
       <c r="M22" s="18"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
@@ -5801,7 +5823,7 @@
       <c r="M23" s="18"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
@@ -5819,7 +5841,7 @@
       <c r="M24" s="18"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
@@ -5837,7 +5859,7 @@
       <c r="M25" s="18"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>72</v>
       </c>
@@ -5855,7 +5877,7 @@
       <c r="M26" s="18"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
@@ -5873,7 +5895,7 @@
       <c r="M27" s="18"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
@@ -5891,7 +5913,7 @@
       <c r="M28" s="18"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>71</v>
       </c>
@@ -5909,7 +5931,7 @@
       <c r="M29" s="18"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>195</v>
       </c>
@@ -5927,7 +5949,7 @@
       </c>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
@@ -5945,7 +5967,7 @@
       </c>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
@@ -5963,7 +5985,7 @@
       </c>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>114</v>
       </c>
@@ -5981,7 +6003,7 @@
       </c>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
@@ -5999,7 +6021,7 @@
       </c>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="15" t="s">
         <v>70</v>
       </c>
@@ -6021,47 +6043,47 @@
       <c r="N35" s="16"/>
       <c r="O35" s="17"/>
     </row>
-    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B48" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6073,25 +6095,25 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="B2:O39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="46.2" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:15" ht="46" x14ac:dyDescent="1">
       <c r="B2" s="95" t="s">
         <v>17</v>
       </c>
@@ -6109,8 +6131,8 @@
       <c r="N2" s="96"/>
       <c r="O2" s="96"/>
     </row>
-    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="2:15" ht="21" x14ac:dyDescent="0.5">
       <c r="B5" s="89" t="s">
         <v>1</v>
       </c>
@@ -6154,7 +6176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="90"/>
       <c r="C6" s="92"/>
       <c r="D6" s="52" t="s">
@@ -6186,7 +6208,7 @@
       </c>
       <c r="O6" s="94"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
       <c r="D7" s="33"/>
@@ -6202,7 +6224,7 @@
       <c r="N7" s="11"/>
       <c r="O7" s="12"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
       <c r="D8" s="31"/>
@@ -6214,7 +6236,7 @@
       <c r="L8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
       <c r="D9" s="31"/>
@@ -6226,7 +6248,7 @@
       <c r="L9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="36"/>
       <c r="C10" s="36"/>
       <c r="D10" s="31"/>
@@ -6238,7 +6260,7 @@
       <c r="L10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="31"/>
@@ -6250,7 +6272,7 @@
       <c r="L11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
       <c r="D12" s="31"/>
@@ -6262,7 +6284,7 @@
       <c r="L12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
       <c r="D13" s="31"/>
@@ -6274,7 +6296,7 @@
       <c r="L13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
       <c r="D14" s="31"/>
@@ -6286,7 +6308,7 @@
       <c r="L14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
       <c r="D15" s="31"/>
@@ -6298,7 +6320,7 @@
       <c r="L15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
       <c r="D16" s="31"/>
@@ -6310,7 +6332,7 @@
       <c r="L16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="31"/>
@@ -6322,7 +6344,7 @@
       <c r="L17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
       <c r="D18" s="31"/>
@@ -6334,7 +6356,7 @@
       <c r="L18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
       <c r="D19" s="31"/>
@@ -6346,7 +6368,7 @@
       <c r="L19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="56"/>
       <c r="C20" s="36"/>
       <c r="D20" s="31"/>
@@ -6358,7 +6380,7 @@
       <c r="L20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
       <c r="D21" s="31"/>
@@ -6370,7 +6392,7 @@
       <c r="L21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="36"/>
       <c r="C22" s="36"/>
       <c r="D22" s="31"/>
@@ -6382,7 +6404,7 @@
       <c r="L22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
       <c r="D23" s="31"/>
@@ -6394,7 +6416,7 @@
       <c r="L23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="36"/>
       <c r="C24" s="36"/>
       <c r="D24" s="40"/>
@@ -6406,7 +6428,7 @@
       <c r="L24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
       <c r="D25" s="31"/>
@@ -6418,7 +6440,7 @@
       <c r="L25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
       <c r="D26" s="31"/>
@@ -6430,7 +6452,7 @@
       <c r="L26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="36"/>
       <c r="C27" s="36"/>
       <c r="D27" s="31"/>
@@ -6442,7 +6464,7 @@
       <c r="L27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="36"/>
       <c r="C28" s="36"/>
       <c r="D28" s="31"/>
@@ -6454,7 +6476,7 @@
       <c r="L28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="18"/>
       <c r="C29" s="36"/>
       <c r="D29" s="31"/>
@@ -6466,7 +6488,7 @@
       <c r="L29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="36"/>
       <c r="C30" s="36"/>
       <c r="D30" s="31"/>
@@ -6478,7 +6500,7 @@
       <c r="L30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="36"/>
       <c r="C31" s="36"/>
       <c r="D31" s="31"/>
@@ -6490,7 +6512,7 @@
       <c r="L31" s="14"/>
       <c r="O31" s="14"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
       <c r="D32" s="31"/>
@@ -6502,7 +6524,7 @@
       <c r="L32" s="14"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" s="36"/>
       <c r="C33" s="36"/>
       <c r="D33" s="31"/>
@@ -6514,7 +6536,7 @@
       <c r="L33" s="14"/>
       <c r="O33" s="14"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
       <c r="D34" s="31"/>
@@ -6526,7 +6548,7 @@
       <c r="L34" s="14"/>
       <c r="O34" s="14"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
       <c r="D35" s="31"/>
@@ -6538,7 +6560,7 @@
       <c r="L35" s="14"/>
       <c r="O35" s="14"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B36" s="36"/>
       <c r="C36" s="36"/>
       <c r="D36" s="31"/>
@@ -6550,7 +6572,7 @@
       <c r="L36" s="14"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B37" s="36"/>
       <c r="C37" s="36"/>
       <c r="D37" s="31"/>
@@ -6562,7 +6584,7 @@
       <c r="L37" s="14"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
       <c r="D38" s="31"/>
@@ -6574,7 +6596,7 @@
       <c r="L38" s="14"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
       <c r="D39" s="32"/>
@@ -6647,28 +6669,28 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:F101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="93.1796875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="44.7" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:6" ht="44.75" customHeight="1" x14ac:dyDescent="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:6" ht="46.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -6685,7 +6707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -6698,7 +6720,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -6711,7 +6733,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -6724,7 +6746,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
@@ -6737,7 +6759,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -6750,7 +6772,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -6763,7 +6785,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -6776,7 +6798,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
@@ -6789,7 +6811,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -6802,7 +6824,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
@@ -6815,7 +6837,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -6828,7 +6850,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>73</v>
       </c>
@@ -6841,7 +6863,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
@@ -6854,7 +6876,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -6867,7 +6889,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -6880,7 +6902,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -6893,7 +6915,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -6906,7 +6928,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -6919,7 +6941,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
@@ -6932,7 +6954,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -6945,7 +6967,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -6958,7 +6980,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -6971,7 +6993,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
@@ -6984,7 +7006,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -6997,7 +7019,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -7010,7 +7032,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>72</v>
       </c>
@@ -7023,7 +7045,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -7036,7 +7058,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
@@ -7049,7 +7071,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -7062,7 +7084,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
@@ -7075,7 +7097,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
@@ -7088,7 +7110,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
@@ -7101,7 +7123,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
@@ -7114,7 +7136,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
@@ -7127,7 +7149,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -7140,7 +7162,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
@@ -7153,7 +7175,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
@@ -7166,7 +7188,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
@@ -7179,7 +7201,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
@@ -7192,7 +7214,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
@@ -7205,7 +7227,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
@@ -7218,7 +7240,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3" t="s">
         <v>67</v>
       </c>
@@ -7231,7 +7253,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
         <v>88</v>
       </c>
@@ -7244,7 +7266,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" s="3" t="s">
         <v>69</v>
       </c>
@@ -7257,7 +7279,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" s="3" t="s">
         <v>70</v>
       </c>
@@ -7270,7 +7292,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>71</v>
       </c>
@@ -7283,7 +7305,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>74</v>
       </c>
@@ -7296,7 +7318,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>75</v>
       </c>
@@ -7309,7 +7331,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>76</v>
       </c>
@@ -7322,7 +7344,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="3" t="s">
         <v>87</v>
       </c>
@@ -7335,7 +7357,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
         <v>78</v>
       </c>
@@ -7348,7 +7370,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>79</v>
       </c>
@@ -7361,7 +7383,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
@@ -7374,7 +7396,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
@@ -7387,7 +7409,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="3" t="s">
         <v>83</v>
       </c>
@@ -7400,7 +7422,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>84</v>
       </c>
@@ -7413,7 +7435,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" s="3" t="s">
         <v>85</v>
       </c>
@@ -7426,7 +7448,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B63" s="3" t="s">
         <v>86</v>
       </c>
@@ -7439,7 +7461,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="3" t="s">
         <v>77</v>
       </c>
@@ -7452,7 +7474,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" s="3" t="s">
         <v>96</v>
       </c>
@@ -7463,7 +7485,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" s="3" t="s">
         <v>97</v>
       </c>
@@ -7474,7 +7496,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
@@ -7485,7 +7507,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" s="3" t="s">
         <v>99</v>
       </c>
@@ -7496,7 +7518,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="3" t="s">
         <v>100</v>
       </c>
@@ -7507,7 +7529,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" s="3" t="s">
         <v>101</v>
       </c>
@@ -7518,7 +7540,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" s="3" t="s">
         <v>102</v>
       </c>
@@ -7529,7 +7551,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
         <v>103</v>
       </c>
@@ -7540,7 +7562,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
         <v>104</v>
       </c>
@@ -7551,7 +7573,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
         <v>120</v>
       </c>
@@ -7562,7 +7584,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
         <v>121</v>
       </c>
@@ -7573,182 +7595,182 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C83DF5-DA03-41A5-9BFC-2D0721530902}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4386DCE5-2AD6-4799-9046-B999A47CBBCC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="223">
   <si>
     <t>Planification globale</t>
   </si>
@@ -701,6 +701,12 @@
   </si>
   <si>
     <t>Afficher le tour de jeu message au centre de l écran: Ajouter component YourTurn</t>
+  </si>
+  <si>
+    <t>Implémentation des combats</t>
+  </si>
+  <si>
+    <t>Erreurs d'affichage, problèmes avec la pause pour l'affichage</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1296,6 +1302,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3964,8 +3976,8 @@
     <col min="4" max="4" width="21.81640625" customWidth="1"/>
     <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="83" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" style="83" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="52.81640625" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.54296875" bestFit="1" customWidth="1"/>
@@ -4004,7 +4016,7 @@
       <c r="F4" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="55" t="s">
+      <c r="G4" s="98" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="53">
@@ -4033,10 +4045,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="94"/>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="97" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="94"/>
@@ -4120,7 +4132,6 @@
       </c>
       <c r="F9" s="80"/>
       <c r="G9" s="81"/>
-      <c r="H9" s="83"/>
       <c r="I9" s="80"/>
       <c r="J9" s="79"/>
       <c r="K9" s="79"/>
@@ -4160,7 +4171,6 @@
       </c>
       <c r="F11" s="80"/>
       <c r="G11" s="81"/>
-      <c r="H11" s="83"/>
       <c r="I11" s="80"/>
       <c r="J11" s="79"/>
       <c r="K11" s="79"/>
@@ -4181,8 +4191,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="14"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="40"/>
+      <c r="G12" s="81"/>
       <c r="I12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="79"/>
@@ -4202,7 +4211,6 @@
       </c>
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
-      <c r="H13" s="83"/>
       <c r="I13" s="80"/>
       <c r="J13" s="79"/>
       <c r="K13" s="79"/>
@@ -4223,8 +4231,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="14"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="40"/>
+      <c r="G14" s="81"/>
       <c r="I14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="79"/>
@@ -4697,7 +4704,6 @@
       <c r="E40" s="83"/>
       <c r="F40" s="80"/>
       <c r="G40" s="81"/>
-      <c r="H40" s="83"/>
       <c r="I40" s="80"/>
       <c r="J40" s="79"/>
       <c r="K40" s="79"/>
@@ -4715,7 +4721,6 @@
       <c r="E41" s="83"/>
       <c r="F41" s="80"/>
       <c r="G41" s="81"/>
-      <c r="H41" s="83"/>
       <c r="I41" s="80"/>
       <c r="J41" s="79"/>
       <c r="K41" s="79"/>
@@ -4733,7 +4738,6 @@
       <c r="E42" s="83"/>
       <c r="F42" s="80"/>
       <c r="G42" s="81"/>
-      <c r="H42" s="83"/>
       <c r="I42" s="80"/>
       <c r="J42" s="79"/>
       <c r="K42" s="79"/>
@@ -4751,7 +4755,6 @@
       <c r="E43" s="83"/>
       <c r="F43" s="80"/>
       <c r="G43" s="81"/>
-      <c r="H43" s="83"/>
       <c r="I43" s="80"/>
       <c r="J43" s="79"/>
       <c r="K43" s="79"/>
@@ -4769,7 +4772,6 @@
       <c r="E44" s="83"/>
       <c r="F44" s="80"/>
       <c r="G44" s="81"/>
-      <c r="H44" s="83"/>
       <c r="I44" s="80"/>
       <c r="J44" s="79"/>
       <c r="K44" s="79"/>
@@ -4787,7 +4789,6 @@
       <c r="E45" s="83"/>
       <c r="F45" s="80"/>
       <c r="G45" s="81"/>
-      <c r="H45" s="83"/>
       <c r="I45" s="80"/>
       <c r="J45" s="79"/>
       <c r="K45" s="79"/>
@@ -4805,7 +4806,6 @@
       <c r="E46" s="83"/>
       <c r="F46" s="80"/>
       <c r="G46" s="81"/>
-      <c r="H46" s="83"/>
       <c r="I46" s="80"/>
       <c r="J46" s="79"/>
       <c r="K46" s="79"/>
@@ -4827,7 +4827,6 @@
       </c>
       <c r="F47" s="80"/>
       <c r="G47" s="81"/>
-      <c r="H47" s="83"/>
       <c r="I47" s="80"/>
       <c r="J47" s="79"/>
       <c r="K47" s="79"/>
@@ -4849,7 +4848,6 @@
       </c>
       <c r="F48" s="80"/>
       <c r="G48" s="81"/>
-      <c r="H48" s="83"/>
       <c r="I48" s="80"/>
       <c r="J48" s="79"/>
       <c r="K48" s="79"/>
@@ -4871,7 +4869,6 @@
       </c>
       <c r="F49" s="80"/>
       <c r="G49" s="81"/>
-      <c r="H49" s="83"/>
       <c r="I49" s="80"/>
       <c r="J49" s="79"/>
       <c r="K49" s="79"/>
@@ -4893,7 +4890,6 @@
       </c>
       <c r="F50" s="80"/>
       <c r="G50" s="81"/>
-      <c r="H50" s="83"/>
       <c r="I50" s="80"/>
       <c r="J50" s="79"/>
       <c r="K50" s="79"/>
@@ -4930,7 +4926,6 @@
       <c r="E52" s="83"/>
       <c r="F52" s="80"/>
       <c r="G52" s="81"/>
-      <c r="H52" s="83"/>
       <c r="I52" s="80"/>
       <c r="J52" s="79"/>
       <c r="K52" s="79"/>
@@ -4952,7 +4947,6 @@
       </c>
       <c r="F53" s="80"/>
       <c r="G53" s="81"/>
-      <c r="H53" s="83"/>
       <c r="I53" s="80"/>
       <c r="J53" s="79"/>
       <c r="K53" s="79"/>
@@ -4974,7 +4968,6 @@
       </c>
       <c r="F54" s="80"/>
       <c r="G54" s="81"/>
-      <c r="H54" s="83"/>
       <c r="I54" s="80"/>
       <c r="J54" s="79"/>
       <c r="K54" s="79"/>
@@ -4995,7 +4988,6 @@
       </c>
       <c r="F55" s="80"/>
       <c r="G55" s="81"/>
-      <c r="H55" s="83"/>
       <c r="I55" s="80"/>
       <c r="J55" s="79"/>
       <c r="K55" s="79"/>
@@ -5037,6 +5029,8 @@
         <v>107</v>
       </c>
       <c r="D58" s="85"/>
+      <c r="G58" s="83"/>
+      <c r="H58" s="83"/>
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B59" s="74" t="s">
@@ -5045,7 +5039,12 @@
       <c r="C59" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="85"/>
+      <c r="D59" s="85">
+        <v>1.5</v>
+      </c>
+      <c r="E59" s="83">
+        <v>75</v>
+      </c>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="74" t="s">
@@ -5055,6 +5054,12 @@
         <v>107</v>
       </c>
       <c r="D60" s="85"/>
+      <c r="G60" s="83">
+        <v>2</v>
+      </c>
+      <c r="H60" s="83">
+        <v>25</v>
+      </c>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="74" t="s">
@@ -5066,9 +5071,22 @@
       <c r="D61" s="85"/>
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B62" s="74"/>
-      <c r="C62" s="8"/>
+      <c r="B62" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="D62" s="85"/>
+      <c r="G62" s="83">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="83">
+        <v>75</v>
+      </c>
+      <c r="I62" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="74"/>

--- a/doc/C61_-_Document_de_planification_L_Attaque.xlsx
+++ b/doc/C61_-_Document_de_planification_L_Attaque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrateur.UTILISA-LQC2BC3\Downloads\__Projet_Projet\L-Attaque\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chacy\My Shit\L-Attaque\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE90C27A-1AA3-4C66-B21A-29E48D28FDDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE37183-6DA6-4031-8F15-03FDB66025D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{0139C51A-36D8-4FB0-B647-CB90E1DC24D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="216">
   <si>
     <t>Planification globale</t>
   </si>
@@ -591,9 +602,6 @@
     <t>Importation des svg en tant que Composant pour les pieces</t>
   </si>
   <si>
-    <t>Implémentation du chat entre joueurs: création de la base de donnée</t>
-  </si>
-  <si>
     <t>Implémenter le MCTS</t>
   </si>
   <si>
@@ -685,6 +693,9 @@
   </si>
   <si>
     <t>Ajouter le score de chaque joueur scores</t>
+  </si>
+  <si>
+    <t>Reste à tester, mais semble fonctionner</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1079,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1159,40 +1170,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1229,94 +1207,14 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="52">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill>
@@ -1407,21 +1305,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFCFDCF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor rgb="FFCCFFFF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFCFDCF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1454,13 +1359,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFCFDCF"/>
         </patternFill>
       </fill>
@@ -1470,18 +1368,6 @@
         <patternFill>
           <bgColor rgb="FFCCFFFF"/>
         </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
       </fill>
     </dxf>
     <dxf>
@@ -1533,124 +1419,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCFDCF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color rgb="FFFCFDCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFCCFFFF"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1671,9 +1439,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1711,7 +1479,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1817,7 +1585,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1959,7 +1727,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1971,26 +1739,26 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="B1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
     <col min="2" max="2" width="116" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="42.81640625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="42.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="44.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="2:5" ht="44.85" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="2:5" ht="46.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2004,7 +1772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="50" t="s">
         <v>141</v>
       </c>
@@ -2018,7 +1786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
         <v>111</v>
       </c>
@@ -2032,7 +1800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="55" t="s">
         <v>112</v>
       </c>
@@ -2046,7 +1814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="55" t="s">
         <v>113</v>
       </c>
@@ -2060,7 +1828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="55" t="s">
         <v>114</v>
       </c>
@@ -2074,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="55" t="s">
         <v>116</v>
       </c>
@@ -2088,7 +1856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="55" t="s">
         <v>117</v>
       </c>
@@ -2102,7 +1870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="55" t="s">
         <v>118</v>
       </c>
@@ -2116,7 +1884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="55" t="s">
         <v>145</v>
       </c>
@@ -2130,7 +1898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="55" t="s">
         <v>121</v>
       </c>
@@ -2144,7 +1912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="55" t="s">
         <v>122</v>
       </c>
@@ -2158,7 +1926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="55" t="s">
         <v>124</v>
       </c>
@@ -2172,7 +1940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="55" t="s">
         <v>130</v>
       </c>
@@ -2186,7 +1954,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="51" t="s">
         <v>119</v>
       </c>
@@ -2200,7 +1968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="51" t="s">
         <v>120</v>
       </c>
@@ -2214,7 +1982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="51" t="s">
         <v>125</v>
       </c>
@@ -2228,7 +1996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
         <v>126</v>
       </c>
@@ -2242,7 +2010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="51" t="s">
         <v>127</v>
       </c>
@@ -2256,7 +2024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="51" t="s">
         <v>129</v>
       </c>
@@ -2270,7 +2038,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="51" t="s">
         <v>133</v>
       </c>
@@ -2284,7 +2052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="51" t="s">
         <v>134</v>
       </c>
@@ -2298,7 +2066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="51" t="s">
         <v>135</v>
       </c>
@@ -2312,7 +2080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="56" t="s">
         <v>128</v>
       </c>
@@ -2326,7 +2094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="56" t="s">
         <v>131</v>
       </c>
@@ -2340,7 +2108,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="56" t="s">
         <v>123</v>
       </c>
@@ -2354,7 +2122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="56" t="s">
         <v>132</v>
       </c>
@@ -2368,7 +2136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="56" t="s">
         <v>136</v>
       </c>
@@ -2382,7 +2150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="56" t="s">
         <v>137</v>
       </c>
@@ -2396,7 +2164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="56" t="s">
         <v>138</v>
       </c>
@@ -2410,7 +2178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="56" t="s">
         <v>139</v>
       </c>
@@ -2424,7 +2192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="56" t="s">
         <v>140</v>
       </c>
@@ -2438,7 +2206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="58" t="s">
         <v>115</v>
       </c>
@@ -2452,8 +2220,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D39" s="33" t="s">
         <v>146</v>
       </c>
@@ -2465,7 +2233,7 @@
   </sheetData>
   <autoFilter ref="B5:E37" xr:uid="{93133217-C8F5-4788-AEEB-7509B70AEF5D}"/>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>MAX($E6,$H6,$K6)=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2488,32 +2256,32 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:S26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.1796875" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
-    <col min="15" max="15" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.85546875" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="15" max="15" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46" x14ac:dyDescent="1">
+    <row r="1" spans="1:18" ht="46.5" x14ac:dyDescent="0.7">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2543,7 +2311,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2597,7 +2365,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
         <v>95</v>
       </c>
@@ -2624,7 +2392,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="10"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
